--- a/first-atlas/producao_2026-03.xlsx
+++ b/first-atlas/producao_2026-03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2403BADF-EE72-454D-A2B4-48416FC4AA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DF4399-D388-4AE9-90F2-B01A2028E700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2585" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3824" uniqueCount="1161">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -2432,12 +2432,6 @@
     <t>C. HENRIQUE SOARES SOUZA LTDA</t>
   </si>
   <si>
-    <t>Procuracao da empresa, assinada via gov.br ou por meio de procuracao publica, em formato PDF. O documento deve conter, de forma expressa, os poderes para abrir e movimentar contas, alem de identificar corretamente o outorgante e o outorgado.</t>
-  </si>
-  <si>
-    <t>Procuracao da empresa M C COMERCIO AUTOMOTIVO LTDA, assinada via gov.br ou por meio de procuracao publica, em formato PDF. O documento deve conter, de forma expressa, os poderes para abrir e movimentar contas, alem de identificar corretamente o outorgante e o outorgado.</t>
-  </si>
-  <si>
     <t>( A procuracao precisa ser assinada via gov. pelos socios ) Procuracao da empresa RP FAUSTINO LTDA. Identificamos que a representacao da sua empresa e realizada em conjunto pelos representantes nomeados na clausula de administracao do contrato social e, por esse motivo, e necessario que os demais representantes tambem assinem a procuracao, via gov.br ou por meio de procuracao publica, em formato PDF.</t>
   </si>
   <si>
@@ -2448,6 +2442,1086 @@
   </si>
   <si>
     <t>Procuracao da empresa L &amp; C INCORPORADORA E EMPREENDIMENTOS LTDA. Identificamos que a representacao da sua empresa e realizada em conjunto pelos representantes nomeados na clausula de administracao do contrato social e, por esse motivo, e necessario que os demais representantes tambem assinem a procuracao, via gov.br ou por meio de procuracao publica, em formato PDF.</t>
+  </si>
+  <si>
+    <t>INVÁLIDA</t>
+  </si>
+  <si>
+    <t>17052388000177</t>
+  </si>
+  <si>
+    <t>FERRAGUT SOLUCOES EM TI LTDA</t>
+  </si>
+  <si>
+    <t>11931249000137</t>
+  </si>
+  <si>
+    <t>BRASIL ASSESSORIA E PRESTACAO DE SERVICOS IMOBILIARIOS LTDA</t>
+  </si>
+  <si>
+    <t>64506125000170</t>
+  </si>
+  <si>
+    <t>ORSINI TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>27483729000112</t>
+  </si>
+  <si>
+    <t>PRADO SISTEMAS CONSTRUTIVOS LTDA</t>
+  </si>
+  <si>
+    <t>61635526000132</t>
+  </si>
+  <si>
+    <t>EMS  CONSULTORIA EM COMPRAS LTDA</t>
+  </si>
+  <si>
+    <t>58889299000167</t>
+  </si>
+  <si>
+    <t>LUCAS DA SILVA MEDEIROS</t>
+  </si>
+  <si>
+    <t>63531643000181</t>
+  </si>
+  <si>
+    <t>EDESIO CLAUDIO SPINDOLA BRAGA</t>
+  </si>
+  <si>
+    <t>65562676000114</t>
+  </si>
+  <si>
+    <t>AQUINO CONSULTORIA IMOBILIARIA LTDA</t>
+  </si>
+  <si>
+    <t>27108957000102</t>
+  </si>
+  <si>
+    <t>ANA CAROLINA COUTINHO PINA</t>
+  </si>
+  <si>
+    <t>48424127000164</t>
+  </si>
+  <si>
+    <t>SERRA MAR SOLUCOES COMERCIAIS LTDA</t>
+  </si>
+  <si>
+    <t>34403799000189</t>
+  </si>
+  <si>
+    <t>JH LOCACOES E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>46955140000114</t>
+  </si>
+  <si>
+    <t>J D &amp; R M COMERCIO DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>30052337000103</t>
+  </si>
+  <si>
+    <t>A F H SOLUCOES LTDA</t>
+  </si>
+  <si>
+    <t>64774147000111</t>
+  </si>
+  <si>
+    <t>TH ARTEE LTDA</t>
+  </si>
+  <si>
+    <t>26587324000161</t>
+  </si>
+  <si>
+    <t>G PECAS SERVICOS E VENDAS DE VEICULOS LTDA</t>
+  </si>
+  <si>
+    <t>59272901000185</t>
+  </si>
+  <si>
+    <t>BASE LC MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>31504879000132</t>
+  </si>
+  <si>
+    <t>H LIMA CONSULTORIA E ASSESSORIA LTDA</t>
+  </si>
+  <si>
+    <t>54131850000158</t>
+  </si>
+  <si>
+    <t>ZION TECNOLOGIA LTDA</t>
+  </si>
+  <si>
+    <t>51300833000109</t>
+  </si>
+  <si>
+    <t>PREFHOME IMOBILIARIA LTDA</t>
+  </si>
+  <si>
+    <t>37072172000180</t>
+  </si>
+  <si>
+    <t>VANESSA WULFF COLVARA NEVES E CIA LTDA</t>
+  </si>
+  <si>
+    <t>41522537000107</t>
+  </si>
+  <si>
+    <t>CVB MATERIAIS DE CONSTRUCAO LTDA</t>
+  </si>
+  <si>
+    <t>13529155000161</t>
+  </si>
+  <si>
+    <t>BBB PRESENTES ULTILIDADES &amp; MERCEARIA LTDA</t>
+  </si>
+  <si>
+    <t>20411309000181</t>
+  </si>
+  <si>
+    <t>ALJ ESQUADRIAS DE ALUMINIO LTDA</t>
+  </si>
+  <si>
+    <t>59127011000180</t>
+  </si>
+  <si>
+    <t>VEM PLANEJARE SOB MEDIDA LTDA</t>
+  </si>
+  <si>
+    <t>49417514000136</t>
+  </si>
+  <si>
+    <t>F RIBEIRO CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>63817975000127</t>
+  </si>
+  <si>
+    <t>FERREIRA FUNILARIA E PINTURA LTDA</t>
+  </si>
+  <si>
+    <t>63328714000143</t>
+  </si>
+  <si>
+    <t>KATIA A. DOS SANTOS RESTAURANTE SABOR DA CASA LTDA</t>
+  </si>
+  <si>
+    <t>65371849000117</t>
+  </si>
+  <si>
+    <t>EDVALDO RODRIGUES DA COSTA JUNIOR</t>
+  </si>
+  <si>
+    <t>62278773000191</t>
+  </si>
+  <si>
+    <t>F LUCAS VINICIUS CARDOSO LTDA</t>
+  </si>
+  <si>
+    <t>04134834000140</t>
+  </si>
+  <si>
+    <t>COSTA E TEIXEIRA CONSTRUCOES E EMPREENDIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>19352882000182</t>
+  </si>
+  <si>
+    <t>MJ OLIVEIRA MERCEARIA LTDA</t>
+  </si>
+  <si>
+    <t>65461133000100</t>
+  </si>
+  <si>
+    <t>ANALUIZA FERREIRA DONATTI FISIOTERAPIA E REABILITACAO LTDA</t>
+  </si>
+  <si>
+    <t>61744281000181</t>
+  </si>
+  <si>
+    <t>RJ LIMA CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>63107500000147</t>
+  </si>
+  <si>
+    <t>WR COMERCIO DE ALIMENTOS E VAREJO LTDA</t>
+  </si>
+  <si>
+    <t>63938510000124</t>
+  </si>
+  <si>
+    <t>INSTALACAO E MANUTENCAO SAO PAULO INOVA SIMPLES (I.S.)</t>
+  </si>
+  <si>
+    <t>01151948000100</t>
+  </si>
+  <si>
+    <t>SAPATARIA CANTINHO DOS PES LTDA</t>
+  </si>
+  <si>
+    <t>14368639000139</t>
+  </si>
+  <si>
+    <t>KERLLUZ MONTAGENS DE ESTANDES E CENOGRAFIA LTDA</t>
+  </si>
+  <si>
+    <t>96501333000173</t>
+  </si>
+  <si>
+    <t>BMVS MONTAGENS INDUSTRIAIS LTDA</t>
+  </si>
+  <si>
+    <t>53267468000103</t>
+  </si>
+  <si>
+    <t>NEXT GESTAO DE OBRAS E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>63103534000163</t>
+  </si>
+  <si>
+    <t>ETAL TRANSPORTES ARMAZENAMENTO E LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t>62010280000176</t>
+  </si>
+  <si>
+    <t>A.C.G ESQUADRIX INSTALACAO DE ESQUADRIAS DE ALUMINIO SOCIEDADE UNIPESSOAL LTDA</t>
+  </si>
+  <si>
+    <t>61434461000167</t>
+  </si>
+  <si>
+    <t>UNIDOS DA TREZE</t>
+  </si>
+  <si>
+    <t>52502990000160</t>
+  </si>
+  <si>
+    <t>ARTEC ICE LTDA</t>
+  </si>
+  <si>
+    <t>64264028000119</t>
+  </si>
+  <si>
+    <t>GERALDO TARGINO RODRIGUES</t>
+  </si>
+  <si>
+    <t>60912939000154</t>
+  </si>
+  <si>
+    <t>BORRACHARIA GR LTDA</t>
+  </si>
+  <si>
+    <t>58823206000100</t>
+  </si>
+  <si>
+    <t>DOCE E COMERCIO SUDOESTE LTDA</t>
+  </si>
+  <si>
+    <t>64815233000125</t>
+  </si>
+  <si>
+    <t>ESQUADRISAN SERRALHERIA LTDA</t>
+  </si>
+  <si>
+    <t>10518222000154</t>
+  </si>
+  <si>
+    <t>ADAPTEC HIDRAULICA E PNEUMATICA LTDA</t>
+  </si>
+  <si>
+    <t>62556039000147</t>
+  </si>
+  <si>
+    <t>J J ATIVIDADE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>36700475000138</t>
+  </si>
+  <si>
+    <t>ALEVINOS RIO BRANCO LTDA</t>
+  </si>
+  <si>
+    <t>64654178000139</t>
+  </si>
+  <si>
+    <t>VOLTEC-RH PRESTACAO DE SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>64800937000124</t>
+  </si>
+  <si>
+    <t>4TK LTDA</t>
+  </si>
+  <si>
+    <t>63914780000103</t>
+  </si>
+  <si>
+    <t>PRIGADEIROS LTDA</t>
+  </si>
+  <si>
+    <t>47051883000122</t>
+  </si>
+  <si>
+    <t>ASSOCIACAO DOS SERVIDORES PUBLICOS MUNICIPAIS</t>
+  </si>
+  <si>
+    <t>48163603000130</t>
+  </si>
+  <si>
+    <t>HUGO &amp; GAMA CONSTRUCOES E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>59122213000139</t>
+  </si>
+  <si>
+    <t>MAICON DE MELO PEREIRA</t>
+  </si>
+  <si>
+    <t>24369885000169</t>
+  </si>
+  <si>
+    <t>FR SEGURANCA ELETRONICA LTDA</t>
+  </si>
+  <si>
+    <t>58145081000106</t>
+  </si>
+  <si>
+    <t>ASSOCIACAO INDEPENDENTE PIRITUBA</t>
+  </si>
+  <si>
+    <t>44422797000190</t>
+  </si>
+  <si>
+    <t>ASSOCIACAO LIGA DESPORTIVA REGIONAL DE RIBEIRAO PRETO</t>
+  </si>
+  <si>
+    <t>60698112000190</t>
+  </si>
+  <si>
+    <t>KSS FIRE &amp; SYSTEMS LTDA</t>
+  </si>
+  <si>
+    <t>51468159000176</t>
+  </si>
+  <si>
+    <t>G SILVA ENGENHARIA E CONSULTORIA LTDA</t>
+  </si>
+  <si>
+    <t>62428152000147</t>
+  </si>
+  <si>
+    <t>AF STEEL &amp; FERRAGENS LTDA</t>
+  </si>
+  <si>
+    <t>63533501000153</t>
+  </si>
+  <si>
+    <t>BUTECO DO TCHE LTDA</t>
+  </si>
+  <si>
+    <t>13718761000125</t>
+  </si>
+  <si>
+    <t>ARIEM EMPREENDIMENTOS IMOBILIARIOS LIMITADA</t>
+  </si>
+  <si>
+    <t>33722114000102</t>
+  </si>
+  <si>
+    <t>CORREIA SERVICOS E CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>61689526000115</t>
+  </si>
+  <si>
+    <t>NASCIMENTO &amp; CO. ALIMENTOS E BEBIDAS LTDA</t>
+  </si>
+  <si>
+    <t>42473677000197</t>
+  </si>
+  <si>
+    <t>DUBLASOFT INDUSTRIA E COMERCIO DE PALMILHAS LTDA</t>
+  </si>
+  <si>
+    <t>07455729000100</t>
+  </si>
+  <si>
+    <t>PERLOTTI ASSISTENCIAL LTDA</t>
+  </si>
+  <si>
+    <t>59697129000143</t>
+  </si>
+  <si>
+    <t>CASA CIRURGICA NOVA PIRAJUSSARA LTDA</t>
+  </si>
+  <si>
+    <t>62738071000143</t>
+  </si>
+  <si>
+    <t>DOCERIA E CONFEITARIA K LTDA</t>
+  </si>
+  <si>
+    <t>58886070000179</t>
+  </si>
+  <si>
+    <t>BS PRODUCOES DE VIDEOS LTDA</t>
+  </si>
+  <si>
+    <t>15095362000423</t>
+  </si>
+  <si>
+    <t>SHOW BRASIL MARQUES EMBALAGENS LTDA</t>
+  </si>
+  <si>
+    <t>57540096000106</t>
+  </si>
+  <si>
+    <t>57.540.096 LTDA</t>
+  </si>
+  <si>
+    <t>60759082000184</t>
+  </si>
+  <si>
+    <t>SKILL GLASS LTDA</t>
+  </si>
+  <si>
+    <t>65126540000161</t>
+  </si>
+  <si>
+    <t>MG VOLTS ELETROPOSTOS LTDA</t>
+  </si>
+  <si>
+    <t>28609495000170</t>
+  </si>
+  <si>
+    <t>GLOBER ASSISTENCIA MECANICA HIDRAULICA LTDA</t>
+  </si>
+  <si>
+    <t>08984259000126</t>
+  </si>
+  <si>
+    <t>WOLF ENERGIA LOCACAO E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>61699910000107</t>
+  </si>
+  <si>
+    <t>SEU PEDRO RESTAURANTE E PANIFICADORA LTDA</t>
+  </si>
+  <si>
+    <t>42138150000106</t>
+  </si>
+  <si>
+    <t>SPOOK CONFECCOES E ARTIGOS DO VESTUARIO LTDA</t>
+  </si>
+  <si>
+    <t>24922004000195</t>
+  </si>
+  <si>
+    <t>A F MANGUEIRAS HIDRAULICAS, PECAS AGRICOLAS E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>61322668000140</t>
+  </si>
+  <si>
+    <t>MDAL COMERCIO DE SORVETES LTDA</t>
+  </si>
+  <si>
+    <t>57367264000103</t>
+  </si>
+  <si>
+    <t>JP DRONE TECNOLOGIA E INOVACAO LTDA</t>
+  </si>
+  <si>
+    <t>52838776000189</t>
+  </si>
+  <si>
+    <t>DM SERVICOS E INSTALACAO DE AR CONDICIONADO LTDA</t>
+  </si>
+  <si>
+    <t>11339862000160</t>
+  </si>
+  <si>
+    <t>CENTRO EDUCACIONAL MAGALHAES LTDA</t>
+  </si>
+  <si>
+    <t>62385014000128</t>
+  </si>
+  <si>
+    <t>NOSSA OTICA VISAO OCULAR LTDA</t>
+  </si>
+  <si>
+    <t>47984322000186</t>
+  </si>
+  <si>
+    <t>WVR INSTALACAO E MANUTENCAO DE AR-CONDICIONADO SLU LTDA</t>
+  </si>
+  <si>
+    <t>61927120000123</t>
+  </si>
+  <si>
+    <t>DURVAL DE ALMEIDA PINTO FILHO LTDA</t>
+  </si>
+  <si>
+    <t>08844187000111</t>
+  </si>
+  <si>
+    <t>SHOP &amp; CLEAN PRODUTOS DE LIMPEZA LTDA</t>
+  </si>
+  <si>
+    <t>60928209000141</t>
+  </si>
+  <si>
+    <t>INSTALL ESQUADRIAS DE ALUMINIO E VIDROS LTDA</t>
+  </si>
+  <si>
+    <t>60541945000142</t>
+  </si>
+  <si>
+    <t>ESQUADRIGLASS VIDROS E ESQUADRIAS LTDA</t>
+  </si>
+  <si>
+    <t>56979411000125</t>
+  </si>
+  <si>
+    <t>RUFF CALHAS LTDA</t>
+  </si>
+  <si>
+    <t>61150910000145</t>
+  </si>
+  <si>
+    <t>PASTELARIA DO IGOR LTDA</t>
+  </si>
+  <si>
+    <t>36536249000163</t>
+  </si>
+  <si>
+    <t>MINHOCA MANUTENCOES HIDRAULICAS LTDA</t>
+  </si>
+  <si>
+    <t>62653080000131</t>
+  </si>
+  <si>
+    <t>RODRIGO RODRIGUES SILVA LTDA</t>
+  </si>
+  <si>
+    <t>65173263000148</t>
+  </si>
+  <si>
+    <t>CARLOS AMARO GONCALVES</t>
+  </si>
+  <si>
+    <t>52605658000120</t>
+  </si>
+  <si>
+    <t>MF COMERCIO DE METAIS E ALUMINIO LTDA</t>
+  </si>
+  <si>
+    <t>44401017000126</t>
+  </si>
+  <si>
+    <t>REF.GAS MANUTENCAO E INSTALACAO UNIPESSOAL LTDA</t>
+  </si>
+  <si>
+    <t>61031890000193</t>
+  </si>
+  <si>
+    <t>IMPERIO 21 COMERCIO VAREJISTA LTDA</t>
+  </si>
+  <si>
+    <t>60864603000163</t>
+  </si>
+  <si>
+    <t>KASSOUHA DISTRIBUIDORA COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>02134354000154</t>
+  </si>
+  <si>
+    <t>W. CORREALE VEICULOS LTDA</t>
+  </si>
+  <si>
+    <t>01783197000145</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA CELESTINO RODRIGUES LTDA</t>
+  </si>
+  <si>
+    <t>62642961000157</t>
+  </si>
+  <si>
+    <t>ESQUENTA ADEGA &amp; TABACARIA LTDA</t>
+  </si>
+  <si>
+    <t>60642635000114</t>
+  </si>
+  <si>
+    <t>GCB CONSTRUCOES LIMITADA</t>
+  </si>
+  <si>
+    <t>57630504000102</t>
+  </si>
+  <si>
+    <t>GARDENSE REALTY PARTNERS LTDA</t>
+  </si>
+  <si>
+    <t>38002381000110</t>
+  </si>
+  <si>
+    <t>OXEN SERVICES LTDA</t>
+  </si>
+  <si>
+    <t>60232554000146</t>
+  </si>
+  <si>
+    <t>RM SERVICOS DE CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>31533934000112</t>
+  </si>
+  <si>
+    <t>JOSE CARLOS BORGES</t>
+  </si>
+  <si>
+    <t>45583243000138</t>
+  </si>
+  <si>
+    <t>GABRIEL FERREIRA SANTANA DE PAULA SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
+    <t>46969071000106</t>
+  </si>
+  <si>
+    <t>MICHEL SILVEIRA HENRIQUES LTDA</t>
+  </si>
+  <si>
+    <t>58188992000102</t>
+  </si>
+  <si>
+    <t>R. L. ANDRADE LTDA</t>
+  </si>
+  <si>
+    <t>65480115000176</t>
+  </si>
+  <si>
+    <t>SUPREMA PISOS LTDA</t>
+  </si>
+  <si>
+    <t>56184289000109</t>
+  </si>
+  <si>
+    <t>E.S.G CONSTRUTORA LTDA</t>
+  </si>
+  <si>
+    <t>59663896000131</t>
+  </si>
+  <si>
+    <t>RESTAURANTE &amp; CHURRASCARIA SABOR D' CASA LTDA</t>
+  </si>
+  <si>
+    <t>11916506000161</t>
+  </si>
+  <si>
+    <t>A.L ROCHA SALAO DE BELEZA LTDA</t>
+  </si>
+  <si>
+    <t>40960935000134</t>
+  </si>
+  <si>
+    <t>VALMIR CALDEIRA GONCALVES LTDA</t>
+  </si>
+  <si>
+    <t>51666727000143</t>
+  </si>
+  <si>
+    <t>COSTA SETUBAL SERVICOS DE ESTETICA LTDA</t>
+  </si>
+  <si>
+    <t>62806274000120</t>
+  </si>
+  <si>
+    <t>R. AFONSO DO AMARAL LTDA</t>
+  </si>
+  <si>
+    <t>INDICAÇÃO</t>
+  </si>
+  <si>
+    <t>22059781000122</t>
+  </si>
+  <si>
+    <t>L S ACOS DESIGNER &amp; ESTRUTURAS LTDA</t>
+  </si>
+  <si>
+    <t>64783950000112</t>
+  </si>
+  <si>
+    <t>J B CAR MULTIMARCAS LTDA</t>
+  </si>
+  <si>
+    <t>65229805000157</t>
+  </si>
+  <si>
+    <t>BELLMO EXECUTIVO EM SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>60982344000175</t>
+  </si>
+  <si>
+    <t>JOANA D ARC FERNANDES RAMOS</t>
+  </si>
+  <si>
+    <t>61112398000142</t>
+  </si>
+  <si>
+    <t>JHONYCAR MANUTENCAO DE TETO SOLAR E ACESSORIOS LTDA</t>
+  </si>
+  <si>
+    <t>61943327000191</t>
+  </si>
+  <si>
+    <t>MERCADO OLIVEIRA LTDA</t>
+  </si>
+  <si>
+    <t>60496881000105</t>
+  </si>
+  <si>
+    <t>D F DIAS SILVA COMERCIO E SERVICO LTDA</t>
+  </si>
+  <si>
+    <t>61678906000154</t>
+  </si>
+  <si>
+    <t>PEREZQUISPE PARTICIPACOES LTDA</t>
+  </si>
+  <si>
+    <t>49674014000180</t>
+  </si>
+  <si>
+    <t>MOVIMPORT LTDA</t>
+  </si>
+  <si>
+    <t>36955439000115</t>
+  </si>
+  <si>
+    <t>ETM DISTRIBUICAO E LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t>64539617000162</t>
+  </si>
+  <si>
+    <t>ABN PROTEGE REGIONAL SANTANA LTDA</t>
+  </si>
+  <si>
+    <t>60726952000119</t>
+  </si>
+  <si>
+    <t>VISTA ALEGRE ATELIE LTDA</t>
+  </si>
+  <si>
+    <t>14785635000156</t>
+  </si>
+  <si>
+    <t>JIBRASIL SERVICOS COMERCIO E REPRESENTACOES LTDA</t>
+  </si>
+  <si>
+    <t>65106206000146</t>
+  </si>
+  <si>
+    <t>RN SERVICOS DE CARREGAMENTO E DESCARREGAMENTO LTDA</t>
+  </si>
+  <si>
+    <t>59339287000121</t>
+  </si>
+  <si>
+    <t>ZR MAV REPRESENTACOES LTDA</t>
+  </si>
+  <si>
+    <t>33708448000113</t>
+  </si>
+  <si>
+    <t>ASSOCIACAO DESPORTIVA ATHLETIC MERITI</t>
+  </si>
+  <si>
+    <t>64793822000150</t>
+  </si>
+  <si>
+    <t>MILAGREXX REPRESENTACOES E CONSULTORIAS LTDA</t>
+  </si>
+  <si>
+    <t>61431105000190</t>
+  </si>
+  <si>
+    <t>BRUNA MARDEGAN CONFECCOES LTDA</t>
+  </si>
+  <si>
+    <t>12749483000100</t>
+  </si>
+  <si>
+    <t>MARMORARIA RANGEL - COMERCIO E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>03998670000137</t>
+  </si>
+  <si>
+    <t>ASSOCIACAO ESCOLINHA FUNDAMENTOS DO FUTEBOL</t>
+  </si>
+  <si>
+    <t>07206882000195</t>
+  </si>
+  <si>
+    <t>BAR E LANCHONETE AGUA BRANCA LTDA</t>
+  </si>
+  <si>
+    <t>59697874000192</t>
+  </si>
+  <si>
+    <t>RODRIGO DOS SANTOS PEREIRA MARINHO TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>34022139000158</t>
+  </si>
+  <si>
+    <t>CERAMICA JR LTDA</t>
+  </si>
+  <si>
+    <t>20753626000186</t>
+  </si>
+  <si>
+    <t>ASSOCIACAO CULTURAL RECREATIVA DESPORTIVA E SOCIAL SAO TARCISIO</t>
+  </si>
+  <si>
+    <t>30174204000100</t>
+  </si>
+  <si>
+    <t>ASSOCIACAO PROJETOS O RETORNO DO REI AO BAENAO</t>
+  </si>
+  <si>
+    <t>58674107000103</t>
+  </si>
+  <si>
+    <t>SOUZA &amp; SILVA CONSTRUCOES UNIPESSOAL LTDA</t>
+  </si>
+  <si>
+    <t>00441333000156</t>
+  </si>
+  <si>
+    <t>S. F. SERVICOS INDUSTRIAIS LTDA</t>
+  </si>
+  <si>
+    <t>51178269000101</t>
+  </si>
+  <si>
+    <t>JC GESSO OBRAS DE ACABAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>65097174000160</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA DE MEDICAMENTOS PIQUIRI MED LTDA</t>
+  </si>
+  <si>
+    <t>61552322000138</t>
+  </si>
+  <si>
+    <t>AGATHA TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>20153124000114</t>
+  </si>
+  <si>
+    <t>SCHEREDER SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>50535378000168</t>
+  </si>
+  <si>
+    <t>SEZEFREDO3636 EMPREENDIMENTOS SPE LTDA</t>
+  </si>
+  <si>
+    <t>02106228000196</t>
+  </si>
+  <si>
+    <t>S B DE SOUZA CONSTRUTORA LTDA</t>
+  </si>
+  <si>
+    <t>65584305000133</t>
+  </si>
+  <si>
+    <t>SECURITY ADMINISTRADORA &amp; GESTAO CONDOMININIOS LTDA</t>
+  </si>
+  <si>
+    <t>53107547000157</t>
+  </si>
+  <si>
+    <t>STEELPOA LTDA</t>
+  </si>
+  <si>
+    <t>04320025000123</t>
+  </si>
+  <si>
+    <t>JFRAN CONSTRUCAO E PAVIMENTACAO LTDA</t>
+  </si>
+  <si>
+    <t>23851522000100</t>
+  </si>
+  <si>
+    <t>DICA EMPREENDIMENTOS IMOBILIARIOS LTDA</t>
+  </si>
+  <si>
+    <t>44734464000105</t>
+  </si>
+  <si>
+    <t>PRIGADEIROS CAFE LTDA</t>
+  </si>
+  <si>
+    <t>37864083000177</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA SILVA GONCALVES</t>
+  </si>
+  <si>
+    <t>30894864000165</t>
+  </si>
+  <si>
+    <t>RK MANUTENCAO E ACABAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>52578097000118</t>
+  </si>
+  <si>
+    <t>Daniel Kawamorita Neves Noia LTDA</t>
+  </si>
+  <si>
+    <t>55019465000186</t>
+  </si>
+  <si>
+    <t>WELLINGTON BARROS DE JESUS LTDA</t>
+  </si>
+  <si>
+    <t>45735320000128</t>
+  </si>
+  <si>
+    <t>UNIAO ANDREENSE FUTEBOL CLUBE</t>
+  </si>
+  <si>
+    <t>12826929000153</t>
+  </si>
+  <si>
+    <t>THIAGO DUTRA DA SILVA</t>
+  </si>
+  <si>
+    <t>62676576000120</t>
+  </si>
+  <si>
+    <t>RRL BEBIDAS E DIVERSAO LTDA</t>
+  </si>
+  <si>
+    <t>56319215000124</t>
+  </si>
+  <si>
+    <t>SILVA E SOUZA COMERCIO DE MATERIAIS PARA CONSTRUCAO LTDA</t>
+  </si>
+  <si>
+    <t>62880749000128</t>
+  </si>
+  <si>
+    <t>SPIDERFIT LTDA</t>
+  </si>
+  <si>
+    <t>23472856000165</t>
+  </si>
+  <si>
+    <t>HENRIQUE APARECIDO PAZ DA SILVA LTDA</t>
+  </si>
+  <si>
+    <t>47436564000135</t>
+  </si>
+  <si>
+    <t>BRILHA REPRESENTACAO, INSTALACAO E MANUTENCAO LTDA</t>
+  </si>
+  <si>
+    <t>64384044000145</t>
+  </si>
+  <si>
+    <t>ALPHA LC CONSULTORIA LTDA</t>
+  </si>
+  <si>
+    <t>35483755000179</t>
+  </si>
+  <si>
+    <t>EL SHADAY SORVETES LTDA</t>
+  </si>
+  <si>
+    <t>50479402000199</t>
+  </si>
+  <si>
+    <t>CLAYTON MARTINS CORRETORA DE SEGUROS LTDA</t>
+  </si>
+  <si>
+    <t>54663784000167</t>
+  </si>
+  <si>
+    <t>AGRO MARQUES RAIZES LTDA</t>
+  </si>
+  <si>
+    <t>55220635000196</t>
+  </si>
+  <si>
+    <t>INSTITUTO VIDA MELHOR</t>
+  </si>
+  <si>
+    <t>62798364000116</t>
+  </si>
+  <si>
+    <t>WL TERRAPLANAGEM LTDA</t>
+  </si>
+  <si>
+    <t>57772934000169</t>
+  </si>
+  <si>
+    <t>MXS CONSTRUCOES E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>31779480000164</t>
+  </si>
+  <si>
+    <t>FORTE CONTRUCOES E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>33614359000108</t>
+  </si>
+  <si>
+    <t>RICONE AR CONDICIONADO REFRIGERACAO E ELETRICA LTDA</t>
+  </si>
+  <si>
+    <t>64707855000130</t>
+  </si>
+  <si>
+    <t>WVI MARCENARIA LTDA</t>
+  </si>
+  <si>
+    <t>35256104000146</t>
+  </si>
+  <si>
+    <t>MERCADO MERCOSUL LTDA</t>
+  </si>
+  <si>
+    <t>62558478000199</t>
+  </si>
+  <si>
+    <t>DOMMA GESTAO E SINDICATURA LTDA</t>
+  </si>
+  <si>
+    <t>Procuracao da empresa SAMC BALANCAS E TECNOLOGIA LTDA, assinada via gov.br ou por meio de procuracao publica, em formato PDF. O documento deve conter, de forma expressa, os poderes para abrir e movimentar contas, alem de identificar corretamente o outorgante e o outorgado.</t>
+  </si>
+  <si>
+    <t>Procuracao da empresa DS FOOD &amp; BEVARAGE LTDA, assinada via gov.br ou por meio de procuracao publica, em formato PDF. O documento deve conter, de forma expressa, os poderes para abrir e movimentar contas, alem de identificar corretamente o outorgante e o outorgado.</t>
   </si>
 </sst>
 </file>
@@ -2820,7 +3894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:I369"/>
+  <dimension ref="A1:I547"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2880,10 +3954,10 @@
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" t="s">
-        <v>797</v>
+        <v>801</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -2909,7 +3983,7 @@
         <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>801</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2938,10 +4012,10 @@
         <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>798</v>
+        <v>801</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -2967,10 +4041,10 @@
         <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -2996,10 +4070,10 @@
         <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" t="s">
-        <v>36</v>
+        <v>801</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -3083,7 +4157,7 @@
         <v>7</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>801</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -3202,7 +4276,7 @@
         <v>30</v>
       </c>
       <c r="I13" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -3286,7 +4360,7 @@
         <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>24</v>
+        <v>801</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -3402,7 +4476,7 @@
         <v>10</v>
       </c>
       <c r="H20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -3663,7 +4737,7 @@
         <v>7</v>
       </c>
       <c r="H29" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -3840,7 +4914,7 @@
         <v>30</v>
       </c>
       <c r="I35" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -4040,7 +5114,7 @@
         <v>8</v>
       </c>
       <c r="H42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -4533,10 +5607,10 @@
         <v>7</v>
       </c>
       <c r="H59" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I59" t="s">
-        <v>35</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -6046,7 +7120,7 @@
         <v>8</v>
       </c>
       <c r="H112" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -6568,7 +7642,7 @@
         <v>7</v>
       </c>
       <c r="H130" t="s">
-        <v>30</v>
+        <v>801</v>
       </c>
       <c r="I130">
         <v>0</v>
@@ -6716,7 +7790,7 @@
         <v>30</v>
       </c>
       <c r="I135" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
@@ -6829,7 +7903,7 @@
         <v>10</v>
       </c>
       <c r="H139" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I139">
         <v>0</v>
@@ -7864,7 +8938,7 @@
         <v>7</v>
       </c>
       <c r="H175" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I175">
         <v>0</v>
@@ -7951,10 +9025,10 @@
         <v>7</v>
       </c>
       <c r="H178" t="s">
-        <v>22</v>
-      </c>
-      <c r="I178">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="I178" t="s">
+        <v>1160</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
@@ -11879,7 +12953,7 @@
         <v>7</v>
       </c>
       <c r="H315" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I315">
         <v>0</v>
@@ -12006,25 +13080,25 @@
         <v>46087</v>
       </c>
       <c r="B320" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C320" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D320" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E320" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F320" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="G320" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H320" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I320">
         <v>0</v>
@@ -12035,10 +13109,10 @@
         <v>46087</v>
       </c>
       <c r="B321" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C321" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D321" t="s">
         <v>151</v>
@@ -12047,7 +13121,7 @@
         <v>152</v>
       </c>
       <c r="F321" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G321" t="s">
         <v>8</v>
@@ -12064,19 +13138,19 @@
         <v>46087</v>
       </c>
       <c r="B322" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C322" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D322" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E322" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F322" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="G322" t="s">
         <v>8</v>
@@ -12093,28 +13167,28 @@
         <v>46087</v>
       </c>
       <c r="B323" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C323" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D323" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E323" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F323" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G323" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H323" t="s">
-        <v>19</v>
-      </c>
-      <c r="I323">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="I323" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
@@ -12122,28 +13196,28 @@
         <v>46087</v>
       </c>
       <c r="B324" t="s">
-        <v>706</v>
+        <v>69</v>
       </c>
       <c r="C324" t="s">
-        <v>707</v>
+        <v>70</v>
       </c>
       <c r="D324" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E324" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F324" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G324" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H324" t="s">
-        <v>30</v>
-      </c>
-      <c r="I324" t="s">
-        <v>36</v>
+        <v>19</v>
+      </c>
+      <c r="I324">
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
@@ -12151,19 +13225,19 @@
         <v>46087</v>
       </c>
       <c r="B325" t="s">
-        <v>69</v>
+        <v>708</v>
       </c>
       <c r="C325" t="s">
-        <v>70</v>
+        <v>709</v>
       </c>
       <c r="D325" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E325" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F325" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G325" t="s">
         <v>8</v>
@@ -12180,19 +13254,19 @@
         <v>46087</v>
       </c>
       <c r="B326" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C326" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D326" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E326" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F326" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G326" t="s">
         <v>8</v>
@@ -12209,19 +13283,19 @@
         <v>46087</v>
       </c>
       <c r="B327" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C327" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D327" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E327" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F327" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G327" t="s">
         <v>8</v>
@@ -12238,10 +13312,10 @@
         <v>46087</v>
       </c>
       <c r="B328" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C328" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D328" t="s">
         <v>147</v>
@@ -12250,13 +13324,13 @@
         <v>148</v>
       </c>
       <c r="F328" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="G328" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H328" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I328">
         <v>0</v>
@@ -12267,25 +13341,25 @@
         <v>46087</v>
       </c>
       <c r="B329" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C329" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D329" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E329" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F329" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="G329" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H329" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I329">
         <v>0</v>
@@ -12293,25 +13367,25 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B330" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C330" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D330" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E330" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F330" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G330" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H330" t="s">
         <v>19</v>
@@ -12325,19 +13399,19 @@
         <v>46090</v>
       </c>
       <c r="B331" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C331" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D331" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E331" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F331" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G331" t="s">
         <v>8</v>
@@ -12354,25 +13428,28 @@
         <v>46090</v>
       </c>
       <c r="B332" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C332" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D332" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E332" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F332" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G332" t="s">
         <v>8</v>
       </c>
       <c r="H332" t="s">
         <v>19</v>
+      </c>
+      <c r="I332">
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
@@ -12380,25 +13457,28 @@
         <v>46090</v>
       </c>
       <c r="B333" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C333" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D333" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E333" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F333" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G333" t="s">
         <v>8</v>
       </c>
       <c r="H333" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="I333">
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
@@ -12406,10 +13486,10 @@
         <v>46090</v>
       </c>
       <c r="B334" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C334" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D334" t="s">
         <v>151</v>
@@ -12418,13 +13498,16 @@
         <v>152</v>
       </c>
       <c r="F334" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G334" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H334" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="I334">
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
@@ -12432,10 +13515,10 @@
         <v>46090</v>
       </c>
       <c r="B335" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C335" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D335" t="s">
         <v>151</v>
@@ -12444,13 +13527,16 @@
         <v>152</v>
       </c>
       <c r="F335" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="G335" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="H335" t="s">
         <v>19</v>
+      </c>
+      <c r="I335">
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.25">
@@ -12458,114 +13544,126 @@
         <v>46090</v>
       </c>
       <c r="B336" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C336" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D336" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E336" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F336" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="G336" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H336" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>46090</v>
       </c>
       <c r="B337" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C337" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D337" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E337" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F337" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="G337" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H337" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>46090</v>
       </c>
       <c r="B338" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C338" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D338" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E338" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F338" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G338" t="s">
-        <v>734</v>
+        <v>7</v>
       </c>
       <c r="H338" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>46090</v>
       </c>
       <c r="B339" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C339" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="D339" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E339" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F339" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G339" t="s">
-        <v>734</v>
+        <v>10</v>
       </c>
       <c r="H339" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>46090</v>
       </c>
       <c r="B340" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C340" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="D340" t="s">
         <v>151</v>
@@ -12574,50 +13672,56 @@
         <v>152</v>
       </c>
       <c r="F340" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="G340" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H340" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>46090</v>
       </c>
       <c r="B341" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C341" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="D341" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E341" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F341" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="G341" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H341" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>46090</v>
       </c>
       <c r="B342" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C342" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D342" t="s">
         <v>147</v>
@@ -12626,111 +13730,123 @@
         <v>148</v>
       </c>
       <c r="F342" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G342" t="s">
         <v>10</v>
       </c>
       <c r="H342" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>46090</v>
       </c>
       <c r="B343" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C343" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="D343" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E343" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F343" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G343" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H343" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>46090</v>
       </c>
       <c r="B344" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C344" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D344" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E344" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F344" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G344" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H344" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>46090</v>
       </c>
       <c r="B345" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C345" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D345" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E345" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F345" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G345" t="s">
         <v>8</v>
       </c>
       <c r="H345" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>46090</v>
       </c>
       <c r="B346" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C346" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="D346" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E346" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F346" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G346" t="s">
         <v>8</v>
@@ -12738,42 +13854,48 @@
       <c r="H346" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>46090</v>
       </c>
       <c r="B347" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C347" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D347" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E347" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F347" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G347" t="s">
         <v>8</v>
       </c>
       <c r="H347" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="I347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>46090</v>
       </c>
       <c r="B348" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C348" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D348" t="s">
         <v>151</v>
@@ -12788,27 +13910,30 @@
         <v>8</v>
       </c>
       <c r="H348" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="I348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>46090</v>
       </c>
       <c r="B349" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C349" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D349" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E349" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F349" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G349" t="s">
         <v>8</v>
@@ -12816,16 +13941,19 @@
       <c r="H349" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>46090</v>
       </c>
       <c r="B350" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C350" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D350" t="s">
         <v>147</v>
@@ -12834,7 +13962,7 @@
         <v>148</v>
       </c>
       <c r="F350" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="G350" t="s">
         <v>8</v>
@@ -12842,42 +13970,48 @@
       <c r="H350" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I350" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <v>46090</v>
       </c>
       <c r="B351" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C351" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D351" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E351" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F351" t="s">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="G351" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H351" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>46090</v>
       </c>
       <c r="B352" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C352" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D352" t="s">
         <v>149</v>
@@ -12886,24 +14020,27 @@
         <v>150</v>
       </c>
       <c r="F352" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G352" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H352" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>46090</v>
       </c>
       <c r="B353" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C353" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D353" t="s">
         <v>149</v>
@@ -12918,44 +14055,50 @@
         <v>8</v>
       </c>
       <c r="H353" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>46090</v>
       </c>
       <c r="B354" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C354" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D354" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E354" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F354" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="G354" t="s">
         <v>8</v>
       </c>
       <c r="H354" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>46090</v>
       </c>
       <c r="B355" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C355" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D355" t="s">
         <v>151</v>
@@ -12964,24 +14107,27 @@
         <v>152</v>
       </c>
       <c r="F355" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G355" t="s">
         <v>8</v>
       </c>
       <c r="H355" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>46090</v>
       </c>
       <c r="B356" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C356" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D356" t="s">
         <v>151</v>
@@ -12990,76 +14136,85 @@
         <v>152</v>
       </c>
       <c r="F356" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G356" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H356" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <v>46090</v>
       </c>
       <c r="B357" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C357" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D357" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E357" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F357" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G357" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H357" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>46090</v>
       </c>
       <c r="B358" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C358" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D358" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E358" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F358" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G358" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H358" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <v>46090</v>
       </c>
       <c r="B359" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C359" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D359" t="s">
         <v>151</v>
@@ -13076,16 +14231,19 @@
       <c r="H359" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>46090</v>
       </c>
       <c r="B360" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C360" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D360" t="s">
         <v>151</v>
@@ -13094,24 +14252,27 @@
         <v>152</v>
       </c>
       <c r="F360" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G360" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H360" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
         <v>46090</v>
       </c>
       <c r="B361" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C361" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D361" t="s">
         <v>151</v>
@@ -13120,85 +14281,94 @@
         <v>152</v>
       </c>
       <c r="F361" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G361" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H361" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <v>46090</v>
       </c>
       <c r="B362" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C362" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="D362" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E362" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F362" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="G362" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H362" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="I362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <v>46090</v>
       </c>
       <c r="B363" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C363" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D363" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E363" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F363" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="G363" t="s">
         <v>8</v>
       </c>
       <c r="H363" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <v>46090</v>
       </c>
       <c r="B364" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C364" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D364" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E364" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F364" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G364" t="s">
         <v>8</v>
@@ -13206,68 +14376,77 @@
       <c r="H364" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>46090</v>
       </c>
       <c r="B365" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C365" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="D365" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E365" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F365" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G365" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H365" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
         <v>46090</v>
       </c>
       <c r="B366" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C366" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D366" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E366" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F366" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G366" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H366" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
         <v>46090</v>
       </c>
       <c r="B367" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C367" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D367" t="s">
         <v>147</v>
@@ -13276,24 +14455,27 @@
         <v>148</v>
       </c>
       <c r="F367" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G367" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H367" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="I367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <v>46090</v>
       </c>
       <c r="B368" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C368" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D368" t="s">
         <v>147</v>
@@ -13302,39 +14484,4931 @@
         <v>148</v>
       </c>
       <c r="F368" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G368" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H368" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B369" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="C369" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="D369" t="s">
+        <v>217</v>
+      </c>
+      <c r="F369" t="s">
+        <v>40</v>
+      </c>
+      <c r="G369" t="s">
+        <v>41</v>
+      </c>
+      <c r="H369" t="s">
+        <v>19</v>
+      </c>
+      <c r="I369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A370" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B370" t="s">
+        <v>804</v>
+      </c>
+      <c r="C370" t="s">
+        <v>805</v>
+      </c>
+      <c r="D370" t="s">
+        <v>151</v>
+      </c>
+      <c r="E370" t="s">
+        <v>152</v>
+      </c>
+      <c r="F370" t="s">
+        <v>17</v>
+      </c>
+      <c r="G370" t="s">
+        <v>8</v>
+      </c>
+      <c r="H370" t="s">
+        <v>19</v>
+      </c>
+      <c r="I370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B371" t="s">
+        <v>806</v>
+      </c>
+      <c r="C371" t="s">
+        <v>807</v>
+      </c>
+      <c r="D371" t="s">
+        <v>151</v>
+      </c>
+      <c r="E371" t="s">
+        <v>152</v>
+      </c>
+      <c r="F371" t="s">
+        <v>17</v>
+      </c>
+      <c r="G371" t="s">
+        <v>8</v>
+      </c>
+      <c r="H371" t="s">
+        <v>19</v>
+      </c>
+      <c r="I371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B372" t="s">
+        <v>808</v>
+      </c>
+      <c r="C372" t="s">
+        <v>809</v>
+      </c>
+      <c r="D372" t="s">
+        <v>151</v>
+      </c>
+      <c r="E372" t="s">
+        <v>152</v>
+      </c>
+      <c r="F372" t="s">
+        <v>17</v>
+      </c>
+      <c r="G372" t="s">
+        <v>8</v>
+      </c>
+      <c r="H372" t="s">
+        <v>19</v>
+      </c>
+      <c r="I372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B373" t="s">
+        <v>810</v>
+      </c>
+      <c r="C373" t="s">
+        <v>811</v>
+      </c>
+      <c r="D373" t="s">
+        <v>217</v>
+      </c>
+      <c r="F373" t="s">
+        <v>40</v>
+      </c>
+      <c r="G373" t="s">
+        <v>8</v>
+      </c>
+      <c r="H373" t="s">
+        <v>19</v>
+      </c>
+      <c r="I373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B374" t="s">
+        <v>812</v>
+      </c>
+      <c r="C374" t="s">
+        <v>813</v>
+      </c>
+      <c r="D374" t="s">
+        <v>217</v>
+      </c>
+      <c r="F374" t="s">
+        <v>40</v>
+      </c>
+      <c r="G374" t="s">
+        <v>41</v>
+      </c>
+      <c r="H374" t="s">
+        <v>19</v>
+      </c>
+      <c r="I374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B375" t="s">
+        <v>814</v>
+      </c>
+      <c r="C375" t="s">
+        <v>815</v>
+      </c>
+      <c r="D375" t="s">
+        <v>217</v>
+      </c>
+      <c r="F375" t="s">
+        <v>40</v>
+      </c>
+      <c r="G375" t="s">
+        <v>41</v>
+      </c>
+      <c r="H375" t="s">
+        <v>19</v>
+      </c>
+      <c r="I375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B376" t="s">
+        <v>816</v>
+      </c>
+      <c r="C376" t="s">
+        <v>817</v>
+      </c>
+      <c r="D376" t="s">
         <v>147</v>
       </c>
-      <c r="E369" t="s">
+      <c r="E376" t="s">
         <v>148</v>
       </c>
-      <c r="F369" t="s">
+      <c r="F376" t="s">
+        <v>49</v>
+      </c>
+      <c r="G376" t="s">
+        <v>10</v>
+      </c>
+      <c r="H376" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B377" t="s">
+        <v>818</v>
+      </c>
+      <c r="C377" t="s">
+        <v>819</v>
+      </c>
+      <c r="D377" t="s">
+        <v>149</v>
+      </c>
+      <c r="E377" t="s">
+        <v>150</v>
+      </c>
+      <c r="F377" t="s">
+        <v>14</v>
+      </c>
+      <c r="G377" t="s">
+        <v>13</v>
+      </c>
+      <c r="H377" t="s">
+        <v>19</v>
+      </c>
+      <c r="I377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B378" t="s">
+        <v>820</v>
+      </c>
+      <c r="C378" t="s">
+        <v>821</v>
+      </c>
+      <c r="D378" t="s">
+        <v>149</v>
+      </c>
+      <c r="E378" t="s">
+        <v>150</v>
+      </c>
+      <c r="F378" t="s">
+        <v>11</v>
+      </c>
+      <c r="G378" t="s">
+        <v>8</v>
+      </c>
+      <c r="H378" t="s">
+        <v>23</v>
+      </c>
+      <c r="I378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B379" t="s">
+        <v>822</v>
+      </c>
+      <c r="C379" t="s">
+        <v>823</v>
+      </c>
+      <c r="D379" t="s">
+        <v>151</v>
+      </c>
+      <c r="E379" t="s">
+        <v>152</v>
+      </c>
+      <c r="F379" t="s">
+        <v>17</v>
+      </c>
+      <c r="G379" t="s">
+        <v>8</v>
+      </c>
+      <c r="H379" t="s">
+        <v>19</v>
+      </c>
+      <c r="I379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B380" t="s">
+        <v>824</v>
+      </c>
+      <c r="C380" t="s">
+        <v>825</v>
+      </c>
+      <c r="D380" t="s">
+        <v>147</v>
+      </c>
+      <c r="E380" t="s">
+        <v>148</v>
+      </c>
+      <c r="F380" t="s">
         <v>73</v>
       </c>
-      <c r="G369" t="s">
-        <v>8</v>
-      </c>
-      <c r="H369" t="s">
+      <c r="G380" t="s">
+        <v>8</v>
+      </c>
+      <c r="H380" t="s">
         <v>22</v>
+      </c>
+      <c r="I380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A381" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B381" t="s">
+        <v>826</v>
+      </c>
+      <c r="C381" t="s">
+        <v>827</v>
+      </c>
+      <c r="D381" t="s">
+        <v>147</v>
+      </c>
+      <c r="E381" t="s">
+        <v>148</v>
+      </c>
+      <c r="F381" t="s">
+        <v>16</v>
+      </c>
+      <c r="G381" t="s">
+        <v>13</v>
+      </c>
+      <c r="H381" t="s">
+        <v>19</v>
+      </c>
+      <c r="I381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A382" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B382" t="s">
+        <v>828</v>
+      </c>
+      <c r="C382" t="s">
+        <v>829</v>
+      </c>
+      <c r="D382" t="s">
+        <v>151</v>
+      </c>
+      <c r="E382" t="s">
+        <v>152</v>
+      </c>
+      <c r="F382" t="s">
+        <v>17</v>
+      </c>
+      <c r="G382" t="s">
+        <v>8</v>
+      </c>
+      <c r="H382" t="s">
+        <v>23</v>
+      </c>
+      <c r="I382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A383" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B383" t="s">
+        <v>830</v>
+      </c>
+      <c r="C383" t="s">
+        <v>831</v>
+      </c>
+      <c r="D383" t="s">
+        <v>149</v>
+      </c>
+      <c r="E383" t="s">
+        <v>150</v>
+      </c>
+      <c r="F383" t="s">
+        <v>9</v>
+      </c>
+      <c r="G383" t="s">
+        <v>7</v>
+      </c>
+      <c r="H383" t="s">
+        <v>19</v>
+      </c>
+      <c r="I383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A384" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B384" t="s">
+        <v>832</v>
+      </c>
+      <c r="C384" t="s">
+        <v>833</v>
+      </c>
+      <c r="D384" t="s">
+        <v>149</v>
+      </c>
+      <c r="E384" t="s">
+        <v>150</v>
+      </c>
+      <c r="F384" t="s">
+        <v>14</v>
+      </c>
+      <c r="G384" t="s">
+        <v>13</v>
+      </c>
+      <c r="H384" t="s">
+        <v>19</v>
+      </c>
+      <c r="I384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A385" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B385" t="s">
+        <v>834</v>
+      </c>
+      <c r="C385" t="s">
+        <v>835</v>
+      </c>
+      <c r="D385" t="s">
+        <v>149</v>
+      </c>
+      <c r="E385" t="s">
+        <v>150</v>
+      </c>
+      <c r="F385" t="s">
+        <v>29</v>
+      </c>
+      <c r="G385" t="s">
+        <v>7</v>
+      </c>
+      <c r="H385" t="s">
+        <v>19</v>
+      </c>
+      <c r="I385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A386" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B386" t="s">
+        <v>836</v>
+      </c>
+      <c r="C386" t="s">
+        <v>837</v>
+      </c>
+      <c r="D386" t="s">
+        <v>151</v>
+      </c>
+      <c r="E386" t="s">
+        <v>152</v>
+      </c>
+      <c r="F386" t="s">
+        <v>6</v>
+      </c>
+      <c r="G386" t="s">
+        <v>13</v>
+      </c>
+      <c r="H386" t="s">
+        <v>23</v>
+      </c>
+      <c r="I386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A387" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B387" t="s">
+        <v>838</v>
+      </c>
+      <c r="C387" t="s">
+        <v>839</v>
+      </c>
+      <c r="D387" t="s">
+        <v>147</v>
+      </c>
+      <c r="E387" t="s">
+        <v>148</v>
+      </c>
+      <c r="F387" t="s">
+        <v>16</v>
+      </c>
+      <c r="G387" t="s">
+        <v>8</v>
+      </c>
+      <c r="H387" t="s">
+        <v>23</v>
+      </c>
+      <c r="I387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A388" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B388" t="s">
+        <v>840</v>
+      </c>
+      <c r="C388" t="s">
+        <v>841</v>
+      </c>
+      <c r="D388" t="s">
+        <v>147</v>
+      </c>
+      <c r="E388" t="s">
+        <v>148</v>
+      </c>
+      <c r="F388" t="s">
+        <v>25</v>
+      </c>
+      <c r="G388" t="s">
+        <v>7</v>
+      </c>
+      <c r="H388" t="s">
+        <v>30</v>
+      </c>
+      <c r="I388" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A389" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B389" t="s">
+        <v>842</v>
+      </c>
+      <c r="C389" t="s">
+        <v>843</v>
+      </c>
+      <c r="D389" t="s">
+        <v>151</v>
+      </c>
+      <c r="E389" t="s">
+        <v>152</v>
+      </c>
+      <c r="F389" t="s">
+        <v>27</v>
+      </c>
+      <c r="G389" t="s">
+        <v>7</v>
+      </c>
+      <c r="H389" t="s">
+        <v>19</v>
+      </c>
+      <c r="I389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A390" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B390" t="s">
+        <v>844</v>
+      </c>
+      <c r="C390" t="s">
+        <v>845</v>
+      </c>
+      <c r="D390" t="s">
+        <v>149</v>
+      </c>
+      <c r="E390" t="s">
+        <v>150</v>
+      </c>
+      <c r="F390" t="s">
+        <v>11</v>
+      </c>
+      <c r="G390" t="s">
+        <v>8</v>
+      </c>
+      <c r="H390" t="s">
+        <v>19</v>
+      </c>
+      <c r="I390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A391" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B391" t="s">
+        <v>846</v>
+      </c>
+      <c r="C391" t="s">
+        <v>847</v>
+      </c>
+      <c r="D391" t="s">
+        <v>151</v>
+      </c>
+      <c r="E391" t="s">
+        <v>152</v>
+      </c>
+      <c r="F391" t="s">
+        <v>27</v>
+      </c>
+      <c r="G391" t="s">
+        <v>8</v>
+      </c>
+      <c r="H391" t="s">
+        <v>19</v>
+      </c>
+      <c r="I391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A392" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B392" t="s">
+        <v>848</v>
+      </c>
+      <c r="C392" t="s">
+        <v>849</v>
+      </c>
+      <c r="D392" t="s">
+        <v>151</v>
+      </c>
+      <c r="E392" t="s">
+        <v>152</v>
+      </c>
+      <c r="F392" t="s">
+        <v>17</v>
+      </c>
+      <c r="G392" t="s">
+        <v>8</v>
+      </c>
+      <c r="H392" t="s">
+        <v>23</v>
+      </c>
+      <c r="I392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A393" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B393" t="s">
+        <v>850</v>
+      </c>
+      <c r="C393" t="s">
+        <v>851</v>
+      </c>
+      <c r="D393" t="s">
+        <v>147</v>
+      </c>
+      <c r="E393" t="s">
+        <v>148</v>
+      </c>
+      <c r="F393" t="s">
+        <v>16</v>
+      </c>
+      <c r="G393" t="s">
+        <v>8</v>
+      </c>
+      <c r="H393" t="s">
+        <v>19</v>
+      </c>
+      <c r="I393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A394" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B394" t="s">
+        <v>852</v>
+      </c>
+      <c r="C394" t="s">
+        <v>853</v>
+      </c>
+      <c r="D394" t="s">
+        <v>147</v>
+      </c>
+      <c r="E394" t="s">
+        <v>148</v>
+      </c>
+      <c r="F394" t="s">
+        <v>73</v>
+      </c>
+      <c r="G394" t="s">
+        <v>8</v>
+      </c>
+      <c r="H394" t="s">
+        <v>22</v>
+      </c>
+      <c r="I394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A395" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B395" t="s">
+        <v>854</v>
+      </c>
+      <c r="C395" t="s">
+        <v>855</v>
+      </c>
+      <c r="D395" t="s">
+        <v>151</v>
+      </c>
+      <c r="E395" t="s">
+        <v>152</v>
+      </c>
+      <c r="F395" t="s">
+        <v>17</v>
+      </c>
+      <c r="G395" t="s">
+        <v>8</v>
+      </c>
+      <c r="H395" t="s">
+        <v>19</v>
+      </c>
+      <c r="I395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A396" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B396" t="s">
+        <v>856</v>
+      </c>
+      <c r="C396" t="s">
+        <v>857</v>
+      </c>
+      <c r="D396" t="s">
+        <v>147</v>
+      </c>
+      <c r="E396" t="s">
+        <v>148</v>
+      </c>
+      <c r="F396" t="s">
+        <v>16</v>
+      </c>
+      <c r="G396" t="s">
+        <v>8</v>
+      </c>
+      <c r="H396" t="s">
+        <v>19</v>
+      </c>
+      <c r="I396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A397" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B397" t="s">
+        <v>858</v>
+      </c>
+      <c r="C397" t="s">
+        <v>859</v>
+      </c>
+      <c r="D397" t="s">
+        <v>149</v>
+      </c>
+      <c r="E397" t="s">
+        <v>150</v>
+      </c>
+      <c r="F397" t="s">
+        <v>14</v>
+      </c>
+      <c r="G397" t="s">
+        <v>8</v>
+      </c>
+      <c r="H397" t="s">
+        <v>23</v>
+      </c>
+      <c r="I397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A398" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B398" t="s">
+        <v>860</v>
+      </c>
+      <c r="C398" t="s">
+        <v>861</v>
+      </c>
+      <c r="D398" t="s">
+        <v>151</v>
+      </c>
+      <c r="E398" t="s">
+        <v>152</v>
+      </c>
+      <c r="F398" t="s">
+        <v>17</v>
+      </c>
+      <c r="G398" t="s">
+        <v>8</v>
+      </c>
+      <c r="H398" t="s">
+        <v>19</v>
+      </c>
+      <c r="I398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A399" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B399" t="s">
+        <v>862</v>
+      </c>
+      <c r="C399" t="s">
+        <v>863</v>
+      </c>
+      <c r="D399" t="s">
+        <v>149</v>
+      </c>
+      <c r="E399" t="s">
+        <v>150</v>
+      </c>
+      <c r="F399" t="s">
+        <v>14</v>
+      </c>
+      <c r="G399" t="s">
+        <v>8</v>
+      </c>
+      <c r="H399" t="s">
+        <v>19</v>
+      </c>
+      <c r="I399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A400" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B400" t="s">
+        <v>864</v>
+      </c>
+      <c r="C400" t="s">
+        <v>865</v>
+      </c>
+      <c r="D400" t="s">
+        <v>151</v>
+      </c>
+      <c r="E400" t="s">
+        <v>152</v>
+      </c>
+      <c r="F400" t="s">
+        <v>42</v>
+      </c>
+      <c r="G400" t="s">
+        <v>10</v>
+      </c>
+      <c r="H400" t="s">
+        <v>19</v>
+      </c>
+      <c r="I400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A401" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B401" t="s">
+        <v>866</v>
+      </c>
+      <c r="C401" t="s">
+        <v>867</v>
+      </c>
+      <c r="D401" t="s">
+        <v>149</v>
+      </c>
+      <c r="E401" t="s">
+        <v>150</v>
+      </c>
+      <c r="F401" t="s">
+        <v>29</v>
+      </c>
+      <c r="G401" t="s">
+        <v>8</v>
+      </c>
+      <c r="H401" t="s">
+        <v>23</v>
+      </c>
+      <c r="I401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A402" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B402" t="s">
+        <v>868</v>
+      </c>
+      <c r="C402" t="s">
+        <v>869</v>
+      </c>
+      <c r="D402" t="s">
+        <v>147</v>
+      </c>
+      <c r="E402" t="s">
+        <v>148</v>
+      </c>
+      <c r="F402" t="s">
+        <v>25</v>
+      </c>
+      <c r="G402" t="s">
+        <v>8</v>
+      </c>
+      <c r="H402" t="s">
+        <v>19</v>
+      </c>
+      <c r="I402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A403" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B403" t="s">
+        <v>870</v>
+      </c>
+      <c r="C403" t="s">
+        <v>871</v>
+      </c>
+      <c r="D403" t="s">
+        <v>149</v>
+      </c>
+      <c r="E403" t="s">
+        <v>150</v>
+      </c>
+      <c r="F403" t="s">
+        <v>11</v>
+      </c>
+      <c r="G403" t="s">
+        <v>8</v>
+      </c>
+      <c r="H403" t="s">
+        <v>19</v>
+      </c>
+      <c r="I403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A404" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B404" t="s">
+        <v>872</v>
+      </c>
+      <c r="C404" t="s">
+        <v>873</v>
+      </c>
+      <c r="D404" t="s">
+        <v>147</v>
+      </c>
+      <c r="E404" t="s">
+        <v>148</v>
+      </c>
+      <c r="F404" t="s">
+        <v>16</v>
+      </c>
+      <c r="G404" t="s">
+        <v>8</v>
+      </c>
+      <c r="H404" t="s">
+        <v>19</v>
+      </c>
+      <c r="I404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A405" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B405" t="s">
+        <v>874</v>
+      </c>
+      <c r="C405" t="s">
+        <v>875</v>
+      </c>
+      <c r="D405" t="s">
+        <v>151</v>
+      </c>
+      <c r="E405" t="s">
+        <v>152</v>
+      </c>
+      <c r="F405" t="s">
+        <v>42</v>
+      </c>
+      <c r="G405" t="s">
+        <v>8</v>
+      </c>
+      <c r="H405" t="s">
+        <v>23</v>
+      </c>
+      <c r="I405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A406" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B406" t="s">
+        <v>876</v>
+      </c>
+      <c r="C406" t="s">
+        <v>877</v>
+      </c>
+      <c r="D406" t="s">
+        <v>147</v>
+      </c>
+      <c r="E406" t="s">
+        <v>148</v>
+      </c>
+      <c r="F406" t="s">
+        <v>73</v>
+      </c>
+      <c r="G406" t="s">
+        <v>8</v>
+      </c>
+      <c r="H406" t="s">
+        <v>19</v>
+      </c>
+      <c r="I406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A407" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B407" t="s">
+        <v>878</v>
+      </c>
+      <c r="C407" t="s">
+        <v>879</v>
+      </c>
+      <c r="D407" t="s">
+        <v>149</v>
+      </c>
+      <c r="E407" t="s">
+        <v>150</v>
+      </c>
+      <c r="F407" t="s">
+        <v>14</v>
+      </c>
+      <c r="G407" t="s">
+        <v>8</v>
+      </c>
+      <c r="H407" t="s">
+        <v>19</v>
+      </c>
+      <c r="I407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A408" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B408" t="s">
+        <v>880</v>
+      </c>
+      <c r="C408" t="s">
+        <v>881</v>
+      </c>
+      <c r="D408" t="s">
+        <v>147</v>
+      </c>
+      <c r="E408" t="s">
+        <v>148</v>
+      </c>
+      <c r="F408" t="s">
+        <v>16</v>
+      </c>
+      <c r="G408" t="s">
+        <v>8</v>
+      </c>
+      <c r="H408" t="s">
+        <v>19</v>
+      </c>
+      <c r="I408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A409" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B409" t="s">
+        <v>882</v>
+      </c>
+      <c r="C409" t="s">
+        <v>883</v>
+      </c>
+      <c r="D409" t="s">
+        <v>149</v>
+      </c>
+      <c r="E409" t="s">
+        <v>150</v>
+      </c>
+      <c r="F409" t="s">
+        <v>12</v>
+      </c>
+      <c r="G409" t="s">
+        <v>8</v>
+      </c>
+      <c r="H409" t="s">
+        <v>19</v>
+      </c>
+      <c r="I409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A410" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B410" t="s">
+        <v>884</v>
+      </c>
+      <c r="C410" t="s">
+        <v>885</v>
+      </c>
+      <c r="D410" t="s">
+        <v>149</v>
+      </c>
+      <c r="E410" t="s">
+        <v>150</v>
+      </c>
+      <c r="F410" t="s">
+        <v>12</v>
+      </c>
+      <c r="G410" t="s">
+        <v>8</v>
+      </c>
+      <c r="H410" t="s">
+        <v>30</v>
+      </c>
+      <c r="I410" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A411" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B411" t="s">
+        <v>886</v>
+      </c>
+      <c r="C411" t="s">
+        <v>887</v>
+      </c>
+      <c r="D411" t="s">
+        <v>147</v>
+      </c>
+      <c r="E411" t="s">
+        <v>148</v>
+      </c>
+      <c r="F411" t="s">
+        <v>73</v>
+      </c>
+      <c r="G411" t="s">
+        <v>8</v>
+      </c>
+      <c r="H411" t="s">
+        <v>19</v>
+      </c>
+      <c r="I411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A412" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B412" t="s">
+        <v>888</v>
+      </c>
+      <c r="C412" t="s">
+        <v>889</v>
+      </c>
+      <c r="D412" t="s">
+        <v>149</v>
+      </c>
+      <c r="E412" t="s">
+        <v>150</v>
+      </c>
+      <c r="F412" t="s">
+        <v>14</v>
+      </c>
+      <c r="G412" t="s">
+        <v>8</v>
+      </c>
+      <c r="H412" t="s">
+        <v>19</v>
+      </c>
+      <c r="I412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A413" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B413" t="s">
+        <v>890</v>
+      </c>
+      <c r="C413" t="s">
+        <v>891</v>
+      </c>
+      <c r="D413" t="s">
+        <v>149</v>
+      </c>
+      <c r="E413" t="s">
+        <v>150</v>
+      </c>
+      <c r="F413" t="s">
+        <v>50</v>
+      </c>
+      <c r="G413" t="s">
+        <v>8</v>
+      </c>
+      <c r="H413" t="s">
+        <v>19</v>
+      </c>
+      <c r="I413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A414" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B414" t="s">
+        <v>892</v>
+      </c>
+      <c r="C414" t="s">
+        <v>893</v>
+      </c>
+      <c r="D414" t="s">
+        <v>151</v>
+      </c>
+      <c r="E414" t="s">
+        <v>152</v>
+      </c>
+      <c r="F414" t="s">
+        <v>6</v>
+      </c>
+      <c r="G414" t="s">
+        <v>32</v>
+      </c>
+      <c r="H414" t="s">
+        <v>19</v>
+      </c>
+      <c r="I414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A415" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B415" t="s">
+        <v>894</v>
+      </c>
+      <c r="C415" t="s">
+        <v>895</v>
+      </c>
+      <c r="D415" t="s">
+        <v>149</v>
+      </c>
+      <c r="E415" t="s">
+        <v>150</v>
+      </c>
+      <c r="F415" t="s">
+        <v>12</v>
+      </c>
+      <c r="G415" t="s">
+        <v>8</v>
+      </c>
+      <c r="H415" t="s">
+        <v>19</v>
+      </c>
+      <c r="I415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A416" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B416" t="s">
+        <v>896</v>
+      </c>
+      <c r="C416" t="s">
+        <v>897</v>
+      </c>
+      <c r="D416" t="s">
+        <v>151</v>
+      </c>
+      <c r="E416" t="s">
+        <v>152</v>
+      </c>
+      <c r="F416" t="s">
+        <v>27</v>
+      </c>
+      <c r="G416" t="s">
+        <v>8</v>
+      </c>
+      <c r="H416" t="s">
+        <v>19</v>
+      </c>
+      <c r="I416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A417" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B417" t="s">
+        <v>898</v>
+      </c>
+      <c r="C417" t="s">
+        <v>899</v>
+      </c>
+      <c r="D417" t="s">
+        <v>149</v>
+      </c>
+      <c r="E417" t="s">
+        <v>150</v>
+      </c>
+      <c r="F417" t="s">
+        <v>11</v>
+      </c>
+      <c r="G417" t="s">
+        <v>8</v>
+      </c>
+      <c r="H417" t="s">
+        <v>19</v>
+      </c>
+      <c r="I417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A418" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B418" t="s">
+        <v>900</v>
+      </c>
+      <c r="C418" t="s">
+        <v>901</v>
+      </c>
+      <c r="D418" t="s">
+        <v>151</v>
+      </c>
+      <c r="E418" t="s">
+        <v>152</v>
+      </c>
+      <c r="F418" t="s">
+        <v>6</v>
+      </c>
+      <c r="G418" t="s">
+        <v>32</v>
+      </c>
+      <c r="H418" t="s">
+        <v>22</v>
+      </c>
+      <c r="I418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A419" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B419" t="s">
+        <v>902</v>
+      </c>
+      <c r="C419" t="s">
+        <v>903</v>
+      </c>
+      <c r="D419" t="s">
+        <v>151</v>
+      </c>
+      <c r="E419" t="s">
+        <v>152</v>
+      </c>
+      <c r="F419" t="s">
+        <v>17</v>
+      </c>
+      <c r="G419" t="s">
+        <v>8</v>
+      </c>
+      <c r="H419" t="s">
+        <v>19</v>
+      </c>
+      <c r="I419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A420" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B420" t="s">
+        <v>904</v>
+      </c>
+      <c r="C420" t="s">
+        <v>905</v>
+      </c>
+      <c r="D420" t="s">
+        <v>147</v>
+      </c>
+      <c r="E420" t="s">
+        <v>148</v>
+      </c>
+      <c r="F420" t="s">
+        <v>31</v>
+      </c>
+      <c r="G420" t="s">
+        <v>8</v>
+      </c>
+      <c r="H420" t="s">
+        <v>22</v>
+      </c>
+      <c r="I420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A421" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B421" t="s">
+        <v>906</v>
+      </c>
+      <c r="C421" t="s">
+        <v>907</v>
+      </c>
+      <c r="D421" t="s">
+        <v>147</v>
+      </c>
+      <c r="E421" t="s">
+        <v>148</v>
+      </c>
+      <c r="F421" t="s">
+        <v>31</v>
+      </c>
+      <c r="G421" t="s">
+        <v>8</v>
+      </c>
+      <c r="H421" t="s">
+        <v>19</v>
+      </c>
+      <c r="I421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A422" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B422" t="s">
+        <v>908</v>
+      </c>
+      <c r="C422" t="s">
+        <v>909</v>
+      </c>
+      <c r="D422" t="s">
+        <v>147</v>
+      </c>
+      <c r="E422" t="s">
+        <v>148</v>
+      </c>
+      <c r="F422" t="s">
+        <v>21</v>
+      </c>
+      <c r="G422" t="s">
+        <v>8</v>
+      </c>
+      <c r="H422" t="s">
+        <v>801</v>
+      </c>
+      <c r="I422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A423" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B423" t="s">
+        <v>910</v>
+      </c>
+      <c r="C423" t="s">
+        <v>911</v>
+      </c>
+      <c r="D423" t="s">
+        <v>147</v>
+      </c>
+      <c r="E423" t="s">
+        <v>148</v>
+      </c>
+      <c r="F423" t="s">
+        <v>49</v>
+      </c>
+      <c r="G423" t="s">
+        <v>8</v>
+      </c>
+      <c r="H423" t="s">
+        <v>22</v>
+      </c>
+      <c r="I423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A424" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B424" t="s">
+        <v>912</v>
+      </c>
+      <c r="C424" t="s">
+        <v>913</v>
+      </c>
+      <c r="D424" t="s">
+        <v>149</v>
+      </c>
+      <c r="E424" t="s">
+        <v>150</v>
+      </c>
+      <c r="F424" t="s">
+        <v>9</v>
+      </c>
+      <c r="G424" t="s">
+        <v>7</v>
+      </c>
+      <c r="H424" t="s">
+        <v>19</v>
+      </c>
+      <c r="I424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A425" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B425" t="s">
+        <v>914</v>
+      </c>
+      <c r="C425" t="s">
+        <v>915</v>
+      </c>
+      <c r="D425" t="s">
+        <v>151</v>
+      </c>
+      <c r="E425" t="s">
+        <v>152</v>
+      </c>
+      <c r="F425" t="s">
+        <v>17</v>
+      </c>
+      <c r="G425" t="s">
+        <v>8</v>
+      </c>
+      <c r="H425" t="s">
+        <v>19</v>
+      </c>
+      <c r="I425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A426" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B426" t="s">
+        <v>916</v>
+      </c>
+      <c r="C426" t="s">
+        <v>917</v>
+      </c>
+      <c r="D426" t="s">
+        <v>147</v>
+      </c>
+      <c r="E426" t="s">
+        <v>148</v>
+      </c>
+      <c r="F426" t="s">
+        <v>16</v>
+      </c>
+      <c r="G426" t="s">
+        <v>8</v>
+      </c>
+      <c r="H426" t="s">
+        <v>22</v>
+      </c>
+      <c r="I426" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A427" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B427" t="s">
+        <v>918</v>
+      </c>
+      <c r="C427" t="s">
+        <v>919</v>
+      </c>
+      <c r="D427" t="s">
+        <v>151</v>
+      </c>
+      <c r="E427" t="s">
+        <v>152</v>
+      </c>
+      <c r="F427" t="s">
+        <v>17</v>
+      </c>
+      <c r="G427" t="s">
+        <v>8</v>
+      </c>
+      <c r="H427" t="s">
+        <v>30</v>
+      </c>
+      <c r="I427" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A428" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B428" t="s">
+        <v>920</v>
+      </c>
+      <c r="C428" t="s">
+        <v>921</v>
+      </c>
+      <c r="D428" t="s">
+        <v>147</v>
+      </c>
+      <c r="E428" t="s">
+        <v>148</v>
+      </c>
+      <c r="F428" t="s">
+        <v>31</v>
+      </c>
+      <c r="G428" t="s">
+        <v>8</v>
+      </c>
+      <c r="H428" t="s">
+        <v>19</v>
+      </c>
+      <c r="I428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A429" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B429" t="s">
+        <v>922</v>
+      </c>
+      <c r="C429" t="s">
+        <v>923</v>
+      </c>
+      <c r="D429" t="s">
+        <v>151</v>
+      </c>
+      <c r="E429" t="s">
+        <v>152</v>
+      </c>
+      <c r="F429" t="s">
+        <v>42</v>
+      </c>
+      <c r="G429" t="s">
+        <v>8</v>
+      </c>
+      <c r="H429" t="s">
+        <v>19</v>
+      </c>
+      <c r="I429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A430" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B430" t="s">
+        <v>924</v>
+      </c>
+      <c r="C430" t="s">
+        <v>925</v>
+      </c>
+      <c r="D430" t="s">
+        <v>151</v>
+      </c>
+      <c r="E430" t="s">
+        <v>152</v>
+      </c>
+      <c r="F430" t="s">
+        <v>33</v>
+      </c>
+      <c r="G430" t="s">
+        <v>8</v>
+      </c>
+      <c r="H430" t="s">
+        <v>19</v>
+      </c>
+      <c r="I430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A431" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B431" t="s">
+        <v>926</v>
+      </c>
+      <c r="C431" t="s">
+        <v>927</v>
+      </c>
+      <c r="D431" t="s">
+        <v>149</v>
+      </c>
+      <c r="E431" t="s">
+        <v>150</v>
+      </c>
+      <c r="F431" t="s">
+        <v>14</v>
+      </c>
+      <c r="G431" t="s">
+        <v>8</v>
+      </c>
+      <c r="H431" t="s">
+        <v>23</v>
+      </c>
+      <c r="I431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A432" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B432" t="s">
+        <v>928</v>
+      </c>
+      <c r="C432" t="s">
+        <v>929</v>
+      </c>
+      <c r="D432" t="s">
+        <v>151</v>
+      </c>
+      <c r="E432" t="s">
+        <v>152</v>
+      </c>
+      <c r="F432" t="s">
+        <v>27</v>
+      </c>
+      <c r="G432" t="s">
+        <v>8</v>
+      </c>
+      <c r="H432" t="s">
+        <v>19</v>
+      </c>
+      <c r="I432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A433" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B433" t="s">
+        <v>930</v>
+      </c>
+      <c r="C433" t="s">
+        <v>931</v>
+      </c>
+      <c r="D433" t="s">
+        <v>147</v>
+      </c>
+      <c r="E433" t="s">
+        <v>148</v>
+      </c>
+      <c r="F433" t="s">
+        <v>49</v>
+      </c>
+      <c r="G433" t="s">
+        <v>8</v>
+      </c>
+      <c r="H433" t="s">
+        <v>19</v>
+      </c>
+      <c r="I433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A434" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B434" t="s">
+        <v>932</v>
+      </c>
+      <c r="C434" t="s">
+        <v>933</v>
+      </c>
+      <c r="D434" t="s">
+        <v>151</v>
+      </c>
+      <c r="E434" t="s">
+        <v>152</v>
+      </c>
+      <c r="F434" t="s">
+        <v>6</v>
+      </c>
+      <c r="G434" t="s">
+        <v>8</v>
+      </c>
+      <c r="H434" t="s">
+        <v>19</v>
+      </c>
+      <c r="I434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A435" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B435" t="s">
+        <v>934</v>
+      </c>
+      <c r="C435" t="s">
+        <v>935</v>
+      </c>
+      <c r="D435" t="s">
+        <v>151</v>
+      </c>
+      <c r="E435" t="s">
+        <v>152</v>
+      </c>
+      <c r="F435" t="s">
+        <v>17</v>
+      </c>
+      <c r="G435" t="s">
+        <v>8</v>
+      </c>
+      <c r="H435" t="s">
+        <v>19</v>
+      </c>
+      <c r="I435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A436" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B436" t="s">
+        <v>936</v>
+      </c>
+      <c r="C436" t="s">
+        <v>937</v>
+      </c>
+      <c r="D436" t="s">
+        <v>147</v>
+      </c>
+      <c r="E436" t="s">
+        <v>148</v>
+      </c>
+      <c r="F436" t="s">
+        <v>16</v>
+      </c>
+      <c r="G436" t="s">
+        <v>8</v>
+      </c>
+      <c r="H436" t="s">
+        <v>19</v>
+      </c>
+      <c r="I436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A437" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B437" t="s">
+        <v>938</v>
+      </c>
+      <c r="C437" t="s">
+        <v>939</v>
+      </c>
+      <c r="D437" t="s">
+        <v>151</v>
+      </c>
+      <c r="E437" t="s">
+        <v>152</v>
+      </c>
+      <c r="F437" t="s">
+        <v>42</v>
+      </c>
+      <c r="G437" t="s">
+        <v>8</v>
+      </c>
+      <c r="H437" t="s">
+        <v>23</v>
+      </c>
+      <c r="I437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A438" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B438" t="s">
+        <v>940</v>
+      </c>
+      <c r="C438" t="s">
+        <v>941</v>
+      </c>
+      <c r="D438" t="s">
+        <v>149</v>
+      </c>
+      <c r="E438" t="s">
+        <v>150</v>
+      </c>
+      <c r="F438" t="s">
+        <v>66</v>
+      </c>
+      <c r="G438" t="s">
+        <v>32</v>
+      </c>
+      <c r="H438" t="s">
+        <v>22</v>
+      </c>
+      <c r="I438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A439" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B439" t="s">
+        <v>942</v>
+      </c>
+      <c r="C439" t="s">
+        <v>943</v>
+      </c>
+      <c r="D439" t="s">
+        <v>147</v>
+      </c>
+      <c r="E439" t="s">
+        <v>148</v>
+      </c>
+      <c r="F439" t="s">
+        <v>49</v>
+      </c>
+      <c r="G439" t="s">
+        <v>8</v>
+      </c>
+      <c r="H439" t="s">
+        <v>23</v>
+      </c>
+      <c r="I439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A440" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B440" t="s">
+        <v>944</v>
+      </c>
+      <c r="C440" t="s">
+        <v>945</v>
+      </c>
+      <c r="D440" t="s">
+        <v>151</v>
+      </c>
+      <c r="E440" t="s">
+        <v>152</v>
+      </c>
+      <c r="F440" t="s">
+        <v>27</v>
+      </c>
+      <c r="G440" t="s">
+        <v>8</v>
+      </c>
+      <c r="H440" t="s">
+        <v>22</v>
+      </c>
+      <c r="I440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A441" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B441" t="s">
+        <v>946</v>
+      </c>
+      <c r="C441" t="s">
+        <v>947</v>
+      </c>
+      <c r="D441" t="s">
+        <v>147</v>
+      </c>
+      <c r="E441" t="s">
+        <v>148</v>
+      </c>
+      <c r="F441" t="s">
+        <v>21</v>
+      </c>
+      <c r="G441" t="s">
+        <v>8</v>
+      </c>
+      <c r="H441" t="s">
+        <v>19</v>
+      </c>
+      <c r="I441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A442" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B442" t="s">
+        <v>948</v>
+      </c>
+      <c r="C442" t="s">
+        <v>949</v>
+      </c>
+      <c r="D442" t="s">
+        <v>149</v>
+      </c>
+      <c r="E442" t="s">
+        <v>150</v>
+      </c>
+      <c r="F442" t="s">
+        <v>11</v>
+      </c>
+      <c r="G442" t="s">
+        <v>8</v>
+      </c>
+      <c r="H442" t="s">
+        <v>19</v>
+      </c>
+      <c r="I442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A443" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B443" t="s">
+        <v>950</v>
+      </c>
+      <c r="C443" t="s">
+        <v>951</v>
+      </c>
+      <c r="D443" t="s">
+        <v>149</v>
+      </c>
+      <c r="E443" t="s">
+        <v>150</v>
+      </c>
+      <c r="F443" t="s">
+        <v>29</v>
+      </c>
+      <c r="G443" t="s">
+        <v>7</v>
+      </c>
+      <c r="H443" t="s">
+        <v>19</v>
+      </c>
+      <c r="I443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A444" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B444" t="s">
+        <v>952</v>
+      </c>
+      <c r="C444" t="s">
+        <v>953</v>
+      </c>
+      <c r="D444" t="s">
+        <v>147</v>
+      </c>
+      <c r="E444" t="s">
+        <v>148</v>
+      </c>
+      <c r="F444" t="s">
+        <v>73</v>
+      </c>
+      <c r="G444" t="s">
+        <v>8</v>
+      </c>
+      <c r="H444" t="s">
+        <v>19</v>
+      </c>
+      <c r="I444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A445" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B445" t="s">
+        <v>954</v>
+      </c>
+      <c r="C445" t="s">
+        <v>955</v>
+      </c>
+      <c r="D445" t="s">
+        <v>151</v>
+      </c>
+      <c r="E445" t="s">
+        <v>152</v>
+      </c>
+      <c r="F445" t="s">
+        <v>33</v>
+      </c>
+      <c r="G445" t="s">
+        <v>8</v>
+      </c>
+      <c r="H445" t="s">
+        <v>19</v>
+      </c>
+      <c r="I445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A446" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B446" t="s">
+        <v>956</v>
+      </c>
+      <c r="C446" t="s">
+        <v>957</v>
+      </c>
+      <c r="D446" t="s">
+        <v>147</v>
+      </c>
+      <c r="E446" t="s">
+        <v>148</v>
+      </c>
+      <c r="F446" t="s">
+        <v>31</v>
+      </c>
+      <c r="G446" t="s">
+        <v>8</v>
+      </c>
+      <c r="H446" t="s">
+        <v>19</v>
+      </c>
+      <c r="I446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A447" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B447" t="s">
+        <v>958</v>
+      </c>
+      <c r="C447" t="s">
+        <v>959</v>
+      </c>
+      <c r="D447" t="s">
+        <v>151</v>
+      </c>
+      <c r="E447" t="s">
+        <v>152</v>
+      </c>
+      <c r="F447" t="s">
+        <v>17</v>
+      </c>
+      <c r="G447" t="s">
+        <v>8</v>
+      </c>
+      <c r="H447" t="s">
+        <v>19</v>
+      </c>
+      <c r="I447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A448" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B448" t="s">
+        <v>960</v>
+      </c>
+      <c r="C448" t="s">
+        <v>961</v>
+      </c>
+      <c r="D448" t="s">
+        <v>149</v>
+      </c>
+      <c r="E448" t="s">
+        <v>150</v>
+      </c>
+      <c r="F448" t="s">
+        <v>66</v>
+      </c>
+      <c r="G448" t="s">
+        <v>8</v>
+      </c>
+      <c r="H448" t="s">
+        <v>19</v>
+      </c>
+      <c r="I448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A449" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B449" t="s">
+        <v>962</v>
+      </c>
+      <c r="C449" t="s">
+        <v>963</v>
+      </c>
+      <c r="D449" t="s">
+        <v>149</v>
+      </c>
+      <c r="E449" t="s">
+        <v>150</v>
+      </c>
+      <c r="F449" t="s">
+        <v>14</v>
+      </c>
+      <c r="G449" t="s">
+        <v>8</v>
+      </c>
+      <c r="H449" t="s">
+        <v>22</v>
+      </c>
+      <c r="I449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A450" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B450" t="s">
+        <v>964</v>
+      </c>
+      <c r="C450" t="s">
+        <v>965</v>
+      </c>
+      <c r="D450" t="s">
+        <v>147</v>
+      </c>
+      <c r="E450" t="s">
+        <v>148</v>
+      </c>
+      <c r="F450" t="s">
+        <v>73</v>
+      </c>
+      <c r="G450" t="s">
+        <v>8</v>
+      </c>
+      <c r="H450" t="s">
+        <v>23</v>
+      </c>
+      <c r="I450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A451" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B451" t="s">
+        <v>966</v>
+      </c>
+      <c r="C451" t="s">
+        <v>967</v>
+      </c>
+      <c r="D451" t="s">
+        <v>151</v>
+      </c>
+      <c r="E451" t="s">
+        <v>152</v>
+      </c>
+      <c r="F451" t="s">
+        <v>33</v>
+      </c>
+      <c r="G451" t="s">
+        <v>8</v>
+      </c>
+      <c r="H451" t="s">
+        <v>19</v>
+      </c>
+      <c r="I451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A452" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B452" t="s">
+        <v>968</v>
+      </c>
+      <c r="C452" t="s">
+        <v>969</v>
+      </c>
+      <c r="D452" t="s">
+        <v>147</v>
+      </c>
+      <c r="E452" t="s">
+        <v>148</v>
+      </c>
+      <c r="F452" t="s">
+        <v>16</v>
+      </c>
+      <c r="G452" t="s">
+        <v>8</v>
+      </c>
+      <c r="H452" t="s">
+        <v>19</v>
+      </c>
+      <c r="I452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A453" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B453" t="s">
+        <v>970</v>
+      </c>
+      <c r="C453" t="s">
+        <v>971</v>
+      </c>
+      <c r="D453" t="s">
+        <v>149</v>
+      </c>
+      <c r="E453" t="s">
+        <v>150</v>
+      </c>
+      <c r="F453" t="s">
+        <v>12</v>
+      </c>
+      <c r="G453" t="s">
+        <v>8</v>
+      </c>
+      <c r="H453" t="s">
+        <v>19</v>
+      </c>
+      <c r="I453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A454" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B454" t="s">
+        <v>972</v>
+      </c>
+      <c r="C454" t="s">
+        <v>973</v>
+      </c>
+      <c r="D454" t="s">
+        <v>147</v>
+      </c>
+      <c r="E454" t="s">
+        <v>148</v>
+      </c>
+      <c r="F454" t="s">
+        <v>49</v>
+      </c>
+      <c r="G454" t="s">
+        <v>8</v>
+      </c>
+      <c r="H454" t="s">
+        <v>22</v>
+      </c>
+      <c r="I454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A455" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B455" t="s">
+        <v>974</v>
+      </c>
+      <c r="C455" t="s">
+        <v>975</v>
+      </c>
+      <c r="D455" t="s">
+        <v>149</v>
+      </c>
+      <c r="E455" t="s">
+        <v>150</v>
+      </c>
+      <c r="F455" t="s">
+        <v>11</v>
+      </c>
+      <c r="G455" t="s">
+        <v>8</v>
+      </c>
+      <c r="H455" t="s">
+        <v>19</v>
+      </c>
+      <c r="I455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A456" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B456" t="s">
+        <v>976</v>
+      </c>
+      <c r="C456" t="s">
+        <v>977</v>
+      </c>
+      <c r="D456" t="s">
+        <v>151</v>
+      </c>
+      <c r="E456" t="s">
+        <v>152</v>
+      </c>
+      <c r="F456" t="s">
+        <v>6</v>
+      </c>
+      <c r="G456" t="s">
+        <v>8</v>
+      </c>
+      <c r="H456" t="s">
+        <v>19</v>
+      </c>
+      <c r="I456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A457" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B457" t="s">
+        <v>978</v>
+      </c>
+      <c r="C457" t="s">
+        <v>979</v>
+      </c>
+      <c r="D457" t="s">
+        <v>147</v>
+      </c>
+      <c r="E457" t="s">
+        <v>148</v>
+      </c>
+      <c r="F457" t="s">
+        <v>73</v>
+      </c>
+      <c r="G457" t="s">
+        <v>8</v>
+      </c>
+      <c r="H457" t="s">
+        <v>23</v>
+      </c>
+      <c r="I457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A458" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B458" t="s">
+        <v>980</v>
+      </c>
+      <c r="C458" t="s">
+        <v>981</v>
+      </c>
+      <c r="D458" t="s">
+        <v>151</v>
+      </c>
+      <c r="E458" t="s">
+        <v>152</v>
+      </c>
+      <c r="F458" t="s">
+        <v>17</v>
+      </c>
+      <c r="G458" t="s">
+        <v>8</v>
+      </c>
+      <c r="H458" t="s">
+        <v>19</v>
+      </c>
+      <c r="I458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A459" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B459" t="s">
+        <v>982</v>
+      </c>
+      <c r="C459" t="s">
+        <v>983</v>
+      </c>
+      <c r="D459" t="s">
+        <v>149</v>
+      </c>
+      <c r="E459" t="s">
+        <v>150</v>
+      </c>
+      <c r="F459" t="s">
+        <v>12</v>
+      </c>
+      <c r="G459" t="s">
+        <v>8</v>
+      </c>
+      <c r="H459" t="s">
+        <v>19</v>
+      </c>
+      <c r="I459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A460" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B460" t="s">
+        <v>984</v>
+      </c>
+      <c r="C460" t="s">
+        <v>985</v>
+      </c>
+      <c r="D460" t="s">
+        <v>149</v>
+      </c>
+      <c r="E460" t="s">
+        <v>150</v>
+      </c>
+      <c r="F460" t="s">
+        <v>14</v>
+      </c>
+      <c r="G460" t="s">
+        <v>8</v>
+      </c>
+      <c r="H460" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A461" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B461" t="s">
+        <v>986</v>
+      </c>
+      <c r="C461" t="s">
+        <v>987</v>
+      </c>
+      <c r="D461" t="s">
+        <v>147</v>
+      </c>
+      <c r="E461" t="s">
+        <v>148</v>
+      </c>
+      <c r="F461" t="s">
+        <v>31</v>
+      </c>
+      <c r="G461" t="s">
+        <v>734</v>
+      </c>
+      <c r="H461" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A462" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B462" t="s">
+        <v>988</v>
+      </c>
+      <c r="C462" t="s">
+        <v>989</v>
+      </c>
+      <c r="D462" t="s">
+        <v>149</v>
+      </c>
+      <c r="E462" t="s">
+        <v>150</v>
+      </c>
+      <c r="F462" t="s">
+        <v>12</v>
+      </c>
+      <c r="G462" t="s">
+        <v>8</v>
+      </c>
+      <c r="H462" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A463" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B463" t="s">
+        <v>990</v>
+      </c>
+      <c r="C463" t="s">
+        <v>991</v>
+      </c>
+      <c r="D463" t="s">
+        <v>147</v>
+      </c>
+      <c r="E463" t="s">
+        <v>148</v>
+      </c>
+      <c r="F463" t="s">
+        <v>31</v>
+      </c>
+      <c r="G463" t="s">
+        <v>120</v>
+      </c>
+      <c r="H463" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A464" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B464" t="s">
+        <v>992</v>
+      </c>
+      <c r="C464" t="s">
+        <v>993</v>
+      </c>
+      <c r="D464" t="s">
+        <v>149</v>
+      </c>
+      <c r="E464" t="s">
+        <v>150</v>
+      </c>
+      <c r="F464" t="s">
+        <v>14</v>
+      </c>
+      <c r="G464" t="s">
+        <v>8</v>
+      </c>
+      <c r="H464" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A465" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B465" t="s">
+        <v>994</v>
+      </c>
+      <c r="C465" t="s">
+        <v>995</v>
+      </c>
+      <c r="D465" t="s">
+        <v>149</v>
+      </c>
+      <c r="E465" t="s">
+        <v>150</v>
+      </c>
+      <c r="F465" t="s">
+        <v>14</v>
+      </c>
+      <c r="G465" t="s">
+        <v>8</v>
+      </c>
+      <c r="H465" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A466" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B466" t="s">
+        <v>996</v>
+      </c>
+      <c r="C466" t="s">
+        <v>997</v>
+      </c>
+      <c r="D466" t="s">
+        <v>147</v>
+      </c>
+      <c r="E466" t="s">
+        <v>148</v>
+      </c>
+      <c r="F466" t="s">
+        <v>16</v>
+      </c>
+      <c r="G466" t="s">
+        <v>8</v>
+      </c>
+      <c r="H466" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A467" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B467" t="s">
+        <v>998</v>
+      </c>
+      <c r="C467" t="s">
+        <v>999</v>
+      </c>
+      <c r="D467" t="s">
+        <v>147</v>
+      </c>
+      <c r="E467" t="s">
+        <v>148</v>
+      </c>
+      <c r="F467" t="s">
+        <v>16</v>
+      </c>
+      <c r="G467" t="s">
+        <v>8</v>
+      </c>
+      <c r="H467" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A468" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C468" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D468" t="s">
+        <v>149</v>
+      </c>
+      <c r="E468" t="s">
+        <v>150</v>
+      </c>
+      <c r="F468" t="s">
+        <v>14</v>
+      </c>
+      <c r="G468" t="s">
+        <v>8</v>
+      </c>
+      <c r="H468" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A469" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B469" t="s">
+        <v>698</v>
+      </c>
+      <c r="C469" t="s">
+        <v>699</v>
+      </c>
+      <c r="D469" t="s">
+        <v>147</v>
+      </c>
+      <c r="E469" t="s">
+        <v>148</v>
+      </c>
+      <c r="F469" t="s">
+        <v>49</v>
+      </c>
+      <c r="G469" t="s">
+        <v>10</v>
+      </c>
+      <c r="H469" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A470" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C470" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D470" t="s">
+        <v>151</v>
+      </c>
+      <c r="E470" t="s">
+        <v>152</v>
+      </c>
+      <c r="F470" t="s">
+        <v>17</v>
+      </c>
+      <c r="G470" t="s">
+        <v>8</v>
+      </c>
+      <c r="H470" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A471" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C471" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D471" t="s">
+        <v>147</v>
+      </c>
+      <c r="E471" t="s">
+        <v>148</v>
+      </c>
+      <c r="F471" t="s">
+        <v>73</v>
+      </c>
+      <c r="G471" t="s">
+        <v>8</v>
+      </c>
+      <c r="H471" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A472" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C472" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D472" t="s">
+        <v>147</v>
+      </c>
+      <c r="E472" t="s">
+        <v>148</v>
+      </c>
+      <c r="F472" t="s">
+        <v>21</v>
+      </c>
+      <c r="G472" t="s">
+        <v>8</v>
+      </c>
+      <c r="H472" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A473" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C473" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D473" t="s">
+        <v>149</v>
+      </c>
+      <c r="E473" t="s">
+        <v>150</v>
+      </c>
+      <c r="F473" t="s">
+        <v>9</v>
+      </c>
+      <c r="G473" t="s">
+        <v>7</v>
+      </c>
+      <c r="H473" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A474" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C474" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D474" t="s">
+        <v>149</v>
+      </c>
+      <c r="E474" t="s">
+        <v>150</v>
+      </c>
+      <c r="F474" t="s">
+        <v>14</v>
+      </c>
+      <c r="G474" t="s">
+        <v>8</v>
+      </c>
+      <c r="H474" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A475" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C475" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D475" t="s">
+        <v>149</v>
+      </c>
+      <c r="E475" t="s">
+        <v>150</v>
+      </c>
+      <c r="F475" t="s">
+        <v>14</v>
+      </c>
+      <c r="G475" t="s">
+        <v>8</v>
+      </c>
+      <c r="H475" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A476" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C476" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D476" t="s">
+        <v>151</v>
+      </c>
+      <c r="E476" t="s">
+        <v>152</v>
+      </c>
+      <c r="F476" t="s">
+        <v>27</v>
+      </c>
+      <c r="G476" t="s">
+        <v>7</v>
+      </c>
+      <c r="H476" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A477" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C477" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D477" t="s">
+        <v>151</v>
+      </c>
+      <c r="E477" t="s">
+        <v>152</v>
+      </c>
+      <c r="F477" t="s">
+        <v>42</v>
+      </c>
+      <c r="G477" t="s">
+        <v>13</v>
+      </c>
+      <c r="H477" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A478" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C478" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D478" t="s">
+        <v>151</v>
+      </c>
+      <c r="E478" t="s">
+        <v>152</v>
+      </c>
+      <c r="F478" t="s">
+        <v>6</v>
+      </c>
+      <c r="G478" t="s">
+        <v>8</v>
+      </c>
+      <c r="H478" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A479" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C479" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D479" t="s">
+        <v>147</v>
+      </c>
+      <c r="E479" t="s">
+        <v>148</v>
+      </c>
+      <c r="F479" t="s">
+        <v>31</v>
+      </c>
+      <c r="G479" t="s">
+        <v>8</v>
+      </c>
+      <c r="H479" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A480" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C480" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D480" t="s">
+        <v>149</v>
+      </c>
+      <c r="E480" t="s">
+        <v>150</v>
+      </c>
+      <c r="F480" t="s">
+        <v>66</v>
+      </c>
+      <c r="G480" t="s">
+        <v>10</v>
+      </c>
+      <c r="H480" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A481" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C481" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D481" t="s">
+        <v>149</v>
+      </c>
+      <c r="E481" t="s">
+        <v>150</v>
+      </c>
+      <c r="F481" t="s">
+        <v>29</v>
+      </c>
+      <c r="G481" t="s">
+        <v>8</v>
+      </c>
+      <c r="H481" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A482" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C482" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D482" t="s">
+        <v>149</v>
+      </c>
+      <c r="E482" t="s">
+        <v>150</v>
+      </c>
+      <c r="F482" t="s">
+        <v>14</v>
+      </c>
+      <c r="G482" t="s">
+        <v>8</v>
+      </c>
+      <c r="H482" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A483" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C483" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D483" t="s">
+        <v>151</v>
+      </c>
+      <c r="E483" t="s">
+        <v>152</v>
+      </c>
+      <c r="F483" t="s">
+        <v>42</v>
+      </c>
+      <c r="G483" t="s">
+        <v>13</v>
+      </c>
+      <c r="H483" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A484" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C484" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D484" t="s">
+        <v>147</v>
+      </c>
+      <c r="E484" t="s">
+        <v>148</v>
+      </c>
+      <c r="F484" t="s">
+        <v>16</v>
+      </c>
+      <c r="G484" t="s">
+        <v>8</v>
+      </c>
+      <c r="H484" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A485" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C485" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D485" t="s">
+        <v>147</v>
+      </c>
+      <c r="E485" t="s">
+        <v>148</v>
+      </c>
+      <c r="F485" t="s">
+        <v>25</v>
+      </c>
+      <c r="G485" t="s">
+        <v>13</v>
+      </c>
+      <c r="H485" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A486" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B486" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C486" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D486" t="s">
+        <v>149</v>
+      </c>
+      <c r="E486" t="s">
+        <v>150</v>
+      </c>
+      <c r="F486" t="s">
+        <v>11</v>
+      </c>
+      <c r="G486" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H486" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A487" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B487" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C487" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D487" t="s">
+        <v>147</v>
+      </c>
+      <c r="E487" t="s">
+        <v>148</v>
+      </c>
+      <c r="F487" t="s">
+        <v>25</v>
+      </c>
+      <c r="G487" t="s">
+        <v>8</v>
+      </c>
+      <c r="H487" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A488" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C488" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D488" t="s">
+        <v>147</v>
+      </c>
+      <c r="E488" t="s">
+        <v>148</v>
+      </c>
+      <c r="F488" t="s">
+        <v>16</v>
+      </c>
+      <c r="G488" t="s">
+        <v>8</v>
+      </c>
+      <c r="H488" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A489" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C489" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D489" t="s">
+        <v>149</v>
+      </c>
+      <c r="E489" t="s">
+        <v>150</v>
+      </c>
+      <c r="F489" t="s">
+        <v>12</v>
+      </c>
+      <c r="G489" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H489" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A490" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C490" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D490" t="s">
+        <v>149</v>
+      </c>
+      <c r="E490" t="s">
+        <v>150</v>
+      </c>
+      <c r="F490" t="s">
+        <v>11</v>
+      </c>
+      <c r="G490" t="s">
+        <v>8</v>
+      </c>
+      <c r="H490" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A491" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C491" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D491" t="s">
+        <v>151</v>
+      </c>
+      <c r="E491" t="s">
+        <v>152</v>
+      </c>
+      <c r="F491" t="s">
+        <v>6</v>
+      </c>
+      <c r="G491" t="s">
+        <v>8</v>
+      </c>
+      <c r="H491" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A492" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C492" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D492" t="s">
+        <v>149</v>
+      </c>
+      <c r="E492" t="s">
+        <v>150</v>
+      </c>
+      <c r="F492" t="s">
+        <v>66</v>
+      </c>
+      <c r="G492" t="s">
+        <v>8</v>
+      </c>
+      <c r="H492" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A493" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B493" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C493" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D493" t="s">
+        <v>147</v>
+      </c>
+      <c r="E493" t="s">
+        <v>148</v>
+      </c>
+      <c r="F493" t="s">
+        <v>49</v>
+      </c>
+      <c r="G493" t="s">
+        <v>8</v>
+      </c>
+      <c r="H493" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A494" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C494" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D494" t="s">
+        <v>149</v>
+      </c>
+      <c r="E494" t="s">
+        <v>150</v>
+      </c>
+      <c r="F494" t="s">
+        <v>11</v>
+      </c>
+      <c r="G494" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H494" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A495" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C495" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D495" t="s">
+        <v>149</v>
+      </c>
+      <c r="E495" t="s">
+        <v>150</v>
+      </c>
+      <c r="F495" t="s">
+        <v>9</v>
+      </c>
+      <c r="G495" t="s">
+        <v>7</v>
+      </c>
+      <c r="H495" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A496" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C496" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D496" t="s">
+        <v>149</v>
+      </c>
+      <c r="E496" t="s">
+        <v>150</v>
+      </c>
+      <c r="F496" t="s">
+        <v>12</v>
+      </c>
+      <c r="G496" t="s">
+        <v>8</v>
+      </c>
+      <c r="H496" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A497" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C497" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D497" t="s">
+        <v>151</v>
+      </c>
+      <c r="E497" t="s">
+        <v>152</v>
+      </c>
+      <c r="F497" t="s">
+        <v>6</v>
+      </c>
+      <c r="G497" t="s">
+        <v>13</v>
+      </c>
+      <c r="H497" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A498" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C498" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D498" t="s">
+        <v>149</v>
+      </c>
+      <c r="E498" t="s">
+        <v>150</v>
+      </c>
+      <c r="F498" t="s">
+        <v>12</v>
+      </c>
+      <c r="G498" t="s">
+        <v>8</v>
+      </c>
+      <c r="H498" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A499" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C499" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D499" t="s">
+        <v>149</v>
+      </c>
+      <c r="E499" t="s">
+        <v>150</v>
+      </c>
+      <c r="F499" t="s">
+        <v>9</v>
+      </c>
+      <c r="G499" t="s">
+        <v>8</v>
+      </c>
+      <c r="H499" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A500" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D500" t="s">
+        <v>149</v>
+      </c>
+      <c r="E500" t="s">
+        <v>150</v>
+      </c>
+      <c r="F500" t="s">
+        <v>11</v>
+      </c>
+      <c r="G500" t="s">
+        <v>8</v>
+      </c>
+      <c r="H500" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A501" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C501" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D501" t="s">
+        <v>147</v>
+      </c>
+      <c r="E501" t="s">
+        <v>148</v>
+      </c>
+      <c r="F501" t="s">
+        <v>21</v>
+      </c>
+      <c r="G501" t="s">
+        <v>8</v>
+      </c>
+      <c r="H501" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A502" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C502" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D502" t="s">
+        <v>149</v>
+      </c>
+      <c r="E502" t="s">
+        <v>150</v>
+      </c>
+      <c r="F502" t="s">
+        <v>50</v>
+      </c>
+      <c r="G502" t="s">
+        <v>8</v>
+      </c>
+      <c r="H502" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A503" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C503" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D503" t="s">
+        <v>149</v>
+      </c>
+      <c r="E503" t="s">
+        <v>150</v>
+      </c>
+      <c r="F503" t="s">
+        <v>14</v>
+      </c>
+      <c r="G503" t="s">
+        <v>8</v>
+      </c>
+      <c r="H503" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A504" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C504" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D504" t="s">
+        <v>147</v>
+      </c>
+      <c r="E504" t="s">
+        <v>148</v>
+      </c>
+      <c r="F504" t="s">
+        <v>21</v>
+      </c>
+      <c r="G504" t="s">
+        <v>8</v>
+      </c>
+      <c r="H504" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A505" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C505" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D505" t="s">
+        <v>147</v>
+      </c>
+      <c r="E505" t="s">
+        <v>148</v>
+      </c>
+      <c r="F505" t="s">
+        <v>73</v>
+      </c>
+      <c r="G505" t="s">
+        <v>8</v>
+      </c>
+      <c r="H505" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A506" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C506" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D506" t="s">
+        <v>149</v>
+      </c>
+      <c r="E506" t="s">
+        <v>150</v>
+      </c>
+      <c r="F506" t="s">
+        <v>14</v>
+      </c>
+      <c r="G506" t="s">
+        <v>8</v>
+      </c>
+      <c r="H506" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A507" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C507" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D507" t="s">
+        <v>147</v>
+      </c>
+      <c r="E507" t="s">
+        <v>148</v>
+      </c>
+      <c r="F507" t="s">
+        <v>21</v>
+      </c>
+      <c r="G507" t="s">
+        <v>8</v>
+      </c>
+      <c r="H507" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A508" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C508" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D508" t="s">
+        <v>147</v>
+      </c>
+      <c r="E508" t="s">
+        <v>148</v>
+      </c>
+      <c r="F508" t="s">
+        <v>31</v>
+      </c>
+      <c r="G508" t="s">
+        <v>8</v>
+      </c>
+      <c r="H508" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A509" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D509" t="s">
+        <v>147</v>
+      </c>
+      <c r="E509" t="s">
+        <v>148</v>
+      </c>
+      <c r="F509" t="s">
+        <v>16</v>
+      </c>
+      <c r="G509" t="s">
+        <v>8</v>
+      </c>
+      <c r="H509" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A510" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D510" t="s">
+        <v>147</v>
+      </c>
+      <c r="E510" t="s">
+        <v>148</v>
+      </c>
+      <c r="F510" t="s">
+        <v>73</v>
+      </c>
+      <c r="G510" t="s">
+        <v>8</v>
+      </c>
+      <c r="H510" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A511" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D511" t="s">
+        <v>151</v>
+      </c>
+      <c r="E511" t="s">
+        <v>152</v>
+      </c>
+      <c r="F511" t="s">
+        <v>33</v>
+      </c>
+      <c r="G511" t="s">
+        <v>8</v>
+      </c>
+      <c r="H511" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A512" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C512" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D512" t="s">
+        <v>149</v>
+      </c>
+      <c r="E512" t="s">
+        <v>150</v>
+      </c>
+      <c r="F512" t="s">
+        <v>66</v>
+      </c>
+      <c r="G512" t="s">
+        <v>32</v>
+      </c>
+      <c r="H512" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A513" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C513" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D513" t="s">
+        <v>151</v>
+      </c>
+      <c r="E513" t="s">
+        <v>152</v>
+      </c>
+      <c r="F513" t="s">
+        <v>17</v>
+      </c>
+      <c r="G513" t="s">
+        <v>8</v>
+      </c>
+      <c r="H513" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A514" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C514" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D514" t="s">
+        <v>149</v>
+      </c>
+      <c r="E514" t="s">
+        <v>150</v>
+      </c>
+      <c r="F514" t="s">
+        <v>11</v>
+      </c>
+      <c r="G514" t="s">
+        <v>8</v>
+      </c>
+      <c r="H514" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A515" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C515" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D515" t="s">
+        <v>151</v>
+      </c>
+      <c r="E515" t="s">
+        <v>152</v>
+      </c>
+      <c r="F515" t="s">
+        <v>17</v>
+      </c>
+      <c r="G515" t="s">
+        <v>8</v>
+      </c>
+      <c r="H515" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A516" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C516" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D516" t="s">
+        <v>149</v>
+      </c>
+      <c r="E516" t="s">
+        <v>150</v>
+      </c>
+      <c r="F516" t="s">
+        <v>9</v>
+      </c>
+      <c r="G516" t="s">
+        <v>8</v>
+      </c>
+      <c r="H516" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A517" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C517" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D517" t="s">
+        <v>149</v>
+      </c>
+      <c r="E517" t="s">
+        <v>150</v>
+      </c>
+      <c r="F517" t="s">
+        <v>11</v>
+      </c>
+      <c r="G517" t="s">
+        <v>8</v>
+      </c>
+      <c r="H517" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A518" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C518" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D518" t="s">
+        <v>151</v>
+      </c>
+      <c r="E518" t="s">
+        <v>152</v>
+      </c>
+      <c r="F518" t="s">
+        <v>33</v>
+      </c>
+      <c r="G518" t="s">
+        <v>10</v>
+      </c>
+      <c r="H518" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A519" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C519" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D519" t="s">
+        <v>147</v>
+      </c>
+      <c r="E519" t="s">
+        <v>148</v>
+      </c>
+      <c r="F519" t="s">
+        <v>73</v>
+      </c>
+      <c r="G519" t="s">
+        <v>8</v>
+      </c>
+      <c r="H519" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A520" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C520" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D520" t="s">
+        <v>147</v>
+      </c>
+      <c r="E520" t="s">
+        <v>148</v>
+      </c>
+      <c r="F520" t="s">
+        <v>31</v>
+      </c>
+      <c r="G520" t="s">
+        <v>734</v>
+      </c>
+      <c r="H520" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A521" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C521" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D521" t="s">
+        <v>147</v>
+      </c>
+      <c r="E521" t="s">
+        <v>148</v>
+      </c>
+      <c r="F521" t="s">
+        <v>49</v>
+      </c>
+      <c r="G521" t="s">
+        <v>10</v>
+      </c>
+      <c r="H521" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A522" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C522" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D522" t="s">
+        <v>147</v>
+      </c>
+      <c r="E522" t="s">
+        <v>148</v>
+      </c>
+      <c r="F522" t="s">
+        <v>25</v>
+      </c>
+      <c r="G522" t="s">
+        <v>8</v>
+      </c>
+      <c r="H522" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A523" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C523" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D523" t="s">
+        <v>151</v>
+      </c>
+      <c r="E523" t="s">
+        <v>152</v>
+      </c>
+      <c r="F523" t="s">
+        <v>17</v>
+      </c>
+      <c r="G523" t="s">
+        <v>8</v>
+      </c>
+      <c r="H523" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A524" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C524" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D524" t="s">
+        <v>147</v>
+      </c>
+      <c r="E524" t="s">
+        <v>148</v>
+      </c>
+      <c r="F524" t="s">
+        <v>31</v>
+      </c>
+      <c r="G524" t="s">
+        <v>734</v>
+      </c>
+      <c r="H524" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A525" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C525" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D525" t="s">
+        <v>149</v>
+      </c>
+      <c r="E525" t="s">
+        <v>150</v>
+      </c>
+      <c r="F525" t="s">
+        <v>11</v>
+      </c>
+      <c r="G525" t="s">
+        <v>8</v>
+      </c>
+      <c r="H525" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A526" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C526" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D526" t="s">
+        <v>151</v>
+      </c>
+      <c r="E526" t="s">
+        <v>152</v>
+      </c>
+      <c r="F526" t="s">
+        <v>17</v>
+      </c>
+      <c r="G526" t="s">
+        <v>8</v>
+      </c>
+      <c r="H526" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A527" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C527" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D527" t="s">
+        <v>149</v>
+      </c>
+      <c r="E527" t="s">
+        <v>150</v>
+      </c>
+      <c r="F527" t="s">
+        <v>29</v>
+      </c>
+      <c r="G527" t="s">
+        <v>8</v>
+      </c>
+      <c r="H527" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A528" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C528" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D528" t="s">
+        <v>149</v>
+      </c>
+      <c r="E528" t="s">
+        <v>150</v>
+      </c>
+      <c r="F528" t="s">
+        <v>14</v>
+      </c>
+      <c r="G528" t="s">
+        <v>8</v>
+      </c>
+      <c r="H528" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A529" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C529" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D529" t="s">
+        <v>147</v>
+      </c>
+      <c r="E529" t="s">
+        <v>148</v>
+      </c>
+      <c r="F529" t="s">
+        <v>21</v>
+      </c>
+      <c r="G529" t="s">
+        <v>8</v>
+      </c>
+      <c r="H529" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A530" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C530" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D530" t="s">
+        <v>147</v>
+      </c>
+      <c r="E530" t="s">
+        <v>148</v>
+      </c>
+      <c r="F530" t="s">
+        <v>16</v>
+      </c>
+      <c r="G530" t="s">
+        <v>8</v>
+      </c>
+      <c r="H530" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A531" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C531" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D531" t="s">
+        <v>147</v>
+      </c>
+      <c r="E531" t="s">
+        <v>148</v>
+      </c>
+      <c r="F531" t="s">
+        <v>73</v>
+      </c>
+      <c r="G531" t="s">
+        <v>8</v>
+      </c>
+      <c r="H531" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A532" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C532" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D532" t="s">
+        <v>147</v>
+      </c>
+      <c r="E532" t="s">
+        <v>148</v>
+      </c>
+      <c r="F532" t="s">
+        <v>49</v>
+      </c>
+      <c r="G532" t="s">
+        <v>8</v>
+      </c>
+      <c r="H532" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A533" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C533" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D533" t="s">
+        <v>147</v>
+      </c>
+      <c r="E533" t="s">
+        <v>148</v>
+      </c>
+      <c r="F533" t="s">
+        <v>25</v>
+      </c>
+      <c r="G533" t="s">
+        <v>8</v>
+      </c>
+      <c r="H533" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A534" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C534" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D534" t="s">
+        <v>147</v>
+      </c>
+      <c r="E534" t="s">
+        <v>148</v>
+      </c>
+      <c r="F534" t="s">
+        <v>73</v>
+      </c>
+      <c r="G534" t="s">
+        <v>8</v>
+      </c>
+      <c r="H534" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A535" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C535" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D535" t="s">
+        <v>151</v>
+      </c>
+      <c r="E535" t="s">
+        <v>152</v>
+      </c>
+      <c r="F535" t="s">
+        <v>33</v>
+      </c>
+      <c r="G535" t="s">
+        <v>8</v>
+      </c>
+      <c r="H535" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A536" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C536" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D536" t="s">
+        <v>151</v>
+      </c>
+      <c r="E536" t="s">
+        <v>152</v>
+      </c>
+      <c r="F536" t="s">
+        <v>42</v>
+      </c>
+      <c r="G536" t="s">
+        <v>13</v>
+      </c>
+      <c r="H536" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A537" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C537" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D537" t="s">
+        <v>147</v>
+      </c>
+      <c r="E537" t="s">
+        <v>148</v>
+      </c>
+      <c r="F537" t="s">
+        <v>25</v>
+      </c>
+      <c r="G537" t="s">
+        <v>8</v>
+      </c>
+      <c r="H537" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A538" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C538" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D538" t="s">
+        <v>147</v>
+      </c>
+      <c r="E538" t="s">
+        <v>148</v>
+      </c>
+      <c r="F538" t="s">
+        <v>25</v>
+      </c>
+      <c r="G538" t="s">
+        <v>32</v>
+      </c>
+      <c r="H538" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A539" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C539" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D539" t="s">
+        <v>151</v>
+      </c>
+      <c r="E539" t="s">
+        <v>152</v>
+      </c>
+      <c r="F539" t="s">
+        <v>42</v>
+      </c>
+      <c r="G539" t="s">
+        <v>13</v>
+      </c>
+      <c r="H539" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A540" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C540" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D540" t="s">
+        <v>151</v>
+      </c>
+      <c r="E540" t="s">
+        <v>152</v>
+      </c>
+      <c r="F540" t="s">
+        <v>6</v>
+      </c>
+      <c r="G540" t="s">
+        <v>8</v>
+      </c>
+      <c r="H540" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A541" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C541" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D541" t="s">
+        <v>217</v>
+      </c>
+      <c r="F541" t="s">
+        <v>40</v>
+      </c>
+      <c r="G541" t="s">
+        <v>8</v>
+      </c>
+      <c r="H541" t="s">
+        <v>19</v>
+      </c>
+      <c r="I541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A542" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C542" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D542" t="s">
+        <v>217</v>
+      </c>
+      <c r="F542" t="s">
+        <v>40</v>
+      </c>
+      <c r="G542" t="s">
+        <v>8</v>
+      </c>
+      <c r="H542" t="s">
+        <v>19</v>
+      </c>
+      <c r="I542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A543" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C543" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D543" t="s">
+        <v>217</v>
+      </c>
+      <c r="F543" t="s">
+        <v>40</v>
+      </c>
+      <c r="G543" t="s">
+        <v>8</v>
+      </c>
+      <c r="H543" t="s">
+        <v>19</v>
+      </c>
+      <c r="I543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A544" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C544" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D544" t="s">
+        <v>217</v>
+      </c>
+      <c r="F544" t="s">
+        <v>40</v>
+      </c>
+      <c r="G544" t="s">
+        <v>8</v>
+      </c>
+      <c r="H544" t="s">
+        <v>19</v>
+      </c>
+      <c r="I544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A545" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C545" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D545" t="s">
+        <v>217</v>
+      </c>
+      <c r="F545" t="s">
+        <v>40</v>
+      </c>
+      <c r="G545" t="s">
+        <v>8</v>
+      </c>
+      <c r="H545" t="s">
+        <v>19</v>
+      </c>
+      <c r="I545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A546" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C546" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D546" t="s">
+        <v>217</v>
+      </c>
+      <c r="F546" t="s">
+        <v>40</v>
+      </c>
+      <c r="G546" t="s">
+        <v>8</v>
+      </c>
+      <c r="H546" t="s">
+        <v>19</v>
+      </c>
+      <c r="I546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A547" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C547" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D547" t="s">
+        <v>151</v>
+      </c>
+      <c r="E547" t="s">
+        <v>152</v>
+      </c>
+      <c r="F547" t="s">
+        <v>26</v>
+      </c>
+      <c r="G547" t="s">
+        <v>8</v>
+      </c>
+      <c r="H547" t="s">
+        <v>19</v>
+      </c>
+      <c r="I547">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/first-atlas/producao_2026-03.xlsx
+++ b/first-atlas/producao_2026-03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EA949C-1415-45F1-9CA3-816AFB1C06B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C4B4DA-6239-449B-8558-F43A5DFB9D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3510" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3584" uniqueCount="1096">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -3243,6 +3243,90 @@
   </si>
   <si>
     <t>BKO</t>
+  </si>
+  <si>
+    <t>06029505000165</t>
+  </si>
+  <si>
+    <t>NEW DREAMS COMERCIO E SERVICOS DE INFORMATICA LTDA</t>
+  </si>
+  <si>
+    <t>19344602000194</t>
+  </si>
+  <si>
+    <t>PGA SOLUCOES TECNICAS LTDA</t>
+  </si>
+  <si>
+    <t>09324631000130</t>
+  </si>
+  <si>
+    <t>ESTRELA AZUL COMERCIO DE CEREAIS LTDA</t>
+  </si>
+  <si>
+    <t>11659063000170</t>
+  </si>
+  <si>
+    <t>GREGOLINI VEICULOS LTDA</t>
+  </si>
+  <si>
+    <t>64847157000130</t>
+  </si>
+  <si>
+    <t>DN REPARO GERAL LTDA</t>
+  </si>
+  <si>
+    <t>17840308000148</t>
+  </si>
+  <si>
+    <t>MP MOVEIS PROJETADOS LTDA</t>
+  </si>
+  <si>
+    <t>63308182000182</t>
+  </si>
+  <si>
+    <t>MV SERVICOS DE MOTO LTDA</t>
+  </si>
+  <si>
+    <t>62406655000111</t>
+  </si>
+  <si>
+    <t>GTPD ALIMENTACAO LTDA</t>
+  </si>
+  <si>
+    <t>59428502000160</t>
+  </si>
+  <si>
+    <t>TABACARIA FENIX LTDA</t>
+  </si>
+  <si>
+    <t>60103323000132</t>
+  </si>
+  <si>
+    <t>ENERGIZAR SOLUCOES ELETRICAS LTDA</t>
+  </si>
+  <si>
+    <t>65372525000101</t>
+  </si>
+  <si>
+    <t>PRIME SOLUTIONS GROUP LTDA</t>
+  </si>
+  <si>
+    <t>65097911000124</t>
+  </si>
+  <si>
+    <t>CLAODECIR LODI RISSINI CLAODECIR LODI RISSINI</t>
+  </si>
+  <si>
+    <t>50867370000107</t>
+  </si>
+  <si>
+    <t>GUSTAVO LIMA BATISTA</t>
+  </si>
+  <si>
+    <t>62187027000192</t>
+  </si>
+  <si>
+    <t>ALBA CRISTINA BATISTA</t>
   </si>
 </sst>
 </file>
@@ -3615,12 +3699,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:I503"/>
+  <dimension ref="A1:I517"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11849,11 +11934,11 @@
       <c r="C287" t="s">
         <v>622</v>
       </c>
-      <c r="D287" t="s">
-        <v>1061</v>
-      </c>
-      <c r="E287" t="s">
-        <v>1062</v>
+      <c r="D287" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E287" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F287" t="s">
         <v>17</v>
@@ -13268,7 +13353,7 @@
         <v>8</v>
       </c>
       <c r="H336" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I336">
         <v>0</v>
@@ -13674,7 +13759,7 @@
         <v>8</v>
       </c>
       <c r="H350" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I350">
         <v>0</v>
@@ -14370,7 +14455,7 @@
         <v>31</v>
       </c>
       <c r="H374" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I374">
         <v>0</v>
@@ -14428,7 +14513,7 @@
         <v>8</v>
       </c>
       <c r="H376" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I376">
         <v>0</v>
@@ -14515,7 +14600,7 @@
         <v>8</v>
       </c>
       <c r="H379" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I379">
         <v>0</v>
@@ -14950,7 +15035,7 @@
         <v>31</v>
       </c>
       <c r="H394" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I394">
         <v>0</v>
@@ -15008,7 +15093,7 @@
         <v>8</v>
       </c>
       <c r="H396" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I396">
         <v>0</v>
@@ -15414,7 +15499,7 @@
         <v>8</v>
       </c>
       <c r="H410" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I410">
         <v>0</v>
@@ -15588,10 +15673,13 @@
         <v>8</v>
       </c>
       <c r="H416" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" s="1">
         <v>46092</v>
       </c>
@@ -15616,8 +15704,11 @@
       <c r="H417" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" s="1">
         <v>46092</v>
       </c>
@@ -15642,8 +15733,11 @@
       <c r="H418" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
         <v>46092</v>
       </c>
@@ -15668,8 +15762,11 @@
       <c r="H419" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" s="1">
         <v>46092</v>
       </c>
@@ -15694,8 +15791,11 @@
       <c r="H420" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
         <v>46092</v>
       </c>
@@ -15718,10 +15818,13 @@
         <v>8</v>
       </c>
       <c r="H421" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
         <v>46092</v>
       </c>
@@ -15746,8 +15849,11 @@
       <c r="H422" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
         <v>46092</v>
       </c>
@@ -15772,8 +15878,11 @@
       <c r="H423" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
         <v>46092</v>
       </c>
@@ -15798,8 +15907,11 @@
       <c r="H424" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
         <v>46092</v>
       </c>
@@ -15824,8 +15936,11 @@
       <c r="H425" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
         <v>46092</v>
       </c>
@@ -15850,8 +15965,11 @@
       <c r="H426" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
         <v>46092</v>
       </c>
@@ -15874,10 +15992,13 @@
         <v>8</v>
       </c>
       <c r="H427" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" s="1">
         <v>46092</v>
       </c>
@@ -15900,10 +16021,13 @@
         <v>8</v>
       </c>
       <c r="H428" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
         <v>46092</v>
       </c>
@@ -15926,10 +16050,13 @@
         <v>7</v>
       </c>
       <c r="H429" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I429" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
         <v>46092</v>
       </c>
@@ -15954,8 +16081,11 @@
       <c r="H430" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
         <v>46092</v>
       </c>
@@ -15980,8 +16110,11 @@
       <c r="H431" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" s="1">
         <v>46092</v>
       </c>
@@ -16006,8 +16139,11 @@
       <c r="H432" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" s="1">
         <v>46092</v>
       </c>
@@ -16032,8 +16168,11 @@
       <c r="H433" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" s="1">
         <v>46092</v>
       </c>
@@ -16058,8 +16197,11 @@
       <c r="H434" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" s="1">
         <v>46092</v>
       </c>
@@ -16084,8 +16226,11 @@
       <c r="H435" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
         <v>46092</v>
       </c>
@@ -16110,8 +16255,11 @@
       <c r="H436" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
         <v>46092</v>
       </c>
@@ -16136,8 +16284,11 @@
       <c r="H437" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
         <v>46092</v>
       </c>
@@ -16162,8 +16313,11 @@
       <c r="H438" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
         <v>46092</v>
       </c>
@@ -16188,8 +16342,11 @@
       <c r="H439" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
         <v>46092</v>
       </c>
@@ -16212,10 +16369,13 @@
         <v>8</v>
       </c>
       <c r="H440" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
         <v>46092</v>
       </c>
@@ -16240,8 +16400,11 @@
       <c r="H441" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" s="1">
         <v>46092</v>
       </c>
@@ -16264,10 +16427,13 @@
         <v>934</v>
       </c>
       <c r="H442" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" s="1">
         <v>46092</v>
       </c>
@@ -16290,10 +16456,13 @@
         <v>8</v>
       </c>
       <c r="H443" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
         <v>46092</v>
       </c>
@@ -16316,10 +16485,13 @@
         <v>8</v>
       </c>
       <c r="H444" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" s="1">
         <v>46092</v>
       </c>
@@ -16344,8 +16516,11 @@
       <c r="H445" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
         <v>46092</v>
       </c>
@@ -16368,10 +16543,13 @@
         <v>8</v>
       </c>
       <c r="H446" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" s="1">
         <v>46092</v>
       </c>
@@ -16396,8 +16574,11 @@
       <c r="H447" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" s="1">
         <v>46092</v>
       </c>
@@ -16422,8 +16603,11 @@
       <c r="H448" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" s="1">
         <v>46092</v>
       </c>
@@ -16448,8 +16632,11 @@
       <c r="H449" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" s="1">
         <v>46092</v>
       </c>
@@ -16472,10 +16659,13 @@
         <v>934</v>
       </c>
       <c r="H450" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
         <v>46092</v>
       </c>
@@ -16500,8 +16690,11 @@
       <c r="H451" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452" s="1">
         <v>46092</v>
       </c>
@@ -16526,8 +16719,11 @@
       <c r="H452" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" s="1">
         <v>46092</v>
       </c>
@@ -16550,10 +16746,10 @@
         <v>13</v>
       </c>
       <c r="H453" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" s="1">
         <v>46092</v>
       </c>
@@ -16578,8 +16774,11 @@
       <c r="H454" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" s="1">
         <v>46092</v>
       </c>
@@ -16604,8 +16803,11 @@
       <c r="H455" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
         <v>46092</v>
       </c>
@@ -16628,10 +16830,13 @@
         <v>8</v>
       </c>
       <c r="H456" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" s="1">
         <v>46092</v>
       </c>
@@ -16656,8 +16861,11 @@
       <c r="H457" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458" s="1">
         <v>46092</v>
       </c>
@@ -16682,8 +16890,11 @@
       <c r="H458" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
         <v>46092</v>
       </c>
@@ -16708,8 +16919,11 @@
       <c r="H459" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" s="1">
         <v>46092</v>
       </c>
@@ -16734,8 +16948,11 @@
       <c r="H460" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
         <v>46092</v>
       </c>
@@ -16760,8 +16977,11 @@
       <c r="H461" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462" s="1">
         <v>46092</v>
       </c>
@@ -16784,10 +17004,13 @@
         <v>8</v>
       </c>
       <c r="H462" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I462" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" s="1">
         <v>46092</v>
       </c>
@@ -16812,8 +17035,11 @@
       <c r="H463" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464" s="1">
         <v>46092</v>
       </c>
@@ -16838,8 +17064,11 @@
       <c r="H464" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" s="1">
         <v>46092</v>
       </c>
@@ -16864,8 +17093,11 @@
       <c r="H465" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" s="1">
         <v>46092</v>
       </c>
@@ -16890,8 +17122,11 @@
       <c r="H466" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" s="1">
         <v>46092</v>
       </c>
@@ -16914,10 +17149,13 @@
         <v>8</v>
       </c>
       <c r="H467" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I467" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" s="1">
         <v>46092</v>
       </c>
@@ -16942,8 +17180,11 @@
       <c r="H468" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469" s="1">
         <v>46092</v>
       </c>
@@ -16968,8 +17209,11 @@
       <c r="H469" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" s="1">
         <v>46092</v>
       </c>
@@ -16992,10 +17236,13 @@
         <v>8</v>
       </c>
       <c r="H470" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" s="1">
         <v>46092</v>
       </c>
@@ -17020,8 +17267,11 @@
       <c r="H471" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" s="1">
         <v>46092</v>
       </c>
@@ -17044,10 +17294,13 @@
         <v>8</v>
       </c>
       <c r="H472" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" s="1">
         <v>46092</v>
       </c>
@@ -17070,10 +17323,13 @@
         <v>8</v>
       </c>
       <c r="H473" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" s="1">
         <v>46092</v>
       </c>
@@ -17098,8 +17354,11 @@
       <c r="H474" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" s="1">
         <v>46092</v>
       </c>
@@ -17122,10 +17381,13 @@
         <v>8</v>
       </c>
       <c r="H475" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I475" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" s="1">
         <v>46092</v>
       </c>
@@ -17148,10 +17410,13 @@
         <v>635</v>
       </c>
       <c r="H476" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" s="1">
         <v>46092</v>
       </c>
@@ -17174,10 +17439,13 @@
         <v>10</v>
       </c>
       <c r="H477" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" s="1">
         <v>46092</v>
       </c>
@@ -17202,8 +17470,11 @@
       <c r="H478" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" s="1">
         <v>46092</v>
       </c>
@@ -17228,8 +17499,11 @@
       <c r="H479" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" s="1">
         <v>46092</v>
       </c>
@@ -17254,8 +17528,11 @@
       <c r="H480" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
         <v>46092</v>
       </c>
@@ -17278,10 +17555,13 @@
         <v>8</v>
       </c>
       <c r="H481" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
         <v>46092</v>
       </c>
@@ -17304,10 +17584,13 @@
         <v>8</v>
       </c>
       <c r="H482" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
         <v>46092</v>
       </c>
@@ -17332,8 +17615,11 @@
       <c r="H483" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" s="1">
         <v>46092</v>
       </c>
@@ -17358,8 +17644,11 @@
       <c r="H484" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
         <v>46092</v>
       </c>
@@ -17382,10 +17671,13 @@
         <v>8</v>
       </c>
       <c r="H485" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I485" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" s="1">
         <v>46092</v>
       </c>
@@ -17410,8 +17702,11 @@
       <c r="H486" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
         <v>46092</v>
       </c>
@@ -17434,10 +17729,13 @@
         <v>8</v>
       </c>
       <c r="H487" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I487" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
         <v>46092</v>
       </c>
@@ -17462,8 +17760,11 @@
       <c r="H488" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" s="1">
         <v>46092</v>
       </c>
@@ -17488,8 +17789,11 @@
       <c r="H489" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" s="1">
         <v>46092</v>
       </c>
@@ -17512,10 +17816,13 @@
         <v>8</v>
       </c>
       <c r="H490" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" s="1">
         <v>46092</v>
       </c>
@@ -17538,10 +17845,13 @@
         <v>8</v>
       </c>
       <c r="H491" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
         <v>46092</v>
       </c>
@@ -17566,8 +17876,11 @@
       <c r="H492" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" s="1">
         <v>46092</v>
       </c>
@@ -17592,8 +17905,11 @@
       <c r="H493" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494" s="1">
         <v>46092</v>
       </c>
@@ -17618,8 +17934,11 @@
       <c r="H494" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A495" s="1">
         <v>46092</v>
       </c>
@@ -17644,8 +17963,11 @@
       <c r="H495" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" s="1">
         <v>46092</v>
       </c>
@@ -17669,6 +17991,9 @@
       </c>
       <c r="H496" t="s">
         <v>21</v>
+      </c>
+      <c r="I496">
+        <v>0</v>
       </c>
     </row>
     <row r="497" spans="1:9" x14ac:dyDescent="0.25">
@@ -17854,6 +18179,319 @@
       </c>
       <c r="I503">
         <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A504" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C504" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F504" t="s">
+        <v>16</v>
+      </c>
+      <c r="G504" t="s">
+        <v>8</v>
+      </c>
+      <c r="H504" t="s">
+        <v>19</v>
+      </c>
+      <c r="I504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A505" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C505" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F505" t="s">
+        <v>20</v>
+      </c>
+      <c r="G505" t="s">
+        <v>8</v>
+      </c>
+      <c r="H505" t="s">
+        <v>19</v>
+      </c>
+      <c r="I505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A506" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C506" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F506" t="s">
+        <v>39</v>
+      </c>
+      <c r="G506" t="s">
+        <v>8</v>
+      </c>
+      <c r="H506" t="s">
+        <v>19</v>
+      </c>
+      <c r="I506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A507" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C507" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F507" t="s">
+        <v>39</v>
+      </c>
+      <c r="G507" t="s">
+        <v>8</v>
+      </c>
+      <c r="H507" t="s">
+        <v>19</v>
+      </c>
+      <c r="I507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A508" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C508" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F508" t="s">
+        <v>39</v>
+      </c>
+      <c r="G508" t="s">
+        <v>8</v>
+      </c>
+      <c r="H508" t="s">
+        <v>19</v>
+      </c>
+      <c r="I508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A509" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F509" t="s">
+        <v>20</v>
+      </c>
+      <c r="G509" t="s">
+        <v>8</v>
+      </c>
+      <c r="H509" t="s">
+        <v>19</v>
+      </c>
+      <c r="I509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A510" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F510" t="s">
+        <v>39</v>
+      </c>
+      <c r="G510" t="s">
+        <v>8</v>
+      </c>
+      <c r="H510" t="s">
+        <v>19</v>
+      </c>
+      <c r="I510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A511" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F511" t="s">
+        <v>39</v>
+      </c>
+      <c r="G511" t="s">
+        <v>8</v>
+      </c>
+      <c r="H511" t="s">
+        <v>19</v>
+      </c>
+      <c r="I511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A512" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C512" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F512" t="s">
+        <v>20</v>
+      </c>
+      <c r="G512" t="s">
+        <v>8</v>
+      </c>
+      <c r="H512" t="s">
+        <v>19</v>
+      </c>
+      <c r="I512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A513" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C513" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F513" t="s">
+        <v>39</v>
+      </c>
+      <c r="G513" t="s">
+        <v>8</v>
+      </c>
+      <c r="H513" t="s">
+        <v>19</v>
+      </c>
+      <c r="I513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A514" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C514" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F514" t="s">
+        <v>41</v>
+      </c>
+      <c r="G514" t="s">
+        <v>8</v>
+      </c>
+      <c r="H514" t="s">
+        <v>19</v>
+      </c>
+      <c r="I514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A515" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C515" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F515" t="s">
+        <v>39</v>
+      </c>
+      <c r="G515" t="s">
+        <v>40</v>
+      </c>
+      <c r="H515" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A516" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C516" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F516" t="s">
+        <v>39</v>
+      </c>
+      <c r="G516" t="s">
+        <v>40</v>
+      </c>
+      <c r="H516" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A517" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C517" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F517" t="s">
+        <v>39</v>
+      </c>
+      <c r="G517" t="s">
+        <v>40</v>
+      </c>
+      <c r="H517" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/first-atlas/producao_2026-03.xlsx
+++ b/first-atlas/producao_2026-03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C032B76F-27EF-49AF-854F-5E6D661E878A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFCBAF7-42CB-495E-8D6F-15261B7ED12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$547</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$I$591</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4102" uniqueCount="1236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4150" uniqueCount="1250">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -3747,6 +3747,48 @@
   </si>
   <si>
     <t>AS PILAR TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>45610115000136</t>
+  </si>
+  <si>
+    <t>CAFE FRUTO CERTO LTDA</t>
+  </si>
+  <si>
+    <t>11197494000162</t>
+  </si>
+  <si>
+    <t>CONSTRUCOES BUENOS AIRES LTDA</t>
+  </si>
+  <si>
+    <t>62694878000121</t>
+  </si>
+  <si>
+    <t>LIGOCKI BURGER LTDA</t>
+  </si>
+  <si>
+    <t>60939673000133</t>
+  </si>
+  <si>
+    <t>AMAZON DRONES LTDA</t>
+  </si>
+  <si>
+    <t>61106874000112</t>
+  </si>
+  <si>
+    <t>GRUPO BETTA ALPHA LTDA</t>
+  </si>
+  <si>
+    <t>36699006000146</t>
+  </si>
+  <si>
+    <t>ATL COMERCIO DE MAQUINAS EQUIPAMENTOS E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>35071900000104</t>
+  </si>
+  <si>
+    <t>MC SERVICOS EM TECNOLOGIA DA INFORMACAO LTDA</t>
   </si>
 </sst>
 </file>
@@ -4119,14 +4161,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:I591"/>
+  <dimension ref="A1:I598"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" customWidth="1"/>
     <col min="8" max="8" width="20.85546875" customWidth="1"/>
-    <col min="9" max="9" width="76.7109375" customWidth="1"/>
+    <col min="9" max="9" width="67.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11128,10 +11170,10 @@
         <v>10</v>
       </c>
       <c r="H246" t="s">
-        <v>29</v>
-      </c>
-      <c r="I246" t="s">
-        <v>34</v>
+        <v>23</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
@@ -13320,7 +13362,7 @@
         <v>7</v>
       </c>
       <c r="H322" t="s">
-        <v>23</v>
+        <v>699</v>
       </c>
       <c r="I322">
         <v>0</v>
@@ -14088,7 +14130,7 @@
         <v>8</v>
       </c>
       <c r="H349" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I349">
         <v>0</v>
@@ -15016,7 +15058,7 @@
         <v>8</v>
       </c>
       <c r="H381" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I381" t="s">
         <v>57</v>
@@ -16437,7 +16479,7 @@
         <v>7</v>
       </c>
       <c r="H430" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I430">
         <v>0</v>
@@ -16553,7 +16595,7 @@
         <v>10</v>
       </c>
       <c r="H434" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I434">
         <v>0</v>
@@ -16640,7 +16682,7 @@
         <v>13</v>
       </c>
       <c r="H437" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I437">
         <v>0</v>
@@ -16930,7 +16972,7 @@
         <v>8</v>
       </c>
       <c r="H447" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I447">
         <v>0</v>
@@ -16988,7 +17030,7 @@
         <v>7</v>
       </c>
       <c r="H449" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I449">
         <v>0</v>
@@ -17101,7 +17143,7 @@
         <v>8</v>
       </c>
       <c r="H453" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I453">
         <v>0</v>
@@ -17275,7 +17317,7 @@
         <v>8</v>
       </c>
       <c r="H459" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I459">
         <v>0</v>
@@ -17768,7 +17810,7 @@
         <v>8</v>
       </c>
       <c r="H476" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I476">
         <v>0</v>
@@ -17942,7 +17984,7 @@
         <v>8</v>
       </c>
       <c r="H482" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I482">
         <v>0</v>
@@ -18203,7 +18245,7 @@
         <v>8</v>
       </c>
       <c r="H491" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I491">
         <v>0</v>
@@ -18232,7 +18274,7 @@
         <v>31</v>
       </c>
       <c r="H492" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I492">
         <v>0</v>
@@ -18778,6 +18820,9 @@
       <c r="H512" t="s">
         <v>19</v>
       </c>
+      <c r="I512">
+        <v>0</v>
+      </c>
     </row>
     <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
@@ -18801,6 +18846,9 @@
       <c r="H513" t="s">
         <v>19</v>
       </c>
+      <c r="I513">
+        <v>0</v>
+      </c>
     </row>
     <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
@@ -18824,6 +18872,9 @@
       <c r="H514" t="s">
         <v>19</v>
       </c>
+      <c r="I514">
+        <v>0</v>
+      </c>
     </row>
     <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" s="1">
@@ -18850,6 +18901,9 @@
       <c r="H515" t="s">
         <v>21</v>
       </c>
+      <c r="I515">
+        <v>0</v>
+      </c>
     </row>
     <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" s="1">
@@ -18876,6 +18930,9 @@
       <c r="H516" t="s">
         <v>19</v>
       </c>
+      <c r="I516">
+        <v>0</v>
+      </c>
     </row>
     <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
@@ -18931,6 +18988,9 @@
       <c r="H518" t="s">
         <v>21</v>
       </c>
+      <c r="I518">
+        <v>0</v>
+      </c>
     </row>
     <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
@@ -18955,7 +19015,10 @@
         <v>31</v>
       </c>
       <c r="H519" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="I519">
+        <v>0</v>
       </c>
     </row>
     <row r="520" spans="1:9" x14ac:dyDescent="0.25">
@@ -18983,6 +19046,9 @@
       <c r="H520" t="s">
         <v>19</v>
       </c>
+      <c r="I520">
+        <v>0</v>
+      </c>
     </row>
     <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" s="1">
@@ -19009,6 +19075,9 @@
       <c r="H521" t="s">
         <v>19</v>
       </c>
+      <c r="I521">
+        <v>0</v>
+      </c>
     </row>
     <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
@@ -19035,6 +19104,9 @@
       <c r="H522" t="s">
         <v>19</v>
       </c>
+      <c r="I522">
+        <v>0</v>
+      </c>
     </row>
     <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
@@ -19061,6 +19133,9 @@
       <c r="H523" t="s">
         <v>19</v>
       </c>
+      <c r="I523">
+        <v>0</v>
+      </c>
     </row>
     <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
@@ -19085,7 +19160,10 @@
         <v>8</v>
       </c>
       <c r="H524" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="I524" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="525" spans="1:9" x14ac:dyDescent="0.25">
@@ -19113,6 +19191,9 @@
       <c r="H525" t="s">
         <v>19</v>
       </c>
+      <c r="I525">
+        <v>0</v>
+      </c>
     </row>
     <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
@@ -19139,6 +19220,9 @@
       <c r="H526" t="s">
         <v>21</v>
       </c>
+      <c r="I526">
+        <v>0</v>
+      </c>
     </row>
     <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
@@ -19163,7 +19247,10 @@
         <v>7</v>
       </c>
       <c r="H527" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="I527" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="528" spans="1:9" x14ac:dyDescent="0.25">
@@ -19191,8 +19278,11 @@
       <c r="H528" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" s="1">
         <v>46093</v>
       </c>
@@ -19215,10 +19305,13 @@
         <v>7</v>
       </c>
       <c r="H529" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
         <v>46093</v>
       </c>
@@ -19243,8 +19336,11 @@
       <c r="H530" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
         <v>46093</v>
       </c>
@@ -19269,8 +19365,11 @@
       <c r="H531" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
         <v>46093</v>
       </c>
@@ -19295,8 +19394,11 @@
       <c r="H532" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
         <v>46093</v>
       </c>
@@ -19321,8 +19423,11 @@
       <c r="H533" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" s="1">
         <v>46093</v>
       </c>
@@ -19347,8 +19452,11 @@
       <c r="H534" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" s="1">
         <v>46093</v>
       </c>
@@ -19371,10 +19479,13 @@
         <v>8</v>
       </c>
       <c r="H535" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" s="1">
         <v>46093</v>
       </c>
@@ -19399,8 +19510,11 @@
       <c r="H536" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" s="1">
         <v>46093</v>
       </c>
@@ -19425,8 +19539,11 @@
       <c r="H537" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" s="1">
         <v>46093</v>
       </c>
@@ -19451,8 +19568,11 @@
       <c r="H538" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" s="1">
         <v>46093</v>
       </c>
@@ -19475,10 +19595,13 @@
         <v>8</v>
       </c>
       <c r="H539" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" s="1">
         <v>46093</v>
       </c>
@@ -19501,10 +19624,13 @@
         <v>8</v>
       </c>
       <c r="H540" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" s="1">
         <v>46093</v>
       </c>
@@ -19527,10 +19653,13 @@
         <v>8</v>
       </c>
       <c r="H541" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" s="1">
         <v>46093</v>
       </c>
@@ -19555,8 +19684,11 @@
       <c r="H542" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" s="1">
         <v>46093</v>
       </c>
@@ -19581,8 +19713,11 @@
       <c r="H543" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" s="1">
         <v>46093</v>
       </c>
@@ -19607,8 +19742,11 @@
       <c r="H544" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" s="1">
         <v>46093</v>
       </c>
@@ -19633,8 +19771,11 @@
       <c r="H545" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546" s="1">
         <v>46093</v>
       </c>
@@ -19659,8 +19800,11 @@
       <c r="H546" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" s="1">
         <v>46093</v>
       </c>
@@ -19685,8 +19829,11 @@
       <c r="H547" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" s="1">
         <v>46093</v>
       </c>
@@ -19709,10 +19856,13 @@
         <v>31</v>
       </c>
       <c r="H548" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" s="1">
         <v>46093</v>
       </c>
@@ -19737,8 +19887,11 @@
       <c r="H549" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" s="1">
         <v>46093</v>
       </c>
@@ -19761,10 +19914,13 @@
         <v>8</v>
       </c>
       <c r="H550" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" s="1">
         <v>46093</v>
       </c>
@@ -19789,8 +19945,11 @@
       <c r="H551" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552" s="1">
         <v>46093</v>
       </c>
@@ -19815,8 +19974,11 @@
       <c r="H552" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" s="1">
         <v>46093</v>
       </c>
@@ -19841,8 +20003,11 @@
       <c r="H553" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" s="1">
         <v>46093</v>
       </c>
@@ -19865,10 +20030,13 @@
         <v>8</v>
       </c>
       <c r="H554" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" s="1">
         <v>46093</v>
       </c>
@@ -19893,8 +20061,11 @@
       <c r="H555" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" s="1">
         <v>46093</v>
       </c>
@@ -19919,8 +20090,11 @@
       <c r="H556" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" s="1">
         <v>46093</v>
       </c>
@@ -19943,10 +20117,13 @@
         <v>8</v>
       </c>
       <c r="H557" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I557" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" s="1">
         <v>46093</v>
       </c>
@@ -19971,8 +20148,11 @@
       <c r="H558" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" s="1">
         <v>46093</v>
       </c>
@@ -19997,8 +20177,11 @@
       <c r="H559" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" s="1">
         <v>46093</v>
       </c>
@@ -20023,8 +20206,11 @@
       <c r="H560" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" s="1">
         <v>46093</v>
       </c>
@@ -20047,10 +20233,13 @@
         <v>8</v>
       </c>
       <c r="H561" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" s="1">
         <v>46093</v>
       </c>
@@ -20073,10 +20262,13 @@
         <v>8</v>
       </c>
       <c r="H562" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
         <v>46093</v>
       </c>
@@ -20101,8 +20293,11 @@
       <c r="H563" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" s="1">
         <v>46093</v>
       </c>
@@ -20127,8 +20322,11 @@
       <c r="H564" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" s="1">
         <v>46093</v>
       </c>
@@ -20153,8 +20351,11 @@
       <c r="H565" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" s="1">
         <v>46093</v>
       </c>
@@ -20179,8 +20380,11 @@
       <c r="H566" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" s="1">
         <v>46093</v>
       </c>
@@ -20205,8 +20409,11 @@
       <c r="H567" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I567" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" s="1">
         <v>46093</v>
       </c>
@@ -20231,8 +20438,11 @@
       <c r="H568" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" s="1">
         <v>46093</v>
       </c>
@@ -20257,8 +20467,11 @@
       <c r="H569" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" s="1">
         <v>46093</v>
       </c>
@@ -20281,10 +20494,13 @@
         <v>8</v>
       </c>
       <c r="H570" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" s="1">
         <v>46093</v>
       </c>
@@ -20309,8 +20525,11 @@
       <c r="H571" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" s="1">
         <v>46093</v>
       </c>
@@ -20335,8 +20554,11 @@
       <c r="H572" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" s="1">
         <v>46093</v>
       </c>
@@ -20361,8 +20583,11 @@
       <c r="H573" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" s="1">
         <v>46093</v>
       </c>
@@ -20385,10 +20610,13 @@
         <v>8</v>
       </c>
       <c r="H574" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" s="1">
         <v>46093</v>
       </c>
@@ -20413,8 +20641,11 @@
       <c r="H575" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" s="1">
         <v>46093</v>
       </c>
@@ -20439,8 +20670,11 @@
       <c r="H576" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" s="1">
         <v>46093</v>
       </c>
@@ -20465,8 +20699,11 @@
       <c r="H577" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" s="1">
         <v>46093</v>
       </c>
@@ -20491,8 +20728,11 @@
       <c r="H578" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579" s="1">
         <v>46093</v>
       </c>
@@ -20515,10 +20755,13 @@
         <v>8</v>
       </c>
       <c r="H579" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I579" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" s="1">
         <v>46093</v>
       </c>
@@ -20541,10 +20784,13 @@
         <v>7</v>
       </c>
       <c r="H580" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="581" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" s="1">
         <v>46093</v>
       </c>
@@ -20569,8 +20815,11 @@
       <c r="H581" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" s="1">
         <v>46093</v>
       </c>
@@ -20595,8 +20844,11 @@
       <c r="H582" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="583" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" s="1">
         <v>46093</v>
       </c>
@@ -20621,8 +20873,11 @@
       <c r="H583" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" s="1">
         <v>46093</v>
       </c>
@@ -20647,8 +20902,11 @@
       <c r="H584" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" s="1">
         <v>46093</v>
       </c>
@@ -20673,8 +20931,11 @@
       <c r="H585" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" s="1">
         <v>46093</v>
       </c>
@@ -20699,8 +20960,11 @@
       <c r="H586" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" s="1">
         <v>46093</v>
       </c>
@@ -20725,8 +20989,11 @@
       <c r="H587" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="588" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I587">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" s="1">
         <v>46093</v>
       </c>
@@ -20752,7 +21019,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="589" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" s="1">
         <v>46093</v>
       </c>
@@ -20777,8 +21044,11 @@
       <c r="H589" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="590" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" s="1">
         <v>46093</v>
       </c>
@@ -20803,8 +21073,11 @@
       <c r="H590" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="591" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I590">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" s="1">
         <v>46093</v>
       </c>
@@ -20827,7 +21100,198 @@
         <v>8</v>
       </c>
       <c r="H591" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="I591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A592" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B592" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C592" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D592" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F592" t="s">
+        <v>39</v>
+      </c>
+      <c r="G592" t="s">
+        <v>8</v>
+      </c>
+      <c r="H592" t="s">
+        <v>19</v>
+      </c>
+      <c r="I592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A593" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B593" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C593" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D593" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E593" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F593" t="s">
+        <v>16</v>
+      </c>
+      <c r="G593" t="s">
+        <v>8</v>
+      </c>
+      <c r="H593" t="s">
+        <v>19</v>
+      </c>
+      <c r="I593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A594" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C594" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D594" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F594" t="s">
+        <v>39</v>
+      </c>
+      <c r="G594" t="s">
+        <v>8</v>
+      </c>
+      <c r="H594" t="s">
+        <v>19</v>
+      </c>
+      <c r="I594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A595" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B595" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C595" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D595" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F595" t="s">
+        <v>39</v>
+      </c>
+      <c r="G595" t="s">
+        <v>8</v>
+      </c>
+      <c r="H595" t="s">
+        <v>19</v>
+      </c>
+      <c r="I595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A596" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B596" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C596" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D596" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F596" t="s">
+        <v>39</v>
+      </c>
+      <c r="G596" t="s">
+        <v>8</v>
+      </c>
+      <c r="H596" t="s">
+        <v>19</v>
+      </c>
+      <c r="I596">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A597" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B597" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C597" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D597" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F597" t="s">
+        <v>39</v>
+      </c>
+      <c r="G597" t="s">
+        <v>8</v>
+      </c>
+      <c r="H597" t="s">
+        <v>19</v>
+      </c>
+      <c r="I597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A598" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B598" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C598" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D598" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E598" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F598" t="s">
+        <v>16</v>
+      </c>
+      <c r="G598" t="s">
+        <v>8</v>
+      </c>
+      <c r="H598" t="s">
+        <v>19</v>
+      </c>
+      <c r="I598">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/first-atlas/producao_2026-03.xlsx
+++ b/first-atlas/producao_2026-03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFCBAF7-42CB-495E-8D6F-15261B7ED12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E63B3B-0EC3-4415-8E09-0ACB01E0739A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4150" uniqueCount="1250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4827" uniqueCount="1451">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -3233,9 +3233,6 @@
     <t>LOBO</t>
   </si>
   <si>
-    <t>LUCAS</t>
-  </si>
-  <si>
     <t>BKO</t>
   </si>
   <si>
@@ -3789,6 +3786,612 @@
   </si>
   <si>
     <t>MC SERVICOS EM TECNOLOGIA DA INFORMACAO LTDA</t>
+  </si>
+  <si>
+    <t>GILSON</t>
+  </si>
+  <si>
+    <t>FALCAO</t>
+  </si>
+  <si>
+    <t>36334028000102</t>
+  </si>
+  <si>
+    <t>INOVA RECICLAGEM LTDA</t>
+  </si>
+  <si>
+    <t>19315391000161</t>
+  </si>
+  <si>
+    <t>LOOP PLAY SERVICOS E ELETRONICOS LTDA</t>
+  </si>
+  <si>
+    <t>30154037000135</t>
+  </si>
+  <si>
+    <t>R.J. FRIOTEC AR CONDICIONADO LTDA</t>
+  </si>
+  <si>
+    <t>40505985000121</t>
+  </si>
+  <si>
+    <t>ADRIANA MANGANELLI CARVALHO SERVICOS DE COSTURA LTDA.</t>
+  </si>
+  <si>
+    <t>53092192000170</t>
+  </si>
+  <si>
+    <t>BM SOLUCOES E MONTAGENS INDUSTRIAIS LTDA</t>
+  </si>
+  <si>
+    <t>61366494000117</t>
+  </si>
+  <si>
+    <t>RC INSTALACOES ELETRICAS E SISTEMA LTDA</t>
+  </si>
+  <si>
+    <t>04224252000155</t>
+  </si>
+  <si>
+    <t>EMBUTIDOS BORGES LTDA</t>
+  </si>
+  <si>
+    <t>62820870000164</t>
+  </si>
+  <si>
+    <t>HME CONSTRUTORA LTDA</t>
+  </si>
+  <si>
+    <t>63184990000185</t>
+  </si>
+  <si>
+    <t>PRACA 135 BAR LTDA</t>
+  </si>
+  <si>
+    <t>45914662000105</t>
+  </si>
+  <si>
+    <t>MHR COMERCIO DE CORREIAS LTDA</t>
+  </si>
+  <si>
+    <t>61348046000190</t>
+  </si>
+  <si>
+    <t>ROCHA FORCE ONE OF GOD LTDA</t>
+  </si>
+  <si>
+    <t>64984910000139</t>
+  </si>
+  <si>
+    <t>HRM CREDITOS E FINANCEIRAS LTDA</t>
+  </si>
+  <si>
+    <t>Felipe Silva</t>
+  </si>
+  <si>
+    <t>61031550000162</t>
+  </si>
+  <si>
+    <t>KMN COMERCIO FERRAMENTAS E PROTECAO LTDA</t>
+  </si>
+  <si>
+    <t>54509606000186</t>
+  </si>
+  <si>
+    <t>DRA MARIANA SILVA PSICOLOGIA LTDA</t>
+  </si>
+  <si>
+    <t>26393072000130</t>
+  </si>
+  <si>
+    <t>RAMOS &amp; ARAUJO ENGENHARIA &amp; CONSULTORIA LTDA</t>
+  </si>
+  <si>
+    <t>61373246000101</t>
+  </si>
+  <si>
+    <t>THAINA SERRALHERIA LTDA</t>
+  </si>
+  <si>
+    <t>64505240000120</t>
+  </si>
+  <si>
+    <t>H. MENDES ENGENHARIA LTDA</t>
+  </si>
+  <si>
+    <t>65086849000175</t>
+  </si>
+  <si>
+    <t>J. DE FRANCA &amp; M. DOS S. AGUIAR BARROS LTDA</t>
+  </si>
+  <si>
+    <t>63332298000157</t>
+  </si>
+  <si>
+    <t>DIRUJIN SUSHI LTDA</t>
+  </si>
+  <si>
+    <t>37983837000108</t>
+  </si>
+  <si>
+    <t>M. L. TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>59552563000135</t>
+  </si>
+  <si>
+    <t>LCG TRANSPORTES E LOCACAO LTDA</t>
+  </si>
+  <si>
+    <t>50837385000203</t>
+  </si>
+  <si>
+    <t>VICTOR GIRO LTDA</t>
+  </si>
+  <si>
+    <t>48183025000102</t>
+  </si>
+  <si>
+    <t>MSN &amp; JSP EQUIPAMENTOS DE PREVENCAO CONTRA INCENDIO LTDA</t>
+  </si>
+  <si>
+    <t>50860498000130</t>
+  </si>
+  <si>
+    <t>VITER COMERCIO DE ROUPAS E ACESSORIOS LTDA</t>
+  </si>
+  <si>
+    <t>65534930000170</t>
+  </si>
+  <si>
+    <t>W D DE OLIVEIRA PNEUMATICOS</t>
+  </si>
+  <si>
+    <t>Ricardo Cirino Mendes Caetano</t>
+  </si>
+  <si>
+    <t>54777202000173</t>
+  </si>
+  <si>
+    <t>PESSOLO COMERCIO DE ALIMENTOS RP LTDA</t>
+  </si>
+  <si>
+    <t>46984949000174</t>
+  </si>
+  <si>
+    <t>TRANS HONORIO TRANSPORTES COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>53556977000156</t>
+  </si>
+  <si>
+    <t>PRONTIDAO SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>65021401000173</t>
+  </si>
+  <si>
+    <t>LEBRAO SERVICOS AGROPECUARIOS LTDA</t>
+  </si>
+  <si>
+    <t>27312366000152</t>
+  </si>
+  <si>
+    <t>CANAA TRANSPORTADORA LTDA</t>
+  </si>
+  <si>
+    <t>64409324000160</t>
+  </si>
+  <si>
+    <t>PIGAN ESPETARIA LTDA</t>
+  </si>
+  <si>
+    <t>64890842000149</t>
+  </si>
+  <si>
+    <t>LILIAN MARIA PLACIDO</t>
+  </si>
+  <si>
+    <t>12367250000143</t>
+  </si>
+  <si>
+    <t>LCS - COMERCIO VAREJISTA DE ALIMENTOS E PRODUTOS EM GERAL LTDA</t>
+  </si>
+  <si>
+    <t>52757682000185</t>
+  </si>
+  <si>
+    <t>MBS AZULEJISTA E REFORMAS LTDA</t>
+  </si>
+  <si>
+    <t>31942785000145</t>
+  </si>
+  <si>
+    <t>STUDIO ANDERSON SILVA BARBERSHOP LTDA</t>
+  </si>
+  <si>
+    <t>20880272000130</t>
+  </si>
+  <si>
+    <t>MY LOVE COLLECTION LTDA</t>
+  </si>
+  <si>
+    <t>27594747000171</t>
+  </si>
+  <si>
+    <t>J MEDEIROS SERVICOS DE CONSULTORIA LTDA</t>
+  </si>
+  <si>
+    <t>21018789000188</t>
+  </si>
+  <si>
+    <t>EDSON GONCALVES BATISTA LTDA</t>
+  </si>
+  <si>
+    <t>42744626000152</t>
+  </si>
+  <si>
+    <t>MARMORARIA CM LTDA</t>
+  </si>
+  <si>
+    <t>62631349000189</t>
+  </si>
+  <si>
+    <t>BRUMAQ SERVICOS E TERRAPLENAGEM LTDA</t>
+  </si>
+  <si>
+    <t>45136743000121</t>
+  </si>
+  <si>
+    <t>HALICSON ALVES LEITE</t>
+  </si>
+  <si>
+    <t>44564084000161</t>
+  </si>
+  <si>
+    <t>START MANUTENCAO E INSTALACAO ELETRICAS LTDA</t>
+  </si>
+  <si>
+    <t>41566690000128</t>
+  </si>
+  <si>
+    <t>ADQUIRA JA - CELULAR E ACESSORIOS LTDA</t>
+  </si>
+  <si>
+    <t>63437829000176</t>
+  </si>
+  <si>
+    <t>MERCADINHO RJR LTDA</t>
+  </si>
+  <si>
+    <t>04533065000153</t>
+  </si>
+  <si>
+    <t>BAR E LANCHES JAQUELINE E GUILHERME LTDA</t>
+  </si>
+  <si>
+    <t>61989354000103</t>
+  </si>
+  <si>
+    <t>DROGARIA DOM PEDRO LTDA</t>
+  </si>
+  <si>
+    <t>61487877000143</t>
+  </si>
+  <si>
+    <t>QUITANDA PH LTDA</t>
+  </si>
+  <si>
+    <t>14031630000138</t>
+  </si>
+  <si>
+    <t>ASSISTENCIA TECNICA MELO LTDA</t>
+  </si>
+  <si>
+    <t>63191248000105</t>
+  </si>
+  <si>
+    <t>SALDAO IMPERIO LTDA</t>
+  </si>
+  <si>
+    <t>48005810000167</t>
+  </si>
+  <si>
+    <t>W.S ROBOTICA LTDA</t>
+  </si>
+  <si>
+    <t>49942305000101</t>
+  </si>
+  <si>
+    <t>J E R NORIEGA SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>17431903000120</t>
+  </si>
+  <si>
+    <t>AEDO TRANSPORTES ESCOLAR LTDA</t>
+  </si>
+  <si>
+    <t>59346617000106</t>
+  </si>
+  <si>
+    <t>RGLB REPRESENTACOES LTDA</t>
+  </si>
+  <si>
+    <t>45094150000140</t>
+  </si>
+  <si>
+    <t>AGS ELETRICA E SISTEMA DE FOTOVOLTAICO LTDA</t>
+  </si>
+  <si>
+    <t>42804685000179</t>
+  </si>
+  <si>
+    <t>PORTELA CONSTRUCOES E REFORMAS LTDA</t>
+  </si>
+  <si>
+    <t>61264433000149</t>
+  </si>
+  <si>
+    <t>EFA SERRALHERIA LTDA</t>
+  </si>
+  <si>
+    <t>07975421000187</t>
+  </si>
+  <si>
+    <t>CONSTRUTORA BEIRA RIO E EMPREENDIMENTOS IMOBILIARIOS LTDA</t>
+  </si>
+  <si>
+    <t>42295281000105</t>
+  </si>
+  <si>
+    <t>AMAZON ENVIDRACAMENTO LTDA</t>
+  </si>
+  <si>
+    <t>63829803000173</t>
+  </si>
+  <si>
+    <t>FERNANDES LABORATORIO DE PROTESE DENTARIA LTDA</t>
+  </si>
+  <si>
+    <t>47158862000100</t>
+  </si>
+  <si>
+    <t>MENEZES JUNIOR COMERCIO LTDA.</t>
+  </si>
+  <si>
+    <t>10403218000140</t>
+  </si>
+  <si>
+    <t>AUTO MECANICA NASCIMENTO LTDA</t>
+  </si>
+  <si>
+    <t>57825996000191</t>
+  </si>
+  <si>
+    <t>COFFEE BEER BAR PETISCARIA CHURRASCARIA LTDA</t>
+  </si>
+  <si>
+    <t>51336411000193</t>
+  </si>
+  <si>
+    <t>FORTZ SOLUCOES ELETRICAS LTDA</t>
+  </si>
+  <si>
+    <t>17950614000137</t>
+  </si>
+  <si>
+    <t>CLAUDINEI BRAZ DA SILVA LTDA</t>
+  </si>
+  <si>
+    <t>58655619000114</t>
+  </si>
+  <si>
+    <t>MARCELO HENRIQUE LORENCINI</t>
+  </si>
+  <si>
+    <t>59889970000132</t>
+  </si>
+  <si>
+    <t>YARUKO PASTEIS LTDA</t>
+  </si>
+  <si>
+    <t>64738666000124</t>
+  </si>
+  <si>
+    <t>KK TURISMO</t>
+  </si>
+  <si>
+    <t>65203837000183</t>
+  </si>
+  <si>
+    <t>LUCELHA FERNANDES DE LIMA</t>
+  </si>
+  <si>
+    <t>36076132000144</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA WOLVERINE</t>
+  </si>
+  <si>
+    <t>61899900000107</t>
+  </si>
+  <si>
+    <t>RAIMUNDO NONATO DA SILVA JUNIOR</t>
+  </si>
+  <si>
+    <t>64504119000184</t>
+  </si>
+  <si>
+    <t>ADSON LUIZ CHRISTO</t>
+  </si>
+  <si>
+    <t>64900197000106</t>
+  </si>
+  <si>
+    <t>CRISNEY MARCIAO BELO</t>
+  </si>
+  <si>
+    <t>37170086000100</t>
+  </si>
+  <si>
+    <t>DYENER DOUGLAS DE SOUSA DIAS</t>
+  </si>
+  <si>
+    <t>01997280000117</t>
+  </si>
+  <si>
+    <t>M.D ASSESSORIA CONTABIL LTDA</t>
+  </si>
+  <si>
+    <t>08639639000123</t>
+  </si>
+  <si>
+    <t>V. A. PECAS E ACESSORIOS PARA MOTOCICLETAS LTDA</t>
+  </si>
+  <si>
+    <t>12076014000178</t>
+  </si>
+  <si>
+    <t>S L EMPREENDIMENTOS COMERCIAIS LTDA</t>
+  </si>
+  <si>
+    <t>12625515000166</t>
+  </si>
+  <si>
+    <t>PADARIA QDELICIA LTDA</t>
+  </si>
+  <si>
+    <t>14828471000105</t>
+  </si>
+  <si>
+    <t>J R SERVICOS DE CONSTRUCAO CIVIL LTDA</t>
+  </si>
+  <si>
+    <t>14185442000164</t>
+  </si>
+  <si>
+    <t>JULIO CESAR PEREIRA DA SILVA TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>24714934000153</t>
+  </si>
+  <si>
+    <t>HERBTON INSTALACOES LTDA</t>
+  </si>
+  <si>
+    <t>39250630000150</t>
+  </si>
+  <si>
+    <t>FORTTE VIDROS E ALUMINIOS LTDA</t>
+  </si>
+  <si>
+    <t>34864472000104</t>
+  </si>
+  <si>
+    <t>MG CONSTRUCOES, ELETRICA E HIDRAULICA LTDA</t>
+  </si>
+  <si>
+    <t>03968292000149</t>
+  </si>
+  <si>
+    <t>SOUZA &amp; FILHOS CARGAS AEREAS LTDA</t>
+  </si>
+  <si>
+    <t>34286471000120</t>
+  </si>
+  <si>
+    <t>POTENCIA SOLAR LTDA</t>
+  </si>
+  <si>
+    <t>Hellen Geovana Silva Anuncicao</t>
+  </si>
+  <si>
+    <t>41506049000106</t>
+  </si>
+  <si>
+    <t>ELIVAL BENTO PEREIRA</t>
+  </si>
+  <si>
+    <t>49046815000109</t>
+  </si>
+  <si>
+    <t>PRIMICIAS CONSTRUTORA LTDA</t>
+  </si>
+  <si>
+    <t>59411503000100</t>
+  </si>
+  <si>
+    <t>I P CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>59837741000174</t>
+  </si>
+  <si>
+    <t>FACILITYS D DOOR CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>62433972000127</t>
+  </si>
+  <si>
+    <t>SUPERMERCADOS BIGBOOM 2 LTDA</t>
+  </si>
+  <si>
+    <t>62809883000132</t>
+  </si>
+  <si>
+    <t>LUCIANO RIBEIRO LTDA</t>
+  </si>
+  <si>
+    <t>04120589000112</t>
+  </si>
+  <si>
+    <t>NUTRIR ANIMAIS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>14170769000162</t>
+  </si>
+  <si>
+    <t>R R FRANGOS LTDA</t>
+  </si>
+  <si>
+    <t>11849868000187</t>
+  </si>
+  <si>
+    <t>HINF-GRAF COMERCIO DE INFORMATICA E GRAFICA LTDA</t>
+  </si>
+  <si>
+    <t>62826132000124</t>
+  </si>
+  <si>
+    <t>COMPLEXO EXPRESS MAUA CAR SERVICE  LTDA</t>
+  </si>
+  <si>
+    <t>22004731000148</t>
+  </si>
+  <si>
+    <t>DICK RONNIE FERNANDES LTDA</t>
+  </si>
+  <si>
+    <t>52490945000132</t>
+  </si>
+  <si>
+    <t>EMPORIO E DISTRIBUIDORA BOI DE OURO LTDA</t>
+  </si>
+  <si>
+    <t>LETICIA VIVIANE CARVALHO DA PENA</t>
+  </si>
+  <si>
+    <t>62921625000143</t>
+  </si>
+  <si>
+    <t>CONFECCOES JULIANA VIEIRA DOS SANTOS LOBO LTDA</t>
+  </si>
+  <si>
+    <t>44954597000189</t>
+  </si>
+  <si>
+    <t>F SMART HOME LTDA</t>
   </si>
 </sst>
 </file>
@@ -3831,7 +4434,58 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4161,7 +4815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:I598"/>
+  <dimension ref="A1:I698"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -4243,7 +4897,7 @@
         <v>1063</v>
       </c>
       <c r="E3" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -4301,7 +4955,7 @@
         <v>1063</v>
       </c>
       <c r="E5" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -4330,7 +4984,7 @@
         <v>1063</v>
       </c>
       <c r="E6" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -4359,7 +5013,7 @@
         <v>1063</v>
       </c>
       <c r="E7" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -4417,7 +5071,7 @@
         <v>1063</v>
       </c>
       <c r="E9" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -4443,7 +5097,7 @@
         <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E10" t="s">
         <v>1062</v>
@@ -4472,10 +5126,10 @@
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E11" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F11" t="s">
         <v>65</v>
@@ -4530,10 +5184,10 @@
         <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E13" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F13" t="s">
         <v>30</v>
@@ -4559,7 +5213,7 @@
         <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F14" t="s">
         <v>45</v>
@@ -4585,7 +5239,7 @@
         <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F15" t="s">
         <v>45</v>
@@ -4672,7 +5326,7 @@
         <v>1063</v>
       </c>
       <c r="E18" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -4701,7 +5355,7 @@
         <v>1063</v>
       </c>
       <c r="E19" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
@@ -4756,7 +5410,7 @@
         <v>118</v>
       </c>
       <c r="D21" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F21" t="s">
         <v>119</v>
@@ -4785,7 +5439,7 @@
         <v>1063</v>
       </c>
       <c r="E22" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
@@ -4814,7 +5468,7 @@
         <v>1063</v>
       </c>
       <c r="E23" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
@@ -4840,7 +5494,7 @@
         <v>125</v>
       </c>
       <c r="D24" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E24" t="s">
         <v>1062</v>
@@ -4872,7 +5526,7 @@
         <v>1063</v>
       </c>
       <c r="E25" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F25" t="s">
         <v>9</v>
@@ -4898,7 +5552,7 @@
         <v>129</v>
       </c>
       <c r="D26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F26" t="s">
         <v>15</v>
@@ -4924,10 +5578,10 @@
         <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E27" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F27" t="s">
         <v>65</v>
@@ -4956,7 +5610,7 @@
         <v>1063</v>
       </c>
       <c r="E28" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F28" t="s">
         <v>11</v>
@@ -4982,7 +5636,7 @@
         <v>135</v>
       </c>
       <c r="D29" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F29" t="s">
         <v>119</v>
@@ -5040,7 +5694,7 @@
         <v>1063</v>
       </c>
       <c r="E31" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -5066,10 +5720,10 @@
         <v>141</v>
       </c>
       <c r="D32" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E32" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F32" t="s">
         <v>20</v>
@@ -5095,10 +5749,10 @@
         <v>143</v>
       </c>
       <c r="D33" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E33" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F33" t="s">
         <v>65</v>
@@ -5153,10 +5807,10 @@
         <v>147</v>
       </c>
       <c r="D35" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E35" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F35" t="s">
         <v>20</v>
@@ -5182,10 +5836,10 @@
         <v>149</v>
       </c>
       <c r="D36" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E36" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F36" t="s">
         <v>30</v>
@@ -5243,7 +5897,7 @@
         <v>1063</v>
       </c>
       <c r="E38" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F38" t="s">
         <v>9</v>
@@ -5269,10 +5923,10 @@
         <v>155</v>
       </c>
       <c r="D39" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E39" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F39" t="s">
         <v>65</v>
@@ -5298,7 +5952,7 @@
         <v>157</v>
       </c>
       <c r="D40" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F40" t="s">
         <v>51</v>
@@ -5324,7 +5978,7 @@
         <v>159</v>
       </c>
       <c r="D41" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E41" t="s">
         <v>1062</v>
@@ -5353,7 +6007,7 @@
         <v>161</v>
       </c>
       <c r="D42" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E42" t="s">
         <v>1062</v>
@@ -5472,7 +6126,7 @@
         <v>1063</v>
       </c>
       <c r="E46" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F46" t="s">
         <v>11</v>
@@ -5498,10 +6152,10 @@
         <v>171</v>
       </c>
       <c r="D47" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E47" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F47" t="s">
         <v>65</v>
@@ -5530,7 +6184,7 @@
         <v>1063</v>
       </c>
       <c r="E48" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F48" t="s">
         <v>58</v>
@@ -5556,7 +6210,7 @@
         <v>175</v>
       </c>
       <c r="D49" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F49" t="s">
         <v>15</v>
@@ -5582,10 +6236,10 @@
         <v>177</v>
       </c>
       <c r="D50" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E50" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F50" t="s">
         <v>65</v>
@@ -5614,7 +6268,7 @@
         <v>1063</v>
       </c>
       <c r="E51" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F51" t="s">
         <v>12</v>
@@ -5643,7 +6297,7 @@
         <v>1063</v>
       </c>
       <c r="E52" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F52" t="s">
         <v>11</v>
@@ -5669,7 +6323,7 @@
         <v>183</v>
       </c>
       <c r="D53" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F53" t="s">
         <v>39</v>
@@ -5727,7 +6381,7 @@
         <v>1063</v>
       </c>
       <c r="E55" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -5753,7 +6407,7 @@
         <v>189</v>
       </c>
       <c r="D56" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F56" t="s">
         <v>39</v>
@@ -5782,7 +6436,7 @@
         <v>1063</v>
       </c>
       <c r="E57" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -5808,7 +6462,7 @@
         <v>193</v>
       </c>
       <c r="D58" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F58" t="s">
         <v>39</v>
@@ -5834,7 +6488,7 @@
         <v>195</v>
       </c>
       <c r="D59" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F59" t="s">
         <v>39</v>
@@ -5860,7 +6514,7 @@
         <v>197</v>
       </c>
       <c r="D60" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E60" t="s">
         <v>1062</v>
@@ -5918,7 +6572,7 @@
         <v>201</v>
       </c>
       <c r="D62" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F62" t="s">
         <v>39</v>
@@ -5944,10 +6598,10 @@
         <v>203</v>
       </c>
       <c r="D63" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E63" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F63" t="s">
         <v>30</v>
@@ -5973,7 +6627,7 @@
         <v>205</v>
       </c>
       <c r="D64" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F64" t="s">
         <v>39</v>
@@ -5999,7 +6653,7 @@
         <v>206</v>
       </c>
       <c r="D65" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E65" t="s">
         <v>1062</v>
@@ -6028,7 +6682,7 @@
         <v>70</v>
       </c>
       <c r="D66" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E66" t="s">
         <v>1062</v>
@@ -6060,7 +6714,7 @@
         <v>1063</v>
       </c>
       <c r="E67" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F67" t="s">
         <v>11</v>
@@ -6086,7 +6740,7 @@
         <v>210</v>
       </c>
       <c r="D68" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E68" t="s">
         <v>1062</v>
@@ -6115,7 +6769,7 @@
         <v>212</v>
       </c>
       <c r="D69" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F69" t="s">
         <v>15</v>
@@ -6170,10 +6824,10 @@
         <v>216</v>
       </c>
       <c r="D71" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E71" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F71" t="s">
         <v>30</v>
@@ -6202,7 +6856,7 @@
         <v>1063</v>
       </c>
       <c r="E72" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -6231,7 +6885,7 @@
         <v>1063</v>
       </c>
       <c r="E73" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F73" t="s">
         <v>11</v>
@@ -6257,7 +6911,7 @@
         <v>222</v>
       </c>
       <c r="D74" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F74" t="s">
         <v>45</v>
@@ -6283,10 +6937,10 @@
         <v>224</v>
       </c>
       <c r="D75" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E75" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F75" t="s">
         <v>20</v>
@@ -6312,7 +6966,7 @@
         <v>226</v>
       </c>
       <c r="D76" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E76" t="s">
         <v>1062</v>
@@ -6341,7 +6995,7 @@
         <v>228</v>
       </c>
       <c r="D77" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E77" t="s">
         <v>1062</v>
@@ -6399,10 +7053,10 @@
         <v>232</v>
       </c>
       <c r="D79" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E79" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F79" t="s">
         <v>65</v>
@@ -6457,7 +7111,7 @@
         <v>68</v>
       </c>
       <c r="D81" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E81" t="s">
         <v>1062</v>
@@ -6515,7 +7169,7 @@
         <v>238</v>
       </c>
       <c r="D83" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F83" t="s">
         <v>33</v>
@@ -6544,7 +7198,7 @@
         <v>1063</v>
       </c>
       <c r="E84" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F84" t="s">
         <v>58</v>
@@ -6631,7 +7285,7 @@
         <v>1063</v>
       </c>
       <c r="E87" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F87" t="s">
         <v>58</v>
@@ -6657,10 +7311,10 @@
         <v>248</v>
       </c>
       <c r="D88" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E88" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F88" t="s">
         <v>65</v>
@@ -6689,7 +7343,7 @@
         <v>1063</v>
       </c>
       <c r="E89" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F89" t="s">
         <v>9</v>
@@ -6718,7 +7372,7 @@
         <v>1063</v>
       </c>
       <c r="E90" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F90" t="s">
         <v>12</v>
@@ -6744,7 +7398,7 @@
         <v>73</v>
       </c>
       <c r="D91" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E91" t="s">
         <v>1062</v>
@@ -6802,7 +7456,7 @@
         <v>256</v>
       </c>
       <c r="D93" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E93" t="s">
         <v>1062</v>
@@ -6834,7 +7488,7 @@
         <v>1063</v>
       </c>
       <c r="E94" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F94" t="s">
         <v>58</v>
@@ -6860,10 +7514,10 @@
         <v>260</v>
       </c>
       <c r="D95" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E95" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F95" t="s">
         <v>30</v>
@@ -6892,7 +7546,7 @@
         <v>1063</v>
       </c>
       <c r="E96" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F96" t="s">
         <v>14</v>
@@ -6921,7 +7575,7 @@
         <v>1063</v>
       </c>
       <c r="E97" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F97" t="s">
         <v>11</v>
@@ -6976,9 +7630,6 @@
         <v>268</v>
       </c>
       <c r="D99" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E99" t="s">
         <v>1064</v>
       </c>
       <c r="F99" t="s">
@@ -7008,7 +7659,7 @@
         <v>1063</v>
       </c>
       <c r="E100" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F100" t="s">
         <v>58</v>
@@ -7037,7 +7688,7 @@
         <v>1063</v>
       </c>
       <c r="E101" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -7066,7 +7717,7 @@
         <v>1063</v>
       </c>
       <c r="E102" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F102" t="s">
         <v>11</v>
@@ -7095,7 +7746,7 @@
         <v>1063</v>
       </c>
       <c r="E103" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F103" t="s">
         <v>48</v>
@@ -7121,7 +7772,7 @@
         <v>1063</v>
       </c>
       <c r="E104" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -7147,10 +7798,10 @@
         <v>278</v>
       </c>
       <c r="D105" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E105" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F105" t="s">
         <v>20</v>
@@ -7176,10 +7827,10 @@
         <v>280</v>
       </c>
       <c r="D106" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E106" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F106" t="s">
         <v>30</v>
@@ -7205,7 +7856,7 @@
         <v>282</v>
       </c>
       <c r="D107" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E107" t="s">
         <v>1062</v>
@@ -7266,7 +7917,7 @@
         <v>1063</v>
       </c>
       <c r="E109" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -7379,7 +8030,7 @@
         <v>294</v>
       </c>
       <c r="D113" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E113" t="s">
         <v>1062</v>
@@ -7408,7 +8059,7 @@
         <v>296</v>
       </c>
       <c r="D114" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E114" t="s">
         <v>1062</v>
@@ -7437,7 +8088,7 @@
         <v>298</v>
       </c>
       <c r="D115" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F115" t="s">
         <v>33</v>
@@ -7492,7 +8143,7 @@
         <v>302</v>
       </c>
       <c r="D117" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F117" t="s">
         <v>33</v>
@@ -7579,7 +8230,7 @@
         <v>1063</v>
       </c>
       <c r="E120" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F120" t="s">
         <v>58</v>
@@ -7605,7 +8256,7 @@
         <v>310</v>
       </c>
       <c r="D121" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F121" t="s">
         <v>33</v>
@@ -7631,7 +8282,7 @@
         <v>312</v>
       </c>
       <c r="D122" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F122" t="s">
         <v>39</v>
@@ -7657,9 +8308,6 @@
         <v>314</v>
       </c>
       <c r="D123" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E123" t="s">
         <v>1064</v>
       </c>
       <c r="F123" t="s">
@@ -7686,7 +8334,7 @@
         <v>316</v>
       </c>
       <c r="D124" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F124" t="s">
         <v>39</v>
@@ -7712,10 +8360,10 @@
         <v>318</v>
       </c>
       <c r="D125" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E125" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F125" t="s">
         <v>65</v>
@@ -7770,7 +8418,7 @@
         <v>322</v>
       </c>
       <c r="D127" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E127" t="s">
         <v>1062</v>
@@ -7857,7 +8505,7 @@
         <v>328</v>
       </c>
       <c r="D130" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F130" t="s">
         <v>33</v>
@@ -7886,7 +8534,7 @@
         <v>1063</v>
       </c>
       <c r="E131" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F131" t="s">
         <v>11</v>
@@ -7912,7 +8560,7 @@
         <v>332</v>
       </c>
       <c r="D132" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E132" t="s">
         <v>1062</v>
@@ -8002,7 +8650,7 @@
         <v>1063</v>
       </c>
       <c r="E135" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F135" t="s">
         <v>9</v>
@@ -8031,7 +8679,7 @@
         <v>1063</v>
       </c>
       <c r="E136" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F136" t="s">
         <v>11</v>
@@ -8057,7 +8705,7 @@
         <v>342</v>
       </c>
       <c r="D137" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F137" t="s">
         <v>45</v>
@@ -8086,7 +8734,7 @@
         <v>1063</v>
       </c>
       <c r="E138" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F138" t="s">
         <v>9</v>
@@ -8141,10 +8789,10 @@
         <v>347</v>
       </c>
       <c r="D140" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E140" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F140" t="s">
         <v>65</v>
@@ -8199,10 +8847,10 @@
         <v>351</v>
       </c>
       <c r="D142" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E142" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F142" t="s">
         <v>30</v>
@@ -8228,7 +8876,7 @@
         <v>353</v>
       </c>
       <c r="D143" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F143" t="s">
         <v>33</v>
@@ -8254,10 +8902,10 @@
         <v>355</v>
       </c>
       <c r="D144" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E144" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F144" t="s">
         <v>30</v>
@@ -8315,7 +8963,7 @@
         <v>1063</v>
       </c>
       <c r="E146" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F146" t="s">
         <v>11</v>
@@ -8344,7 +8992,7 @@
         <v>1063</v>
       </c>
       <c r="E147" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F147" t="s">
         <v>11</v>
@@ -8370,10 +9018,10 @@
         <v>363</v>
       </c>
       <c r="D148" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E148" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F148" t="s">
         <v>20</v>
@@ -8402,7 +9050,7 @@
         <v>1063</v>
       </c>
       <c r="E149" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F149" t="s">
         <v>9</v>
@@ -8460,7 +9108,7 @@
         <v>1063</v>
       </c>
       <c r="E151" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
@@ -8518,7 +9166,7 @@
         <v>1063</v>
       </c>
       <c r="E153" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F153" t="s">
         <v>9</v>
@@ -8544,7 +9192,7 @@
         <v>371</v>
       </c>
       <c r="D154" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F154" t="s">
         <v>33</v>
@@ -8570,9 +9218,6 @@
         <v>373</v>
       </c>
       <c r="D155" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E155" t="s">
         <v>1064</v>
       </c>
       <c r="F155" t="s">
@@ -8599,10 +9244,10 @@
         <v>375</v>
       </c>
       <c r="D156" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E156" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F156" t="s">
         <v>20</v>
@@ -8628,7 +9273,7 @@
         <v>377</v>
       </c>
       <c r="D157" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E157" t="s">
         <v>1062</v>
@@ -8657,7 +9302,7 @@
         <v>379</v>
       </c>
       <c r="D158" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E158" t="s">
         <v>1062</v>
@@ -8686,7 +9331,7 @@
         <v>381</v>
       </c>
       <c r="D159" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E159" t="s">
         <v>1062</v>
@@ -8715,10 +9360,10 @@
         <v>385</v>
       </c>
       <c r="D160" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E160" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F160" t="s">
         <v>30</v>
@@ -8773,10 +9418,10 @@
         <v>389</v>
       </c>
       <c r="D162" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E162" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F162" t="s">
         <v>30</v>
@@ -8802,7 +9447,7 @@
         <v>391</v>
       </c>
       <c r="D163" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E163" t="s">
         <v>1062</v>
@@ -8831,7 +9476,7 @@
         <v>393</v>
       </c>
       <c r="D164" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F164" t="s">
         <v>45</v>
@@ -8857,7 +9502,7 @@
         <v>395</v>
       </c>
       <c r="D165" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E165" t="s">
         <v>1062</v>
@@ -8889,7 +9534,7 @@
         <v>1063</v>
       </c>
       <c r="E166" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F166" t="s">
         <v>48</v>
@@ -8944,10 +9589,10 @@
         <v>399</v>
       </c>
       <c r="D168" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E168" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F168" t="s">
         <v>20</v>
@@ -8973,7 +9618,7 @@
         <v>401</v>
       </c>
       <c r="D169" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F169" t="s">
         <v>33</v>
@@ -9057,7 +9702,7 @@
         <v>407</v>
       </c>
       <c r="D172" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E172" t="s">
         <v>1062</v>
@@ -9086,10 +9731,10 @@
         <v>409</v>
       </c>
       <c r="D173" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E173" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F173" t="s">
         <v>20</v>
@@ -9115,10 +9760,10 @@
         <v>411</v>
       </c>
       <c r="D174" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E174" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F174" t="s">
         <v>65</v>
@@ -9173,7 +9818,7 @@
         <v>415</v>
       </c>
       <c r="D176" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E176" t="s">
         <v>1062</v>
@@ -9286,10 +9931,10 @@
         <v>423</v>
       </c>
       <c r="D180" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E180" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F180" t="s">
         <v>30</v>
@@ -9315,7 +9960,7 @@
         <v>425</v>
       </c>
       <c r="D181" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F181" t="s">
         <v>39</v>
@@ -9399,10 +10044,10 @@
         <v>431</v>
       </c>
       <c r="D184" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E184" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F184" t="s">
         <v>65</v>
@@ -9457,7 +10102,7 @@
         <v>435</v>
       </c>
       <c r="D186" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E186" t="s">
         <v>1062</v>
@@ -9483,10 +10128,10 @@
         <v>437</v>
       </c>
       <c r="D187" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E187" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F187" t="s">
         <v>65</v>
@@ -9515,7 +10160,7 @@
         <v>1063</v>
       </c>
       <c r="E188" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F188" t="s">
         <v>9</v>
@@ -9602,7 +10247,7 @@
         <v>1063</v>
       </c>
       <c r="E191" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F191" t="s">
         <v>11</v>
@@ -9660,7 +10305,7 @@
         <v>1063</v>
       </c>
       <c r="E193" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -9686,10 +10331,10 @@
         <v>451</v>
       </c>
       <c r="D194" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E194" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F194" t="s">
         <v>20</v>
@@ -9747,7 +10392,7 @@
         <v>1063</v>
       </c>
       <c r="E196" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F196" t="s">
         <v>11</v>
@@ -9773,10 +10418,10 @@
         <v>457</v>
       </c>
       <c r="D197" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E197" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F197" t="s">
         <v>65</v>
@@ -9805,7 +10450,7 @@
         <v>1063</v>
       </c>
       <c r="E198" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F198" t="s">
         <v>11</v>
@@ -9892,7 +10537,7 @@
         <v>1063</v>
       </c>
       <c r="E201" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F201" t="s">
         <v>9</v>
@@ -9950,7 +10595,7 @@
         <v>1063</v>
       </c>
       <c r="E203" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F203" t="s">
         <v>11</v>
@@ -9959,7 +10604,7 @@
         <v>8</v>
       </c>
       <c r="H203" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I203">
         <v>0</v>
@@ -10008,7 +10653,7 @@
         <v>1063</v>
       </c>
       <c r="E205" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F205" t="s">
         <v>9</v>
@@ -10063,7 +10708,7 @@
         <v>475</v>
       </c>
       <c r="D207" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F207" t="s">
         <v>45</v>
@@ -10118,7 +10763,7 @@
         <v>479</v>
       </c>
       <c r="D209" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E209" t="s">
         <v>1062</v>
@@ -10147,7 +10792,7 @@
         <v>481</v>
       </c>
       <c r="D210" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E210" t="s">
         <v>1062</v>
@@ -10176,10 +10821,10 @@
         <v>483</v>
       </c>
       <c r="D211" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E211" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F211" t="s">
         <v>20</v>
@@ -10208,7 +10853,7 @@
         <v>1063</v>
       </c>
       <c r="E212" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -10234,7 +10879,7 @@
         <v>487</v>
       </c>
       <c r="D213" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E213" t="s">
         <v>1062</v>
@@ -10295,7 +10940,7 @@
         <v>1063</v>
       </c>
       <c r="E215" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -10321,7 +10966,7 @@
         <v>493</v>
       </c>
       <c r="D216" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E216" t="s">
         <v>1062</v>
@@ -10379,7 +11024,7 @@
         <v>497</v>
       </c>
       <c r="D218" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E218" t="s">
         <v>1062</v>
@@ -10411,7 +11056,7 @@
         <v>1063</v>
       </c>
       <c r="E219" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F219" t="s">
         <v>58</v>
@@ -10437,7 +11082,7 @@
         <v>53</v>
       </c>
       <c r="D220" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E220" t="s">
         <v>1062</v>
@@ -10495,10 +11140,10 @@
         <v>503</v>
       </c>
       <c r="D222" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E222" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F222" t="s">
         <v>30</v>
@@ -10524,10 +11169,10 @@
         <v>505</v>
       </c>
       <c r="D223" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E223" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F223" t="s">
         <v>65</v>
@@ -10553,7 +11198,7 @@
         <v>507</v>
       </c>
       <c r="D224" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E224" t="s">
         <v>1062</v>
@@ -10582,7 +11227,7 @@
         <v>509</v>
       </c>
       <c r="D225" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F225" t="s">
         <v>39</v>
@@ -10608,7 +11253,7 @@
         <v>510</v>
       </c>
       <c r="D226" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F226" t="s">
         <v>39</v>
@@ -10634,7 +11279,7 @@
         <v>511</v>
       </c>
       <c r="D227" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F227" t="s">
         <v>39</v>
@@ -10660,7 +11305,7 @@
         <v>513</v>
       </c>
       <c r="D228" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F228" t="s">
         <v>39</v>
@@ -10686,7 +11331,7 @@
         <v>80</v>
       </c>
       <c r="D229" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F229" t="s">
         <v>39</v>
@@ -10712,7 +11357,7 @@
         <v>516</v>
       </c>
       <c r="D230" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E230" t="s">
         <v>1062</v>
@@ -10741,7 +11386,7 @@
         <v>518</v>
       </c>
       <c r="D231" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F231" t="s">
         <v>39</v>
@@ -10799,7 +11444,7 @@
         <v>1063</v>
       </c>
       <c r="E233" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F233" t="s">
         <v>58</v>
@@ -10825,7 +11470,7 @@
         <v>524</v>
       </c>
       <c r="D234" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F234" t="s">
         <v>39</v>
@@ -10854,7 +11499,7 @@
         <v>1063</v>
       </c>
       <c r="E235" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F235" t="s">
         <v>11</v>
@@ -10880,7 +11525,7 @@
         <v>528</v>
       </c>
       <c r="D236" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F236" t="s">
         <v>39</v>
@@ -10906,7 +11551,7 @@
         <v>530</v>
       </c>
       <c r="D237" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F237" t="s">
         <v>39</v>
@@ -10932,7 +11577,7 @@
         <v>532</v>
       </c>
       <c r="D238" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F238" t="s">
         <v>39</v>
@@ -10958,7 +11603,7 @@
         <v>534</v>
       </c>
       <c r="D239" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F239" t="s">
         <v>39</v>
@@ -10984,7 +11629,7 @@
         <v>536</v>
       </c>
       <c r="D240" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E240" t="s">
         <v>1062</v>
@@ -11013,7 +11658,7 @@
         <v>538</v>
       </c>
       <c r="D241" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E241" t="s">
         <v>1062</v>
@@ -11042,10 +11687,10 @@
         <v>540</v>
       </c>
       <c r="D242" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E242" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F242" t="s">
         <v>30</v>
@@ -11074,7 +11719,7 @@
         <v>1063</v>
       </c>
       <c r="E243" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -11103,7 +11748,7 @@
         <v>1063</v>
       </c>
       <c r="E244" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F244" t="s">
         <v>58</v>
@@ -11129,7 +11774,7 @@
         <v>544</v>
       </c>
       <c r="D245" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E245" t="s">
         <v>1062</v>
@@ -11161,7 +11806,7 @@
         <v>1063</v>
       </c>
       <c r="E246" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F246" t="s">
         <v>9</v>
@@ -11170,10 +11815,10 @@
         <v>10</v>
       </c>
       <c r="H246" t="s">
-        <v>23</v>
-      </c>
-      <c r="I246">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="I246" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
@@ -11274,10 +11919,10 @@
         <v>552</v>
       </c>
       <c r="D250" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E250" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F250" t="s">
         <v>20</v>
@@ -11306,7 +11951,7 @@
         <v>1063</v>
       </c>
       <c r="E251" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F251" t="s">
         <v>11</v>
@@ -11332,7 +11977,7 @@
         <v>556</v>
       </c>
       <c r="D252" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F252" t="s">
         <v>45</v>
@@ -11358,10 +12003,10 @@
         <v>558</v>
       </c>
       <c r="D253" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E253" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F253" t="s">
         <v>65</v>
@@ -11387,7 +12032,7 @@
         <v>560</v>
       </c>
       <c r="D254" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E254" t="s">
         <v>1062</v>
@@ -11445,7 +12090,7 @@
         <v>1063</v>
       </c>
       <c r="E256" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F256" t="s">
         <v>58</v>
@@ -11474,7 +12119,7 @@
         <v>1063</v>
       </c>
       <c r="E257" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F257" t="s">
         <v>11</v>
@@ -11645,10 +12290,10 @@
         <v>578</v>
       </c>
       <c r="D263" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E263" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F263" t="s">
         <v>65</v>
@@ -11706,7 +12351,7 @@
         <v>1063</v>
       </c>
       <c r="E265" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F265" t="s">
         <v>9</v>
@@ -11735,7 +12380,7 @@
         <v>1063</v>
       </c>
       <c r="E266" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F266" t="s">
         <v>48</v>
@@ -11764,7 +12409,7 @@
         <v>1063</v>
       </c>
       <c r="E267" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F267" t="s">
         <v>58</v>
@@ -11790,10 +12435,10 @@
         <v>588</v>
       </c>
       <c r="D268" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E268" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F268" t="s">
         <v>30</v>
@@ -11906,10 +12551,10 @@
         <v>594</v>
       </c>
       <c r="D272" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E272" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F272" t="s">
         <v>20</v>
@@ -11938,7 +12583,7 @@
         <v>1063</v>
       </c>
       <c r="E273" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F273" t="s">
         <v>11</v>
@@ -12022,7 +12667,7 @@
         <v>604</v>
       </c>
       <c r="D276" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F276" t="s">
         <v>45</v>
@@ -12048,7 +12693,7 @@
         <v>606</v>
       </c>
       <c r="D277" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E277" t="s">
         <v>1062</v>
@@ -12109,7 +12754,7 @@
         <v>1063</v>
       </c>
       <c r="E279" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -12135,7 +12780,7 @@
         <v>610</v>
       </c>
       <c r="D280" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E280" t="s">
         <v>1062</v>
@@ -12193,7 +12838,7 @@
         <v>614</v>
       </c>
       <c r="D282" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E282" t="s">
         <v>1062</v>
@@ -12222,7 +12867,7 @@
         <v>616</v>
       </c>
       <c r="D283" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E283" t="s">
         <v>1062</v>
@@ -12280,7 +12925,7 @@
         <v>620</v>
       </c>
       <c r="D285" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E285" t="s">
         <v>1062</v>
@@ -12338,7 +12983,7 @@
         <v>624</v>
       </c>
       <c r="D287" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E287" t="s">
         <v>1062</v>
@@ -12425,7 +13070,7 @@
         <v>630</v>
       </c>
       <c r="D290" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F290" t="s">
         <v>45</v>
@@ -12454,7 +13099,7 @@
         <v>1063</v>
       </c>
       <c r="E291" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F291" t="s">
         <v>11</v>
@@ -12480,10 +13125,10 @@
         <v>634</v>
       </c>
       <c r="D292" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E292" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F292" t="s">
         <v>30</v>
@@ -12512,7 +13157,7 @@
         <v>1063</v>
       </c>
       <c r="E293" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F293" t="s">
         <v>9</v>
@@ -12596,7 +13241,7 @@
         <v>643</v>
       </c>
       <c r="D296" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E296" t="s">
         <v>1062</v>
@@ -12625,10 +13270,10 @@
         <v>645</v>
       </c>
       <c r="D297" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E297" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F297" t="s">
         <v>30</v>
@@ -12686,7 +13331,7 @@
         <v>1063</v>
       </c>
       <c r="E299" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F299" t="s">
         <v>11</v>
@@ -12744,7 +13389,7 @@
         <v>1063</v>
       </c>
       <c r="E301" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F301" t="s">
         <v>11</v>
@@ -12828,7 +13473,7 @@
         <v>659</v>
       </c>
       <c r="D304" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E304" t="s">
         <v>1062</v>
@@ -12857,10 +13502,10 @@
         <v>661</v>
       </c>
       <c r="D305" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E305" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F305" t="s">
         <v>65</v>
@@ -12889,7 +13534,7 @@
         <v>1063</v>
       </c>
       <c r="E306" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F306" t="s">
         <v>9</v>
@@ -12918,7 +13563,7 @@
         <v>1063</v>
       </c>
       <c r="E307" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F307" t="s">
         <v>11</v>
@@ -12947,7 +13592,7 @@
         <v>1063</v>
       </c>
       <c r="E308" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F308" t="s">
         <v>11</v>
@@ -13063,7 +13708,7 @@
         <v>1063</v>
       </c>
       <c r="E312" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F312" t="s">
         <v>11</v>
@@ -13205,10 +13850,10 @@
         <v>685</v>
       </c>
       <c r="D317" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E317" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F317" t="s">
         <v>65</v>
@@ -13266,7 +13911,7 @@
         <v>1063</v>
       </c>
       <c r="E319" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F319" t="s">
         <v>11</v>
@@ -13321,7 +13966,7 @@
         <v>693</v>
       </c>
       <c r="D321" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E321" t="s">
         <v>1062</v>
@@ -13350,7 +13995,7 @@
         <v>695</v>
       </c>
       <c r="D322" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E322" t="s">
         <v>1062</v>
@@ -13362,7 +14007,7 @@
         <v>7</v>
       </c>
       <c r="H322" t="s">
-        <v>699</v>
+        <v>19</v>
       </c>
       <c r="I322">
         <v>0</v>
@@ -13379,10 +14024,10 @@
         <v>697</v>
       </c>
       <c r="D323" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E323" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F323" t="s">
         <v>65</v>
@@ -13408,7 +14053,7 @@
         <v>701</v>
       </c>
       <c r="D324" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F324" t="s">
         <v>39</v>
@@ -13521,7 +14166,7 @@
         <v>709</v>
       </c>
       <c r="D328" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F328" t="s">
         <v>39</v>
@@ -13547,7 +14192,7 @@
         <v>711</v>
       </c>
       <c r="D329" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F329" t="s">
         <v>39</v>
@@ -13573,7 +14218,7 @@
         <v>713</v>
       </c>
       <c r="D330" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F330" t="s">
         <v>39</v>
@@ -13599,7 +14244,7 @@
         <v>715</v>
       </c>
       <c r="D331" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E331" t="s">
         <v>1062</v>
@@ -13628,7 +14273,7 @@
         <v>1063</v>
       </c>
       <c r="E332" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F332" t="s">
         <v>14</v>
@@ -13657,7 +14302,7 @@
         <v>1063</v>
       </c>
       <c r="E333" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F333" t="s">
         <v>11</v>
@@ -13712,10 +14357,10 @@
         <v>723</v>
       </c>
       <c r="D335" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E335" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F335" t="s">
         <v>65</v>
@@ -13741,7 +14386,7 @@
         <v>725</v>
       </c>
       <c r="D336" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E336" t="s">
         <v>1062</v>
@@ -13802,7 +14447,7 @@
         <v>1063</v>
       </c>
       <c r="E338" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F338" t="s">
         <v>9</v>
@@ -13831,7 +14476,7 @@
         <v>1063</v>
       </c>
       <c r="E339" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F339" t="s">
         <v>14</v>
@@ -13860,7 +14505,7 @@
         <v>1063</v>
       </c>
       <c r="E340" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -13915,7 +14560,7 @@
         <v>737</v>
       </c>
       <c r="D342" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E342" t="s">
         <v>1062</v>
@@ -13944,7 +14589,7 @@
         <v>739</v>
       </c>
       <c r="D343" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E343" t="s">
         <v>1062</v>
@@ -14005,7 +14650,7 @@
         <v>1063</v>
       </c>
       <c r="E345" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F345" t="s">
         <v>11</v>
@@ -14089,7 +14734,7 @@
         <v>749</v>
       </c>
       <c r="D348" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E348" t="s">
         <v>1062</v>
@@ -14118,10 +14763,10 @@
         <v>751</v>
       </c>
       <c r="D349" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E349" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F349" t="s">
         <v>65</v>
@@ -14176,7 +14821,7 @@
         <v>755</v>
       </c>
       <c r="D351" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E351" t="s">
         <v>1062</v>
@@ -14208,7 +14853,7 @@
         <v>1063</v>
       </c>
       <c r="E352" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F352" t="s">
         <v>14</v>
@@ -14266,7 +14911,7 @@
         <v>1063</v>
       </c>
       <c r="E354" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F354" t="s">
         <v>14</v>
@@ -14324,7 +14969,7 @@
         <v>1063</v>
       </c>
       <c r="E356" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F356" t="s">
         <v>28</v>
@@ -14350,7 +14995,7 @@
         <v>767</v>
       </c>
       <c r="D357" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E357" t="s">
         <v>1062</v>
@@ -14382,7 +15027,7 @@
         <v>1063</v>
       </c>
       <c r="E358" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F358" t="s">
         <v>11</v>
@@ -14408,7 +15053,7 @@
         <v>771</v>
       </c>
       <c r="D359" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E359" t="s">
         <v>1062</v>
@@ -14437,10 +15082,10 @@
         <v>775</v>
       </c>
       <c r="D360" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E360" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F360" t="s">
         <v>65</v>
@@ -14469,7 +15114,7 @@
         <v>1063</v>
       </c>
       <c r="E361" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F361" t="s">
         <v>14</v>
@@ -14495,7 +15140,7 @@
         <v>779</v>
       </c>
       <c r="D362" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E362" t="s">
         <v>1062</v>
@@ -14527,7 +15172,7 @@
         <v>1063</v>
       </c>
       <c r="E363" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F363" t="s">
         <v>12</v>
@@ -14556,7 +15201,7 @@
         <v>1063</v>
       </c>
       <c r="E364" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F364" t="s">
         <v>12</v>
@@ -14582,10 +15227,10 @@
         <v>785</v>
       </c>
       <c r="D365" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E365" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F365" t="s">
         <v>65</v>
@@ -14614,7 +15259,7 @@
         <v>1063</v>
       </c>
       <c r="E366" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F366" t="s">
         <v>14</v>
@@ -14643,7 +15288,7 @@
         <v>1063</v>
       </c>
       <c r="E367" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F367" t="s">
         <v>48</v>
@@ -14701,7 +15346,7 @@
         <v>1063</v>
       </c>
       <c r="E369" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F369" t="s">
         <v>12</v>
@@ -14759,7 +15404,7 @@
         <v>1063</v>
       </c>
       <c r="E371" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F371" t="s">
         <v>11</v>
@@ -14843,10 +15488,10 @@
         <v>803</v>
       </c>
       <c r="D374" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E374" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F374" t="s">
         <v>30</v>
@@ -14872,10 +15517,10 @@
         <v>805</v>
       </c>
       <c r="D375" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E375" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F375" t="s">
         <v>30</v>
@@ -14901,10 +15546,10 @@
         <v>807</v>
       </c>
       <c r="D376" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E376" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F376" t="s">
         <v>20</v>
@@ -14930,7 +15575,7 @@
         <v>809</v>
       </c>
       <c r="D377" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E377" t="s">
         <v>1062</v>
@@ -14962,7 +15607,7 @@
         <v>1063</v>
       </c>
       <c r="E378" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F378" t="s">
         <v>9</v>
@@ -15017,7 +15662,7 @@
         <v>815</v>
       </c>
       <c r="D380" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E380" t="s">
         <v>1062</v>
@@ -15075,10 +15720,10 @@
         <v>819</v>
       </c>
       <c r="D382" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E382" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F382" t="s">
         <v>30</v>
@@ -15165,7 +15810,7 @@
         <v>1063</v>
       </c>
       <c r="E385" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F385" t="s">
         <v>14</v>
@@ -15220,7 +15865,7 @@
         <v>829</v>
       </c>
       <c r="D387" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E387" t="s">
         <v>1062</v>
@@ -15307,7 +15952,7 @@
         <v>835</v>
       </c>
       <c r="D390" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E390" t="s">
         <v>1062</v>
@@ -15368,7 +16013,7 @@
         <v>1063</v>
       </c>
       <c r="E392" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F392" t="s">
         <v>58</v>
@@ -15394,7 +16039,7 @@
         <v>841</v>
       </c>
       <c r="D393" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E393" t="s">
         <v>1062</v>
@@ -15452,10 +16097,10 @@
         <v>845</v>
       </c>
       <c r="D395" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E395" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F395" t="s">
         <v>20</v>
@@ -15484,7 +16129,7 @@
         <v>1063</v>
       </c>
       <c r="E396" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F396" t="s">
         <v>11</v>
@@ -15513,7 +16158,7 @@
         <v>1063</v>
       </c>
       <c r="E397" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F397" t="s">
         <v>28</v>
@@ -15539,10 +16184,10 @@
         <v>851</v>
       </c>
       <c r="D398" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E398" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F398" t="s">
         <v>65</v>
@@ -15597,10 +16242,10 @@
         <v>855</v>
       </c>
       <c r="D400" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E400" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F400" t="s">
         <v>30</v>
@@ -15658,7 +16303,7 @@
         <v>1063</v>
       </c>
       <c r="E402" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F402" t="s">
         <v>58</v>
@@ -15687,7 +16332,7 @@
         <v>1063</v>
       </c>
       <c r="E403" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F403" t="s">
         <v>14</v>
@@ -15713,10 +16358,10 @@
         <v>863</v>
       </c>
       <c r="D404" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E404" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F404" t="s">
         <v>65</v>
@@ -15771,7 +16416,7 @@
         <v>867</v>
       </c>
       <c r="D406" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E406" t="s">
         <v>1062</v>
@@ -15803,7 +16448,7 @@
         <v>1063</v>
       </c>
       <c r="E407" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F407" t="s">
         <v>12</v>
@@ -15829,7 +16474,7 @@
         <v>871</v>
       </c>
       <c r="D408" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E408" t="s">
         <v>1062</v>
@@ -15861,7 +16506,7 @@
         <v>1063</v>
       </c>
       <c r="E409" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F409" t="s">
         <v>11</v>
@@ -15916,10 +16561,10 @@
         <v>877</v>
       </c>
       <c r="D411" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E411" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F411" t="s">
         <v>65</v>
@@ -15977,7 +16622,7 @@
         <v>1063</v>
       </c>
       <c r="E413" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F413" t="s">
         <v>12</v>
@@ -16006,7 +16651,7 @@
         <v>1063</v>
       </c>
       <c r="E414" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F414" t="s">
         <v>14</v>
@@ -16016,9 +16661,6 @@
       </c>
       <c r="H414" t="s">
         <v>23</v>
-      </c>
-      <c r="I414">
-        <v>0</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.25">
@@ -16032,10 +16674,10 @@
         <v>885</v>
       </c>
       <c r="D415" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E415" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F415" t="s">
         <v>30</v>
@@ -16064,7 +16706,7 @@
         <v>1063</v>
       </c>
       <c r="E416" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F416" t="s">
         <v>12</v>
@@ -16090,10 +16732,10 @@
         <v>889</v>
       </c>
       <c r="D417" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E417" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F417" t="s">
         <v>30</v>
@@ -16122,7 +16764,7 @@
         <v>1063</v>
       </c>
       <c r="E418" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F418" t="s">
         <v>14</v>
@@ -16151,7 +16793,7 @@
         <v>1063</v>
       </c>
       <c r="E419" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F419" t="s">
         <v>14</v>
@@ -16177,7 +16819,7 @@
         <v>895</v>
       </c>
       <c r="D420" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E420" t="s">
         <v>1062</v>
@@ -16206,7 +16848,7 @@
         <v>897</v>
       </c>
       <c r="D421" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E421" t="s">
         <v>1062</v>
@@ -16238,7 +16880,7 @@
         <v>1063</v>
       </c>
       <c r="E422" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F422" t="s">
         <v>14</v>
@@ -16264,7 +16906,7 @@
         <v>600</v>
       </c>
       <c r="D423" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E423" t="s">
         <v>1062</v>
@@ -16322,10 +16964,10 @@
         <v>903</v>
       </c>
       <c r="D425" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E425" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F425" t="s">
         <v>65</v>
@@ -16351,10 +16993,10 @@
         <v>905</v>
       </c>
       <c r="D426" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E426" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F426" t="s">
         <v>20</v>
@@ -16383,7 +17025,7 @@
         <v>1063</v>
       </c>
       <c r="E427" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F427" t="s">
         <v>9</v>
@@ -16412,7 +17054,7 @@
         <v>1063</v>
       </c>
       <c r="E428" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F428" t="s">
         <v>14</v>
@@ -16441,7 +17083,7 @@
         <v>1063</v>
       </c>
       <c r="E429" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F429" t="s">
         <v>14</v>
@@ -16554,10 +17196,10 @@
         <v>919</v>
       </c>
       <c r="D433" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E433" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F433" t="s">
         <v>30</v>
@@ -16586,7 +17228,7 @@
         <v>1063</v>
       </c>
       <c r="E434" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F434" t="s">
         <v>58</v>
@@ -16615,7 +17257,7 @@
         <v>1063</v>
       </c>
       <c r="E435" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F435" t="s">
         <v>28</v>
@@ -16644,7 +17286,7 @@
         <v>1063</v>
       </c>
       <c r="E436" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F436" t="s">
         <v>14</v>
@@ -16699,7 +17341,7 @@
         <v>929</v>
       </c>
       <c r="D438" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E438" t="s">
         <v>1062</v>
@@ -16728,7 +17370,7 @@
         <v>931</v>
       </c>
       <c r="D439" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E439" t="s">
         <v>1062</v>
@@ -16760,7 +17402,7 @@
         <v>1063</v>
       </c>
       <c r="E440" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F440" t="s">
         <v>11</v>
@@ -16786,7 +17428,7 @@
         <v>936</v>
       </c>
       <c r="D441" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E441" t="s">
         <v>1062</v>
@@ -16815,7 +17457,7 @@
         <v>938</v>
       </c>
       <c r="D442" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E442" t="s">
         <v>1062</v>
@@ -16847,7 +17489,7 @@
         <v>1063</v>
       </c>
       <c r="E443" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F443" t="s">
         <v>12</v>
@@ -16876,7 +17518,7 @@
         <v>1063</v>
       </c>
       <c r="E444" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F444" t="s">
         <v>11</v>
@@ -16934,7 +17576,7 @@
         <v>1063</v>
       </c>
       <c r="E446" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F446" t="s">
         <v>58</v>
@@ -16960,7 +17602,7 @@
         <v>948</v>
       </c>
       <c r="D447" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E447" t="s">
         <v>1062</v>
@@ -16992,7 +17634,7 @@
         <v>1063</v>
       </c>
       <c r="E448" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F448" t="s">
         <v>11</v>
@@ -17021,7 +17663,7 @@
         <v>1063</v>
       </c>
       <c r="E449" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F449" t="s">
         <v>9</v>
@@ -17050,7 +17692,7 @@
         <v>1063</v>
       </c>
       <c r="E450" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F450" t="s">
         <v>12</v>
@@ -17105,7 +17747,7 @@
         <v>1063</v>
       </c>
       <c r="E452" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F452" t="s">
         <v>12</v>
@@ -17134,7 +17776,7 @@
         <v>1063</v>
       </c>
       <c r="E453" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F453" t="s">
         <v>9</v>
@@ -17163,7 +17805,7 @@
         <v>1063</v>
       </c>
       <c r="E454" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F454" t="s">
         <v>11</v>
@@ -17189,10 +17831,10 @@
         <v>964</v>
       </c>
       <c r="D455" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E455" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F455" t="s">
         <v>20</v>
@@ -17221,7 +17863,7 @@
         <v>1063</v>
       </c>
       <c r="E456" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F456" t="s">
         <v>48</v>
@@ -17250,7 +17892,7 @@
         <v>1063</v>
       </c>
       <c r="E457" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F457" t="s">
         <v>14</v>
@@ -17276,10 +17918,10 @@
         <v>970</v>
       </c>
       <c r="D458" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E458" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F458" t="s">
         <v>20</v>
@@ -17305,10 +17947,10 @@
         <v>972</v>
       </c>
       <c r="D459" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E459" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F459" t="s">
         <v>65</v>
@@ -17337,7 +17979,7 @@
         <v>1063</v>
       </c>
       <c r="E460" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F460" t="s">
         <v>14</v>
@@ -17346,7 +17988,7 @@
         <v>8</v>
       </c>
       <c r="H460" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I460" t="s">
         <v>57</v>
@@ -17363,10 +18005,10 @@
         <v>976</v>
       </c>
       <c r="D461" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E461" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F461" t="s">
         <v>20</v>
@@ -17392,10 +18034,10 @@
         <v>978</v>
       </c>
       <c r="D462" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E462" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F462" t="s">
         <v>30</v>
@@ -17421,7 +18063,7 @@
         <v>980</v>
       </c>
       <c r="D463" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E463" t="s">
         <v>1062</v>
@@ -17450,10 +18092,10 @@
         <v>982</v>
       </c>
       <c r="D464" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E464" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F464" t="s">
         <v>65</v>
@@ -17511,7 +18153,7 @@
         <v>1063</v>
       </c>
       <c r="E466" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F466" t="s">
         <v>58</v>
@@ -17569,7 +18211,7 @@
         <v>1063</v>
       </c>
       <c r="E468" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F468" t="s">
         <v>11</v>
@@ -17627,7 +18269,7 @@
         <v>1063</v>
       </c>
       <c r="E470" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F470" t="s">
         <v>9</v>
@@ -17656,7 +18298,7 @@
         <v>1063</v>
       </c>
       <c r="E471" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F471" t="s">
         <v>11</v>
@@ -17711,10 +18353,10 @@
         <v>1000</v>
       </c>
       <c r="D473" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E473" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F473" t="s">
         <v>65</v>
@@ -17740,10 +18382,10 @@
         <v>1002</v>
       </c>
       <c r="D474" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E474" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F474" t="s">
         <v>30</v>
@@ -17769,7 +18411,7 @@
         <v>1004</v>
       </c>
       <c r="D475" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E475" t="s">
         <v>1062</v>
@@ -17798,7 +18440,7 @@
         <v>1006</v>
       </c>
       <c r="D476" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E476" t="s">
         <v>1062</v>
@@ -17856,10 +18498,10 @@
         <v>1010</v>
       </c>
       <c r="D478" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E478" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F478" t="s">
         <v>30</v>
@@ -17888,7 +18530,7 @@
         <v>1063</v>
       </c>
       <c r="E479" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F479" t="s">
         <v>11</v>
@@ -17946,7 +18588,7 @@
         <v>1063</v>
       </c>
       <c r="E481" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F481" t="s">
         <v>28</v>
@@ -17975,7 +18617,7 @@
         <v>1063</v>
       </c>
       <c r="E482" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F482" t="s">
         <v>14</v>
@@ -18001,10 +18643,10 @@
         <v>1020</v>
       </c>
       <c r="D483" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E483" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F483" t="s">
         <v>20</v>
@@ -18030,7 +18672,7 @@
         <v>1022</v>
       </c>
       <c r="D484" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E484" t="s">
         <v>1062</v>
@@ -18059,10 +18701,10 @@
         <v>1024</v>
       </c>
       <c r="D485" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E485" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F485" t="s">
         <v>65</v>
@@ -18088,7 +18730,7 @@
         <v>1026</v>
       </c>
       <c r="D486" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E486" t="s">
         <v>1062</v>
@@ -18117,7 +18759,7 @@
         <v>1028</v>
       </c>
       <c r="D487" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E487" t="s">
         <v>1062</v>
@@ -18146,10 +18788,10 @@
         <v>1030</v>
       </c>
       <c r="D488" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E488" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F488" t="s">
         <v>65</v>
@@ -18233,7 +18875,7 @@
         <v>1036</v>
       </c>
       <c r="D491" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E491" t="s">
         <v>1062</v>
@@ -18262,7 +18904,7 @@
         <v>1038</v>
       </c>
       <c r="D492" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E492" t="s">
         <v>1062</v>
@@ -18349,7 +18991,7 @@
         <v>1046</v>
       </c>
       <c r="D495" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F495" t="s">
         <v>39</v>
@@ -18375,7 +19017,7 @@
         <v>1048</v>
       </c>
       <c r="D496" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F496" t="s">
         <v>39</v>
@@ -18401,7 +19043,7 @@
         <v>1050</v>
       </c>
       <c r="D497" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F497" t="s">
         <v>39</v>
@@ -18427,7 +19069,7 @@
         <v>1052</v>
       </c>
       <c r="D498" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F498" t="s">
         <v>39</v>
@@ -18453,7 +19095,7 @@
         <v>1054</v>
       </c>
       <c r="D499" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F499" t="s">
         <v>39</v>
@@ -18479,7 +19121,7 @@
         <v>1044</v>
       </c>
       <c r="D500" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E500" t="s">
         <v>1062</v>
@@ -18502,13 +19144,13 @@
         <v>46093</v>
       </c>
       <c r="B501" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C501" t="s">
         <v>1066</v>
       </c>
-      <c r="C501" t="s">
-        <v>1067</v>
-      </c>
       <c r="D501" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E501" t="s">
         <v>1062</v>
@@ -18531,16 +19173,16 @@
         <v>46093</v>
       </c>
       <c r="B502" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C502" t="s">
         <v>1068</v>
       </c>
-      <c r="C502" t="s">
-        <v>1069</v>
-      </c>
       <c r="D502" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E502" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F502" t="s">
         <v>20</v>
@@ -18560,13 +19202,13 @@
         <v>46093</v>
       </c>
       <c r="B503" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C503" t="s">
         <v>1070</v>
       </c>
-      <c r="C503" t="s">
-        <v>1071</v>
-      </c>
       <c r="D503" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F503" t="s">
         <v>39</v>
@@ -18586,13 +19228,13 @@
         <v>46093</v>
       </c>
       <c r="B504" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C504" t="s">
         <v>1072</v>
       </c>
-      <c r="C504" t="s">
-        <v>1073</v>
-      </c>
       <c r="D504" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F504" t="s">
         <v>39</v>
@@ -18612,13 +19254,13 @@
         <v>46093</v>
       </c>
       <c r="B505" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C505" t="s">
         <v>1074</v>
       </c>
-      <c r="C505" t="s">
-        <v>1075</v>
-      </c>
       <c r="D505" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F505" t="s">
         <v>39</v>
@@ -18638,16 +19280,16 @@
         <v>46093</v>
       </c>
       <c r="B506" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C506" t="s">
         <v>1076</v>
       </c>
-      <c r="C506" t="s">
-        <v>1077</v>
-      </c>
       <c r="D506" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E506" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F506" t="s">
         <v>20</v>
@@ -18667,13 +19309,13 @@
         <v>46093</v>
       </c>
       <c r="B507" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C507" t="s">
         <v>1078</v>
       </c>
-      <c r="C507" t="s">
-        <v>1079</v>
-      </c>
       <c r="D507" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F507" t="s">
         <v>39</v>
@@ -18693,13 +19335,13 @@
         <v>46093</v>
       </c>
       <c r="B508" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C508" t="s">
         <v>1080</v>
       </c>
-      <c r="C508" t="s">
-        <v>1081</v>
-      </c>
       <c r="D508" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F508" t="s">
         <v>39</v>
@@ -18719,16 +19361,16 @@
         <v>46093</v>
       </c>
       <c r="B509" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C509" t="s">
         <v>1082</v>
       </c>
-      <c r="C509" t="s">
-        <v>1083</v>
-      </c>
       <c r="D509" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E509" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F509" t="s">
         <v>20</v>
@@ -18748,13 +19390,13 @@
         <v>46093</v>
       </c>
       <c r="B510" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C510" t="s">
         <v>1084</v>
       </c>
-      <c r="C510" t="s">
-        <v>1085</v>
-      </c>
       <c r="D510" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F510" t="s">
         <v>39</v>
@@ -18774,10 +19416,10 @@
         <v>46093</v>
       </c>
       <c r="B511" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C511" t="s">
         <v>1086</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1087</v>
       </c>
       <c r="D511" t="s">
         <v>1061</v>
@@ -18803,13 +19445,13 @@
         <v>46093</v>
       </c>
       <c r="B512" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C512" t="s">
         <v>1088</v>
       </c>
-      <c r="C512" t="s">
-        <v>1089</v>
-      </c>
       <c r="D512" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F512" t="s">
         <v>39</v>
@@ -18829,13 +19471,13 @@
         <v>46093</v>
       </c>
       <c r="B513" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C513" t="s">
         <v>1090</v>
       </c>
-      <c r="C513" t="s">
-        <v>1091</v>
-      </c>
       <c r="D513" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F513" t="s">
         <v>39</v>
@@ -18855,13 +19497,13 @@
         <v>46093</v>
       </c>
       <c r="B514" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C514" t="s">
         <v>1092</v>
       </c>
-      <c r="C514" t="s">
-        <v>1093</v>
-      </c>
       <c r="D514" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F514" t="s">
         <v>39</v>
@@ -18881,16 +19523,16 @@
         <v>46093</v>
       </c>
       <c r="B515" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C515" t="s">
         <v>1094</v>
       </c>
-      <c r="C515" t="s">
-        <v>1095</v>
-      </c>
       <c r="D515" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E515" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F515" t="s">
         <v>30</v>
@@ -18899,7 +19541,7 @@
         <v>7</v>
       </c>
       <c r="H515" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I515">
         <v>0</v>
@@ -18910,16 +19552,16 @@
         <v>46093</v>
       </c>
       <c r="B516" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C516" t="s">
         <v>1096</v>
-      </c>
-      <c r="C516" t="s">
-        <v>1097</v>
       </c>
       <c r="D516" t="s">
         <v>1063</v>
       </c>
       <c r="E516" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F516" t="s">
         <v>11</v>
@@ -18968,16 +19610,16 @@
         <v>46093</v>
       </c>
       <c r="B518" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C518" t="s">
         <v>1098</v>
       </c>
-      <c r="C518" t="s">
-        <v>1099</v>
-      </c>
       <c r="D518" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E518" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F518" t="s">
         <v>65</v>
@@ -18986,7 +19628,7 @@
         <v>8</v>
       </c>
       <c r="H518" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I518">
         <v>0</v>
@@ -18997,16 +19639,16 @@
         <v>46093</v>
       </c>
       <c r="B519" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C519" t="s">
         <v>1100</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1101</v>
       </c>
       <c r="D519" t="s">
         <v>1063</v>
       </c>
       <c r="E519" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F519" t="s">
         <v>58</v>
@@ -19026,13 +19668,13 @@
         <v>46093</v>
       </c>
       <c r="B520" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C520" t="s">
         <v>1066</v>
       </c>
-      <c r="C520" t="s">
-        <v>1067</v>
-      </c>
       <c r="D520" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E520" t="s">
         <v>1062</v>
@@ -19055,16 +19697,16 @@
         <v>46093</v>
       </c>
       <c r="B521" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C521" t="s">
         <v>1068</v>
       </c>
-      <c r="C521" t="s">
-        <v>1069</v>
-      </c>
       <c r="D521" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E521" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F521" t="s">
         <v>20</v>
@@ -19084,10 +19726,10 @@
         <v>46093</v>
       </c>
       <c r="B522" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C522" t="s">
         <v>1102</v>
-      </c>
-      <c r="C522" t="s">
-        <v>1103</v>
       </c>
       <c r="D522" t="s">
         <v>1061</v>
@@ -19113,16 +19755,16 @@
         <v>46093</v>
       </c>
       <c r="B523" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C523" t="s">
         <v>1076</v>
       </c>
-      <c r="C523" t="s">
-        <v>1077</v>
-      </c>
       <c r="D523" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E523" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F523" t="s">
         <v>20</v>
@@ -19142,16 +19784,16 @@
         <v>46093</v>
       </c>
       <c r="B524" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C524" t="s">
         <v>1104</v>
-      </c>
-      <c r="C524" t="s">
-        <v>1105</v>
       </c>
       <c r="D524" t="s">
         <v>1063</v>
       </c>
       <c r="E524" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F524" t="s">
         <v>14</v>
@@ -19171,10 +19813,10 @@
         <v>46093</v>
       </c>
       <c r="B525" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C525" t="s">
         <v>1106</v>
-      </c>
-      <c r="C525" t="s">
-        <v>1107</v>
       </c>
       <c r="D525" t="s">
         <v>1061</v>
@@ -19200,13 +19842,13 @@
         <v>46093</v>
       </c>
       <c r="B526" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C526" t="s">
         <v>1108</v>
       </c>
-      <c r="C526" t="s">
-        <v>1109</v>
-      </c>
       <c r="D526" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E526" t="s">
         <v>1062</v>
@@ -19218,7 +19860,7 @@
         <v>10</v>
       </c>
       <c r="H526" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I526">
         <v>0</v>
@@ -19229,10 +19871,10 @@
         <v>46093</v>
       </c>
       <c r="B527" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C527" t="s">
         <v>1110</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1111</v>
       </c>
       <c r="D527" t="s">
         <v>1061</v>
@@ -19258,10 +19900,10 @@
         <v>46093</v>
       </c>
       <c r="B528" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C528" t="s">
         <v>1112</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1113</v>
       </c>
       <c r="D528" t="s">
         <v>1061</v>
@@ -19287,10 +19929,10 @@
         <v>46093</v>
       </c>
       <c r="B529" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C529" t="s">
         <v>1114</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1115</v>
       </c>
       <c r="D529" t="s">
         <v>1061</v>
@@ -19316,10 +19958,10 @@
         <v>46093</v>
       </c>
       <c r="B530" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C530" t="s">
         <v>1116</v>
-      </c>
-      <c r="C530" t="s">
-        <v>1117</v>
       </c>
       <c r="D530" t="s">
         <v>1061</v>
@@ -19345,10 +19987,10 @@
         <v>46093</v>
       </c>
       <c r="B531" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C531" t="s">
         <v>1118</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1119</v>
       </c>
       <c r="D531" t="s">
         <v>1061</v>
@@ -19374,16 +20016,16 @@
         <v>46093</v>
       </c>
       <c r="B532" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C532" t="s">
         <v>1120</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1121</v>
       </c>
       <c r="D532" t="s">
         <v>1063</v>
       </c>
       <c r="E532" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F532" t="s">
         <v>11</v>
@@ -19403,13 +20045,13 @@
         <v>46093</v>
       </c>
       <c r="B533" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C533" t="s">
         <v>1122</v>
       </c>
-      <c r="C533" t="s">
-        <v>1123</v>
-      </c>
       <c r="D533" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E533" t="s">
         <v>1062</v>
@@ -19421,7 +20063,7 @@
         <v>8</v>
       </c>
       <c r="H533" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I533">
         <v>0</v>
@@ -19432,10 +20074,10 @@
         <v>46093</v>
       </c>
       <c r="B534" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C534" t="s">
         <v>1124</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1125</v>
       </c>
       <c r="D534" t="s">
         <v>1061</v>
@@ -19461,16 +20103,16 @@
         <v>46093</v>
       </c>
       <c r="B535" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C535" t="s">
         <v>1126</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1127</v>
       </c>
       <c r="D535" t="s">
         <v>1063</v>
       </c>
       <c r="E535" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F535" t="s">
         <v>11</v>
@@ -19490,13 +20132,13 @@
         <v>46093</v>
       </c>
       <c r="B536" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C536" t="s">
         <v>1128</v>
       </c>
-      <c r="C536" t="s">
-        <v>1129</v>
-      </c>
       <c r="D536" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E536" t="s">
         <v>1062</v>
@@ -19508,7 +20150,7 @@
         <v>8</v>
       </c>
       <c r="H536" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I536">
         <v>0</v>
@@ -19519,10 +20161,10 @@
         <v>46093</v>
       </c>
       <c r="B537" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C537" t="s">
         <v>1130</v>
-      </c>
-      <c r="C537" t="s">
-        <v>1131</v>
       </c>
       <c r="D537" t="s">
         <v>1061</v>
@@ -19548,16 +20190,16 @@
         <v>46093</v>
       </c>
       <c r="B538" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C538" t="s">
         <v>1132</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1133</v>
       </c>
       <c r="D538" t="s">
         <v>1063</v>
       </c>
       <c r="E538" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F538" t="s">
         <v>58</v>
@@ -19577,16 +20219,16 @@
         <v>46093</v>
       </c>
       <c r="B539" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C539" t="s">
         <v>1134</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1135</v>
       </c>
       <c r="D539" t="s">
         <v>1063</v>
       </c>
       <c r="E539" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F539" t="s">
         <v>14</v>
@@ -19635,16 +20277,16 @@
         <v>46093</v>
       </c>
       <c r="B541" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C541" t="s">
         <v>1136</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1137</v>
       </c>
       <c r="D541" t="s">
         <v>1063</v>
       </c>
       <c r="E541" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F541" t="s">
         <v>14</v>
@@ -19664,16 +20306,16 @@
         <v>46093</v>
       </c>
       <c r="B542" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C542" t="s">
         <v>1138</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1139</v>
       </c>
       <c r="D542" t="s">
         <v>1063</v>
       </c>
       <c r="E542" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F542" t="s">
         <v>58</v>
@@ -19693,16 +20335,16 @@
         <v>46093</v>
       </c>
       <c r="B543" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C543" t="s">
         <v>1140</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1141</v>
       </c>
       <c r="D543" t="s">
         <v>1063</v>
       </c>
       <c r="E543" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F543" t="s">
         <v>14</v>
@@ -19722,10 +20364,10 @@
         <v>46093</v>
       </c>
       <c r="B544" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C544" t="s">
         <v>1142</v>
-      </c>
-      <c r="C544" t="s">
-        <v>1143</v>
       </c>
       <c r="D544" t="s">
         <v>1061</v>
@@ -19751,16 +20393,16 @@
         <v>46093</v>
       </c>
       <c r="B545" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C545" t="s">
         <v>1144</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1145</v>
       </c>
       <c r="D545" t="s">
         <v>1063</v>
       </c>
       <c r="E545" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F545" t="s">
         <v>14</v>
@@ -19780,13 +20422,13 @@
         <v>46093</v>
       </c>
       <c r="B546" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C546" t="s">
         <v>1146</v>
       </c>
-      <c r="C546" t="s">
-        <v>1147</v>
-      </c>
       <c r="D546" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E546" t="s">
         <v>1062</v>
@@ -19809,16 +20451,16 @@
         <v>46093</v>
       </c>
       <c r="B547" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C547" t="s">
         <v>1148</v>
-      </c>
-      <c r="C547" t="s">
-        <v>1149</v>
       </c>
       <c r="D547" t="s">
         <v>1063</v>
       </c>
       <c r="E547" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F547" t="s">
         <v>14</v>
@@ -19838,16 +20480,16 @@
         <v>46093</v>
       </c>
       <c r="B548" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C548" t="s">
         <v>1150</v>
-      </c>
-      <c r="C548" t="s">
-        <v>1151</v>
       </c>
       <c r="D548" t="s">
         <v>1063</v>
       </c>
       <c r="E548" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F548" t="s">
         <v>9</v>
@@ -19867,13 +20509,13 @@
         <v>46093</v>
       </c>
       <c r="B549" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C549" t="s">
         <v>1152</v>
       </c>
-      <c r="C549" t="s">
-        <v>1153</v>
-      </c>
       <c r="D549" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E549" t="s">
         <v>1062</v>
@@ -19896,16 +20538,16 @@
         <v>46093</v>
       </c>
       <c r="B550" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C550" t="s">
         <v>1154</v>
-      </c>
-      <c r="C550" t="s">
-        <v>1155</v>
       </c>
       <c r="D550" t="s">
         <v>1063</v>
       </c>
       <c r="E550" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F550" t="s">
         <v>14</v>
@@ -19925,16 +20567,16 @@
         <v>46093</v>
       </c>
       <c r="B551" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C551" t="s">
         <v>1156</v>
       </c>
-      <c r="C551" t="s">
-        <v>1157</v>
-      </c>
       <c r="D551" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E551" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F551" t="s">
         <v>65</v>
@@ -19954,10 +20596,10 @@
         <v>46093</v>
       </c>
       <c r="B552" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C552" t="s">
         <v>1158</v>
-      </c>
-      <c r="C552" t="s">
-        <v>1159</v>
       </c>
       <c r="D552" t="s">
         <v>1061</v>
@@ -19983,16 +20625,16 @@
         <v>46093</v>
       </c>
       <c r="B553" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C553" t="s">
         <v>1160</v>
       </c>
-      <c r="C553" t="s">
-        <v>1161</v>
-      </c>
       <c r="D553" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E553" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F553" t="s">
         <v>20</v>
@@ -20012,10 +20654,10 @@
         <v>46093</v>
       </c>
       <c r="B554" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C554" t="s">
         <v>1162</v>
-      </c>
-      <c r="C554" t="s">
-        <v>1163</v>
       </c>
       <c r="D554" t="s">
         <v>1061</v>
@@ -20041,16 +20683,16 @@
         <v>46093</v>
       </c>
       <c r="B555" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C555" t="s">
         <v>1164</v>
-      </c>
-      <c r="C555" t="s">
-        <v>1165</v>
       </c>
       <c r="D555" t="s">
         <v>1063</v>
       </c>
       <c r="E555" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F555" t="s">
         <v>28</v>
@@ -20070,10 +20712,10 @@
         <v>46093</v>
       </c>
       <c r="B556" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C556" t="s">
         <v>1166</v>
-      </c>
-      <c r="C556" t="s">
-        <v>1167</v>
       </c>
       <c r="D556" t="s">
         <v>1061</v>
@@ -20099,16 +20741,16 @@
         <v>46093</v>
       </c>
       <c r="B557" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C557" t="s">
         <v>1168</v>
       </c>
-      <c r="C557" t="s">
-        <v>1169</v>
-      </c>
       <c r="D557" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E557" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F557" t="s">
         <v>20</v>
@@ -20128,10 +20770,10 @@
         <v>46093</v>
       </c>
       <c r="B558" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C558" t="s">
         <v>1170</v>
-      </c>
-      <c r="C558" t="s">
-        <v>1171</v>
       </c>
       <c r="D558" t="s">
         <v>1061</v>
@@ -20157,10 +20799,10 @@
         <v>46093</v>
       </c>
       <c r="B559" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C559" t="s">
         <v>1172</v>
-      </c>
-      <c r="C559" t="s">
-        <v>1173</v>
       </c>
       <c r="D559" t="s">
         <v>1061</v>
@@ -20186,16 +20828,16 @@
         <v>46093</v>
       </c>
       <c r="B560" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C560" t="s">
         <v>1174</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1175</v>
       </c>
       <c r="D560" t="s">
         <v>1063</v>
       </c>
       <c r="E560" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F560" t="s">
         <v>14</v>
@@ -20215,16 +20857,16 @@
         <v>46093</v>
       </c>
       <c r="B561" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C561" t="s">
         <v>1176</v>
       </c>
-      <c r="C561" t="s">
-        <v>1177</v>
-      </c>
       <c r="D561" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E561" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F561" t="s">
         <v>65</v>
@@ -20244,16 +20886,16 @@
         <v>46093</v>
       </c>
       <c r="B562" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C562" t="s">
         <v>1178</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1179</v>
       </c>
       <c r="D562" t="s">
         <v>1063</v>
       </c>
       <c r="E562" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F562" t="s">
         <v>14</v>
@@ -20273,10 +20915,10 @@
         <v>46093</v>
       </c>
       <c r="B563" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C563" t="s">
         <v>1180</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1181</v>
       </c>
       <c r="D563" t="s">
         <v>1061</v>
@@ -20291,7 +20933,7 @@
         <v>8</v>
       </c>
       <c r="H563" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I563">
         <v>0</v>
@@ -20302,16 +20944,16 @@
         <v>46093</v>
       </c>
       <c r="B564" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C564" t="s">
         <v>1182</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1183</v>
       </c>
       <c r="D564" t="s">
         <v>1063</v>
       </c>
       <c r="E564" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F564" t="s">
         <v>11</v>
@@ -20331,10 +20973,10 @@
         <v>46093</v>
       </c>
       <c r="B565" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C565" t="s">
         <v>1184</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1185</v>
       </c>
       <c r="D565" t="s">
         <v>1061</v>
@@ -20360,16 +21002,16 @@
         <v>46093</v>
       </c>
       <c r="B566" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C566" t="s">
         <v>1186</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1187</v>
       </c>
       <c r="D566" t="s">
         <v>1063</v>
       </c>
       <c r="E566" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F566" t="s">
         <v>9</v>
@@ -20378,7 +21020,7 @@
         <v>7</v>
       </c>
       <c r="H566" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I566">
         <v>0</v>
@@ -20389,13 +21031,13 @@
         <v>46093</v>
       </c>
       <c r="B567" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C567" t="s">
         <v>1188</v>
       </c>
-      <c r="C567" t="s">
-        <v>1189</v>
-      </c>
       <c r="D567" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E567" t="s">
         <v>1062</v>
@@ -20418,16 +21060,16 @@
         <v>46093</v>
       </c>
       <c r="B568" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C568" t="s">
         <v>1190</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1191</v>
       </c>
       <c r="D568" t="s">
         <v>1063</v>
       </c>
       <c r="E568" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F568" t="s">
         <v>14</v>
@@ -20447,10 +21089,10 @@
         <v>46093</v>
       </c>
       <c r="B569" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C569" t="s">
         <v>1192</v>
-      </c>
-      <c r="C569" t="s">
-        <v>1193</v>
       </c>
       <c r="D569" t="s">
         <v>1061</v>
@@ -20476,13 +21118,13 @@
         <v>46093</v>
       </c>
       <c r="B570" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C570" t="s">
         <v>1194</v>
       </c>
-      <c r="C570" t="s">
-        <v>1195</v>
-      </c>
       <c r="D570" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E570" t="s">
         <v>1062</v>
@@ -20505,10 +21147,10 @@
         <v>46093</v>
       </c>
       <c r="B571" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C571" t="s">
         <v>1196</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1197</v>
       </c>
       <c r="D571" t="s">
         <v>1061</v>
@@ -20534,10 +21176,10 @@
         <v>46093</v>
       </c>
       <c r="B572" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C572" t="s">
         <v>1198</v>
-      </c>
-      <c r="C572" t="s">
-        <v>1199</v>
       </c>
       <c r="D572" t="s">
         <v>1061</v>
@@ -20563,13 +21205,13 @@
         <v>46093</v>
       </c>
       <c r="B573" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C573" t="s">
         <v>1200</v>
       </c>
-      <c r="C573" t="s">
-        <v>1201</v>
-      </c>
       <c r="D573" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E573" t="s">
         <v>1062</v>
@@ -20581,7 +21223,7 @@
         <v>10</v>
       </c>
       <c r="H573" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I573">
         <v>0</v>
@@ -20592,16 +21234,16 @@
         <v>46093</v>
       </c>
       <c r="B574" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C574" t="s">
         <v>1202</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1203</v>
       </c>
       <c r="D574" t="s">
         <v>1063</v>
       </c>
       <c r="E574" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F574" t="s">
         <v>58</v>
@@ -20621,16 +21263,16 @@
         <v>46093</v>
       </c>
       <c r="B575" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C575" t="s">
         <v>1204</v>
-      </c>
-      <c r="C575" t="s">
-        <v>1205</v>
       </c>
       <c r="D575" t="s">
         <v>1063</v>
       </c>
       <c r="E575" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F575" t="s">
         <v>14</v>
@@ -20639,7 +21281,7 @@
         <v>8</v>
       </c>
       <c r="H575" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I575">
         <v>0</v>
@@ -20650,16 +21292,16 @@
         <v>46093</v>
       </c>
       <c r="B576" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C576" t="s">
         <v>1206</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1207</v>
       </c>
       <c r="D576" t="s">
         <v>1063</v>
       </c>
       <c r="E576" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F576" t="s">
         <v>28</v>
@@ -20679,16 +21321,16 @@
         <v>46093</v>
       </c>
       <c r="B577" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C577" t="s">
         <v>1208</v>
-      </c>
-      <c r="C577" t="s">
-        <v>1209</v>
       </c>
       <c r="D577" t="s">
         <v>1063</v>
       </c>
       <c r="E577" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F577" t="s">
         <v>14</v>
@@ -20726,7 +21368,7 @@
         <v>8</v>
       </c>
       <c r="H578" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I578">
         <v>0</v>
@@ -20737,10 +21379,10 @@
         <v>46093</v>
       </c>
       <c r="B579" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C579" t="s">
         <v>1210</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1211</v>
       </c>
       <c r="D579" t="s">
         <v>1061</v>
@@ -20766,10 +21408,10 @@
         <v>46093</v>
       </c>
       <c r="B580" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C580" t="s">
         <v>1212</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1213</v>
       </c>
       <c r="D580" t="s">
         <v>1061</v>
@@ -20795,10 +21437,10 @@
         <v>46093</v>
       </c>
       <c r="B581" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C581" t="s">
         <v>1214</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1215</v>
       </c>
       <c r="D581" t="s">
         <v>1061</v>
@@ -20813,7 +21455,7 @@
         <v>8</v>
       </c>
       <c r="H581" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I581">
         <v>0</v>
@@ -20824,16 +21466,16 @@
         <v>46093</v>
       </c>
       <c r="B582" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C582" t="s">
         <v>1216</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1217</v>
       </c>
       <c r="D582" t="s">
         <v>1063</v>
       </c>
       <c r="E582" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F582" t="s">
         <v>11</v>
@@ -20853,13 +21495,13 @@
         <v>46093</v>
       </c>
       <c r="B583" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C583" t="s">
         <v>1218</v>
       </c>
-      <c r="C583" t="s">
-        <v>1219</v>
-      </c>
       <c r="D583" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E583" t="s">
         <v>1062</v>
@@ -20871,7 +21513,7 @@
         <v>10</v>
       </c>
       <c r="H583" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I583">
         <v>0</v>
@@ -20882,10 +21524,10 @@
         <v>46093</v>
       </c>
       <c r="B584" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C584" t="s">
         <v>1220</v>
-      </c>
-      <c r="C584" t="s">
-        <v>1221</v>
       </c>
       <c r="D584" t="s">
         <v>1061</v>
@@ -20911,16 +21553,16 @@
         <v>46093</v>
       </c>
       <c r="B585" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C585" t="s">
         <v>1222</v>
       </c>
-      <c r="C585" t="s">
-        <v>1223</v>
-      </c>
       <c r="D585" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E585" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F585" t="s">
         <v>65</v>
@@ -20929,7 +21571,7 @@
         <v>8</v>
       </c>
       <c r="H585" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I585">
         <v>0</v>
@@ -20940,10 +21582,10 @@
         <v>46093</v>
       </c>
       <c r="B586" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C586" t="s">
         <v>1224</v>
-      </c>
-      <c r="C586" t="s">
-        <v>1225</v>
       </c>
       <c r="D586" t="s">
         <v>1061</v>
@@ -20969,16 +21611,16 @@
         <v>46093</v>
       </c>
       <c r="B587" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C587" t="s">
         <v>1226</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1227</v>
       </c>
       <c r="D587" t="s">
         <v>1063</v>
       </c>
       <c r="E587" t="s">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="F587" t="s">
         <v>14</v>
@@ -20998,13 +21640,13 @@
         <v>46093</v>
       </c>
       <c r="B588" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C588" t="s">
         <v>1228</v>
       </c>
-      <c r="C588" t="s">
-        <v>1229</v>
-      </c>
       <c r="D588" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E588" t="s">
         <v>1062</v>
@@ -21016,7 +21658,10 @@
         <v>8</v>
       </c>
       <c r="H588" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="I588">
+        <v>0</v>
       </c>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.25">
@@ -21024,16 +21669,16 @@
         <v>46093</v>
       </c>
       <c r="B589" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C589" t="s">
         <v>1230</v>
       </c>
-      <c r="C589" t="s">
-        <v>1231</v>
-      </c>
       <c r="D589" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E589" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F589" t="s">
         <v>65</v>
@@ -21042,7 +21687,7 @@
         <v>8</v>
       </c>
       <c r="H589" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I589">
         <v>0</v>
@@ -21053,10 +21698,10 @@
         <v>46093</v>
       </c>
       <c r="B590" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C590" t="s">
         <v>1232</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1233</v>
       </c>
       <c r="D590" t="s">
         <v>1061</v>
@@ -21082,16 +21727,16 @@
         <v>46093</v>
       </c>
       <c r="B591" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C591" t="s">
         <v>1234</v>
       </c>
-      <c r="C591" t="s">
-        <v>1235</v>
-      </c>
       <c r="D591" t="s">
-        <v>1063</v>
+        <v>1250</v>
       </c>
       <c r="E591" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F591" t="s">
         <v>20</v>
@@ -21111,13 +21756,13 @@
         <v>46094</v>
       </c>
       <c r="B592" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C592" t="s">
         <v>1236</v>
       </c>
-      <c r="C592" t="s">
-        <v>1237</v>
-      </c>
       <c r="D592" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F592" t="s">
         <v>39</v>
@@ -21137,13 +21782,13 @@
         <v>46094</v>
       </c>
       <c r="B593" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C593" t="s">
         <v>1238</v>
       </c>
-      <c r="C593" t="s">
-        <v>1239</v>
-      </c>
       <c r="D593" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E593" t="s">
         <v>1062</v>
@@ -21166,13 +21811,13 @@
         <v>46094</v>
       </c>
       <c r="B594" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C594" t="s">
         <v>1240</v>
       </c>
-      <c r="C594" t="s">
-        <v>1241</v>
-      </c>
       <c r="D594" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F594" t="s">
         <v>39</v>
@@ -21192,13 +21837,13 @@
         <v>46094</v>
       </c>
       <c r="B595" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C595" t="s">
         <v>1242</v>
       </c>
-      <c r="C595" t="s">
-        <v>1243</v>
-      </c>
       <c r="D595" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F595" t="s">
         <v>39</v>
@@ -21218,13 +21863,13 @@
         <v>46094</v>
       </c>
       <c r="B596" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C596" t="s">
         <v>1244</v>
       </c>
-      <c r="C596" t="s">
-        <v>1245</v>
-      </c>
       <c r="D596" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F596" t="s">
         <v>39</v>
@@ -21244,13 +21889,13 @@
         <v>46094</v>
       </c>
       <c r="B597" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C597" t="s">
         <v>1246</v>
       </c>
-      <c r="C597" t="s">
-        <v>1247</v>
-      </c>
       <c r="D597" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F597" t="s">
         <v>39</v>
@@ -21270,13 +21915,13 @@
         <v>46094</v>
       </c>
       <c r="B598" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C598" t="s">
         <v>1248</v>
       </c>
-      <c r="C598" t="s">
-        <v>1249</v>
-      </c>
       <c r="D598" t="s">
-        <v>1061</v>
+        <v>1250</v>
       </c>
       <c r="E598" t="s">
         <v>1062</v>
@@ -21292,6 +21937,2729 @@
       </c>
       <c r="I598">
         <v>0</v>
+      </c>
+    </row>
+    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A599" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B599" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C599" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D599" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E599" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F599" t="s">
+        <v>30</v>
+      </c>
+      <c r="G599" t="s">
+        <v>7</v>
+      </c>
+      <c r="H599" t="s">
+        <v>21</v>
+      </c>
+      <c r="I599">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A600" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B600" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C600" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D600" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E600" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F600" t="s">
+        <v>26</v>
+      </c>
+      <c r="G600" t="s">
+        <v>7</v>
+      </c>
+      <c r="H600" t="s">
+        <v>21</v>
+      </c>
+      <c r="I600">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A601" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B601" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C601" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D601" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E601" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F601" t="s">
+        <v>14</v>
+      </c>
+      <c r="G601" t="s">
+        <v>8</v>
+      </c>
+      <c r="H601" t="s">
+        <v>22</v>
+      </c>
+      <c r="I601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A602" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B602" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C602" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D602" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E602" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F602" t="s">
+        <v>16</v>
+      </c>
+      <c r="G602" t="s">
+        <v>8</v>
+      </c>
+      <c r="H602" t="s">
+        <v>19</v>
+      </c>
+      <c r="I602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A603" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B603" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C603" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D603" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E603" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F603" t="s">
+        <v>30</v>
+      </c>
+      <c r="G603" t="s">
+        <v>7</v>
+      </c>
+      <c r="H603" t="s">
+        <v>21</v>
+      </c>
+      <c r="I603">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A604" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B604" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C604" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D604" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E604" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F604" t="s">
+        <v>14</v>
+      </c>
+      <c r="G604" t="s">
+        <v>8</v>
+      </c>
+      <c r="H604" t="s">
+        <v>21</v>
+      </c>
+      <c r="I604">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A605" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B605" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C605" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D605" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E605" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F605" t="s">
+        <v>47</v>
+      </c>
+      <c r="G605" t="s">
+        <v>10</v>
+      </c>
+      <c r="H605" t="s">
+        <v>19</v>
+      </c>
+      <c r="I605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A606" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B606" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C606" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D606" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E606" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F606" t="s">
+        <v>25</v>
+      </c>
+      <c r="G606" t="s">
+        <v>8</v>
+      </c>
+      <c r="H606" t="s">
+        <v>19</v>
+      </c>
+      <c r="I606">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A607" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B607" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C607" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D607" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E607" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F607" t="s">
+        <v>16</v>
+      </c>
+      <c r="G607" t="s">
+        <v>8</v>
+      </c>
+      <c r="H607" t="s">
+        <v>19</v>
+      </c>
+      <c r="I607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A608" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B608" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C608" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D608" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E608" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F608" t="s">
+        <v>14</v>
+      </c>
+      <c r="G608" t="s">
+        <v>8</v>
+      </c>
+      <c r="H608" t="s">
+        <v>19</v>
+      </c>
+      <c r="I608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A609" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B609" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C609" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D609" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E609" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F609" t="s">
+        <v>65</v>
+      </c>
+      <c r="G609" t="s">
+        <v>8</v>
+      </c>
+      <c r="H609" t="s">
+        <v>19</v>
+      </c>
+      <c r="I609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A610" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B610" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C610" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D610" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E610" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F610" t="s">
+        <v>1275</v>
+      </c>
+      <c r="G610" t="s">
+        <v>934</v>
+      </c>
+      <c r="H610" t="s">
+        <v>19</v>
+      </c>
+      <c r="I610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A611" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B611" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C611" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D611" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E611" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F611" t="s">
+        <v>16</v>
+      </c>
+      <c r="G611" t="s">
+        <v>8</v>
+      </c>
+      <c r="H611" t="s">
+        <v>22</v>
+      </c>
+      <c r="I611">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A612" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C612" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D612" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E612" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F612" t="s">
+        <v>58</v>
+      </c>
+      <c r="G612" t="s">
+        <v>31</v>
+      </c>
+      <c r="H612" t="s">
+        <v>19</v>
+      </c>
+      <c r="I612">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A613" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C613" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D613" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E613" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F613" t="s">
+        <v>9</v>
+      </c>
+      <c r="G613" t="s">
+        <v>7</v>
+      </c>
+      <c r="H613" t="s">
+        <v>21</v>
+      </c>
+      <c r="I613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A614" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B614" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C614" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D614" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E614" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F614" t="s">
+        <v>14</v>
+      </c>
+      <c r="G614" t="s">
+        <v>8</v>
+      </c>
+      <c r="H614" t="s">
+        <v>19</v>
+      </c>
+      <c r="I614">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A615" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B615" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C615" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D615" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E615" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F615" t="s">
+        <v>6</v>
+      </c>
+      <c r="G615" t="s">
+        <v>8</v>
+      </c>
+      <c r="H615" t="s">
+        <v>19</v>
+      </c>
+      <c r="I615">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A616" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B616" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C616" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D616" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E616" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F616" t="s">
+        <v>25</v>
+      </c>
+      <c r="G616" t="s">
+        <v>8</v>
+      </c>
+      <c r="H616" t="s">
+        <v>19</v>
+      </c>
+      <c r="I616">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A617" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B617" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C617" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D617" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E617" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F617" t="s">
+        <v>9</v>
+      </c>
+      <c r="G617" t="s">
+        <v>7</v>
+      </c>
+      <c r="H617" t="s">
+        <v>21</v>
+      </c>
+      <c r="I617">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A618" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B618" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C618" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D618" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E618" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F618" t="s">
+        <v>14</v>
+      </c>
+      <c r="G618" t="s">
+        <v>8</v>
+      </c>
+      <c r="H618" t="s">
+        <v>22</v>
+      </c>
+      <c r="I618" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A619" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B619" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C619" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D619" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E619" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F619" t="s">
+        <v>11</v>
+      </c>
+      <c r="G619" t="s">
+        <v>8</v>
+      </c>
+      <c r="H619" t="s">
+        <v>29</v>
+      </c>
+      <c r="I619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A620" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B620" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C620" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D620" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E620" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F620" t="s">
+        <v>30</v>
+      </c>
+      <c r="G620" t="s">
+        <v>8</v>
+      </c>
+      <c r="H620" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A621" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B621" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C621" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D621" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E621" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F621" t="s">
+        <v>14</v>
+      </c>
+      <c r="G621" t="s">
+        <v>8</v>
+      </c>
+      <c r="H621" t="s">
+        <v>19</v>
+      </c>
+      <c r="I621">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A622" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B622" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C622" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D622" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E622" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F622" t="s">
+        <v>30</v>
+      </c>
+      <c r="G622" t="s">
+        <v>8</v>
+      </c>
+      <c r="H622" t="s">
+        <v>19</v>
+      </c>
+      <c r="I622">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A623" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B623" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C623" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D623" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E623" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F623" t="s">
+        <v>65</v>
+      </c>
+      <c r="G623" t="s">
+        <v>8</v>
+      </c>
+      <c r="H623" t="s">
+        <v>19</v>
+      </c>
+      <c r="I623">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A624" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B624" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C624" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D624" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E624" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F624" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G624" t="s">
+        <v>934</v>
+      </c>
+      <c r="H624" t="s">
+        <v>19</v>
+      </c>
+      <c r="I624">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A625" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B625" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C625" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D625" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E625" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F625" t="s">
+        <v>16</v>
+      </c>
+      <c r="G625" t="s">
+        <v>8</v>
+      </c>
+      <c r="H625" t="s">
+        <v>22</v>
+      </c>
+      <c r="I625">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A626" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B626" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C626" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D626" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E626" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F626" t="s">
+        <v>26</v>
+      </c>
+      <c r="G626" t="s">
+        <v>8</v>
+      </c>
+      <c r="H626" t="s">
+        <v>29</v>
+      </c>
+      <c r="I626" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A627" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B627" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C627" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D627" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E627" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F627" t="s">
+        <v>58</v>
+      </c>
+      <c r="G627" t="s">
+        <v>8</v>
+      </c>
+      <c r="H627" t="s">
+        <v>19</v>
+      </c>
+      <c r="I627">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A628" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B628" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C628" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D628" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E628" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F628" t="s">
+        <v>9</v>
+      </c>
+      <c r="G628" t="s">
+        <v>8</v>
+      </c>
+      <c r="H628" t="s">
+        <v>19</v>
+      </c>
+      <c r="I628">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A629" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B629" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C629" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D629" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E629" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F629" t="s">
+        <v>47</v>
+      </c>
+      <c r="G629" t="s">
+        <v>8</v>
+      </c>
+      <c r="H629" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A630" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B630" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C630" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D630" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E630" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F630" t="s">
+        <v>14</v>
+      </c>
+      <c r="G630" t="s">
+        <v>8</v>
+      </c>
+      <c r="H630" t="s">
+        <v>19</v>
+      </c>
+      <c r="I630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A631" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B631" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C631" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D631" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E631" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F631" t="s">
+        <v>11</v>
+      </c>
+      <c r="G631" t="s">
+        <v>8</v>
+      </c>
+      <c r="H631" t="s">
+        <v>22</v>
+      </c>
+      <c r="I631">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A632" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B632" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C632" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D632" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E632" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F632" t="s">
+        <v>11</v>
+      </c>
+      <c r="G632" t="s">
+        <v>8</v>
+      </c>
+      <c r="H632" t="s">
+        <v>19</v>
+      </c>
+      <c r="I632">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A633" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B633" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C633" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D633" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E633" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F633" t="s">
+        <v>41</v>
+      </c>
+      <c r="G633" t="s">
+        <v>7</v>
+      </c>
+      <c r="H633" t="s">
+        <v>19</v>
+      </c>
+      <c r="I633">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A634" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B634" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C634" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D634" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E634" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F634" t="s">
+        <v>28</v>
+      </c>
+      <c r="G634" t="s">
+        <v>7</v>
+      </c>
+      <c r="H634" t="s">
+        <v>19</v>
+      </c>
+      <c r="I634">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A635" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B635" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C635" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D635" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E635" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F635" t="s">
+        <v>6</v>
+      </c>
+      <c r="G635" t="s">
+        <v>8</v>
+      </c>
+      <c r="H635" t="s">
+        <v>19</v>
+      </c>
+      <c r="I635">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A636" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B636" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C636" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D636" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E636" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F636" t="s">
+        <v>25</v>
+      </c>
+      <c r="G636" t="s">
+        <v>8</v>
+      </c>
+      <c r="H636" t="s">
+        <v>19</v>
+      </c>
+      <c r="I636">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A637" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B637" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C637" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D637" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E637" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F637" t="s">
+        <v>32</v>
+      </c>
+      <c r="G637" t="s">
+        <v>10</v>
+      </c>
+      <c r="H637" t="s">
+        <v>19</v>
+      </c>
+      <c r="I637">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A638" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B638" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C638" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D638" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E638" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F638" t="s">
+        <v>17</v>
+      </c>
+      <c r="G638" t="s">
+        <v>8</v>
+      </c>
+      <c r="H638" t="s">
+        <v>19</v>
+      </c>
+      <c r="I638">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A639" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B639" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C639" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D639" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E639" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F639" t="s">
+        <v>16</v>
+      </c>
+      <c r="G639" t="s">
+        <v>8</v>
+      </c>
+      <c r="H639" t="s">
+        <v>21</v>
+      </c>
+      <c r="I639">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A640" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B640" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C640" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D640" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E640" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F640" t="s">
+        <v>26</v>
+      </c>
+      <c r="G640" t="s">
+        <v>934</v>
+      </c>
+      <c r="H640" t="s">
+        <v>19</v>
+      </c>
+      <c r="I640">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A641" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B641" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C641" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D641" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E641" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F641" t="s">
+        <v>47</v>
+      </c>
+      <c r="G641" t="s">
+        <v>10</v>
+      </c>
+      <c r="H641" t="s">
+        <v>21</v>
+      </c>
+      <c r="I641">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A642" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B642" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C642" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D642" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E642" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F642" t="s">
+        <v>16</v>
+      </c>
+      <c r="G642" t="s">
+        <v>8</v>
+      </c>
+      <c r="H642" t="s">
+        <v>19</v>
+      </c>
+      <c r="I642">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A643" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B643" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C643" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D643" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E643" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F643" t="s">
+        <v>14</v>
+      </c>
+      <c r="G643" t="s">
+        <v>8</v>
+      </c>
+      <c r="H643" t="s">
+        <v>22</v>
+      </c>
+      <c r="I643">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A644" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B644" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C644" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D644" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E644" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F644" t="s">
+        <v>17</v>
+      </c>
+      <c r="G644" t="s">
+        <v>8</v>
+      </c>
+      <c r="H644" t="s">
+        <v>19</v>
+      </c>
+      <c r="I644">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A645" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B645" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C645" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D645" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E645" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F645" t="s">
+        <v>6</v>
+      </c>
+      <c r="G645" t="s">
+        <v>8</v>
+      </c>
+      <c r="H645" t="s">
+        <v>22</v>
+      </c>
+      <c r="I645">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A646" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B646" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C646" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D646" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E646" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F646" t="s">
+        <v>11</v>
+      </c>
+      <c r="G646" t="s">
+        <v>8</v>
+      </c>
+      <c r="H646" t="s">
+        <v>19</v>
+      </c>
+      <c r="I646">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A647" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B647" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C647" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D647" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E647" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F647" t="s">
+        <v>14</v>
+      </c>
+      <c r="G647" t="s">
+        <v>8</v>
+      </c>
+      <c r="H647" t="s">
+        <v>21</v>
+      </c>
+      <c r="I647">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A648" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B648" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C648" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D648" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E648" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F648" t="s">
+        <v>6</v>
+      </c>
+      <c r="G648" t="s">
+        <v>8</v>
+      </c>
+      <c r="H648" t="s">
+        <v>22</v>
+      </c>
+      <c r="I648">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A649" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B649" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C649" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D649" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E649" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F649" t="s">
+        <v>17</v>
+      </c>
+      <c r="G649" t="s">
+        <v>8</v>
+      </c>
+      <c r="H649" t="s">
+        <v>19</v>
+      </c>
+      <c r="I649">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A650" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B650" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C650" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D650" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E650" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F650" t="s">
+        <v>14</v>
+      </c>
+      <c r="G650" t="s">
+        <v>8</v>
+      </c>
+      <c r="H650" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A651" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B651" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C651" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D651" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E651" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F651" t="s">
+        <v>16</v>
+      </c>
+      <c r="G651" t="s">
+        <v>8</v>
+      </c>
+      <c r="H651" t="s">
+        <v>19</v>
+      </c>
+      <c r="I651">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A652" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B652" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C652" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D652" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E652" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F652" t="s">
+        <v>28</v>
+      </c>
+      <c r="G652" t="s">
+        <v>8</v>
+      </c>
+      <c r="H652" t="s">
+        <v>22</v>
+      </c>
+      <c r="I652">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A653" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B653" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C653" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D653" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E653" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F653" t="s">
+        <v>26</v>
+      </c>
+      <c r="G653" t="s">
+        <v>8</v>
+      </c>
+      <c r="H653" t="s">
+        <v>21</v>
+      </c>
+      <c r="I653">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A654" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B654" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C654" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D654" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E654" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F654" t="s">
+        <v>17</v>
+      </c>
+      <c r="G654" t="s">
+        <v>8</v>
+      </c>
+      <c r="H654" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A655" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B655" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C655" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D655" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E655" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F655" t="s">
+        <v>14</v>
+      </c>
+      <c r="G655" t="s">
+        <v>8</v>
+      </c>
+      <c r="H655" t="s">
+        <v>19</v>
+      </c>
+      <c r="I655">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A656" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B656" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C656" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D656" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E656" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F656" t="s">
+        <v>11</v>
+      </c>
+      <c r="G656" t="s">
+        <v>8</v>
+      </c>
+      <c r="H656" t="s">
+        <v>19</v>
+      </c>
+      <c r="I656">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A657" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B657" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C657" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D657" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E657" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F657" t="s">
+        <v>47</v>
+      </c>
+      <c r="G657" t="s">
+        <v>8</v>
+      </c>
+      <c r="H657" t="s">
+        <v>21</v>
+      </c>
+      <c r="I657">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A658" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B658" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C658" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D658" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E658" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F658" t="s">
+        <v>14</v>
+      </c>
+      <c r="G658" t="s">
+        <v>8</v>
+      </c>
+      <c r="H658" t="s">
+        <v>21</v>
+      </c>
+      <c r="I658">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A659" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B659" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C659" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D659" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E659" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F659" t="s">
+        <v>16</v>
+      </c>
+      <c r="G659" t="s">
+        <v>8</v>
+      </c>
+      <c r="H659" t="s">
+        <v>19</v>
+      </c>
+      <c r="I659">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A660" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B660" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C660" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D660" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E660" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F660" t="s">
+        <v>65</v>
+      </c>
+      <c r="G660" t="s">
+        <v>8</v>
+      </c>
+      <c r="H660" t="s">
+        <v>19</v>
+      </c>
+      <c r="I660">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A661" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B661" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C661" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D661" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E661" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F661" t="s">
+        <v>14</v>
+      </c>
+      <c r="G661" t="s">
+        <v>8</v>
+      </c>
+      <c r="H661" t="s">
+        <v>19</v>
+      </c>
+      <c r="I661">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A662" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B662" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C662" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D662" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F662" t="s">
+        <v>39</v>
+      </c>
+      <c r="G662" t="s">
+        <v>8</v>
+      </c>
+      <c r="H662" t="s">
+        <v>19</v>
+      </c>
+      <c r="I662">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A663" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B663" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C663" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D663" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E663" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F663" t="s">
+        <v>65</v>
+      </c>
+      <c r="G663" t="s">
+        <v>8</v>
+      </c>
+      <c r="H663" t="s">
+        <v>19</v>
+      </c>
+      <c r="I663">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A664" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B664" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C664" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D664" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F664" t="s">
+        <v>39</v>
+      </c>
+      <c r="G664" t="s">
+        <v>8</v>
+      </c>
+      <c r="H664" t="s">
+        <v>19</v>
+      </c>
+      <c r="I664">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A665" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B665" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C665" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D665" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F665" t="s">
+        <v>39</v>
+      </c>
+      <c r="G665" t="s">
+        <v>8</v>
+      </c>
+      <c r="H665" t="s">
+        <v>19</v>
+      </c>
+      <c r="I665">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A666" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B666" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C666" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D666" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F666" t="s">
+        <v>39</v>
+      </c>
+      <c r="G666" t="s">
+        <v>8</v>
+      </c>
+      <c r="H666" t="s">
+        <v>19</v>
+      </c>
+      <c r="I666">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A667" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B667" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C667" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D667" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E667" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F667" t="s">
+        <v>11</v>
+      </c>
+      <c r="G667" t="s">
+        <v>40</v>
+      </c>
+      <c r="H667" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A668" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B668" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C668" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D668" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F668" t="s">
+        <v>39</v>
+      </c>
+      <c r="G668" t="s">
+        <v>8</v>
+      </c>
+      <c r="H668" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A669" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B669" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C669" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D669" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F669" t="s">
+        <v>39</v>
+      </c>
+      <c r="G669" t="s">
+        <v>40</v>
+      </c>
+      <c r="H669" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A670" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B670" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C670" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D670" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F670" t="s">
+        <v>39</v>
+      </c>
+      <c r="G670" t="s">
+        <v>40</v>
+      </c>
+      <c r="H670" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A671" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B671" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C671" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D671" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F671" t="s">
+        <v>39</v>
+      </c>
+      <c r="G671" t="s">
+        <v>40</v>
+      </c>
+      <c r="H671" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A672" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B672" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C672" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D672" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F672" t="s">
+        <v>39</v>
+      </c>
+      <c r="G672" t="s">
+        <v>40</v>
+      </c>
+      <c r="H672" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="673" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A673" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B673" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C673" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D673" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E673" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F673" t="s">
+        <v>65</v>
+      </c>
+      <c r="G673" t="s">
+        <v>8</v>
+      </c>
+      <c r="H673" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A674" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B674" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C674" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D674" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E674" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F674" t="s">
+        <v>65</v>
+      </c>
+      <c r="G674" t="s">
+        <v>8</v>
+      </c>
+      <c r="H674" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A675" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B675" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C675" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D675" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E675" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F675" t="s">
+        <v>47</v>
+      </c>
+      <c r="G675" t="s">
+        <v>8</v>
+      </c>
+      <c r="H675" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A676" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B676" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C676" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D676" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E676" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F676" t="s">
+        <v>47</v>
+      </c>
+      <c r="G676" t="s">
+        <v>8</v>
+      </c>
+      <c r="H676" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A677" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B677" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C677" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D677" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E677" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F677" t="s">
+        <v>65</v>
+      </c>
+      <c r="G677" t="s">
+        <v>8</v>
+      </c>
+      <c r="H677" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A678" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B678" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C678" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D678" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E678" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F678" t="s">
+        <v>14</v>
+      </c>
+      <c r="G678" t="s">
+        <v>8</v>
+      </c>
+      <c r="H678" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A679" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B679" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C679" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D679" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E679" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F679" t="s">
+        <v>28</v>
+      </c>
+      <c r="G679" t="s">
+        <v>8</v>
+      </c>
+      <c r="H679" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A680" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B680" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C680" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D680" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E680" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F680" t="s">
+        <v>47</v>
+      </c>
+      <c r="G680" t="s">
+        <v>8</v>
+      </c>
+      <c r="H680" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A681" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B681" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C681" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D681" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E681" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F681" t="s">
+        <v>14</v>
+      </c>
+      <c r="G681" t="s">
+        <v>8</v>
+      </c>
+      <c r="H681" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="682" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A682" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B682" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C682" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D682" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F682" t="s">
+        <v>54</v>
+      </c>
+      <c r="G682" t="s">
+        <v>8</v>
+      </c>
+      <c r="H682" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A683" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B683" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C683" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D683" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E683" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F683" t="s">
+        <v>28</v>
+      </c>
+      <c r="G683" t="s">
+        <v>8</v>
+      </c>
+      <c r="H683" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A684" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B684" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C684" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D684" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F684" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G684" t="s">
+        <v>8</v>
+      </c>
+      <c r="H684" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="685" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A685" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B685" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C685" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D685" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E685" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F685" t="s">
+        <v>65</v>
+      </c>
+      <c r="G685" t="s">
+        <v>13</v>
+      </c>
+      <c r="H685" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="686" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A686" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B686" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C686" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D686" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F686" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G686" t="s">
+        <v>8</v>
+      </c>
+      <c r="H686" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="687" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A687" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B687" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C687" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D687" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E687" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F687" t="s">
+        <v>47</v>
+      </c>
+      <c r="G687" t="s">
+        <v>8</v>
+      </c>
+      <c r="H687" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="688" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A688" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B688" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C688" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D688" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E688" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F688" t="s">
+        <v>14</v>
+      </c>
+      <c r="G688" t="s">
+        <v>8</v>
+      </c>
+      <c r="H688" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="689" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A689" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B689" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C689" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D689" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E689" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F689" t="s">
+        <v>65</v>
+      </c>
+      <c r="G689" t="s">
+        <v>8</v>
+      </c>
+      <c r="H689" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="690" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A690" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B690" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C690" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D690" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E690" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F690" t="s">
+        <v>14</v>
+      </c>
+      <c r="G690" t="s">
+        <v>8</v>
+      </c>
+      <c r="H690" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="691" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A691" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B691" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C691" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D691" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E691" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F691" t="s">
+        <v>47</v>
+      </c>
+      <c r="G691" t="s">
+        <v>8</v>
+      </c>
+      <c r="H691" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="692" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A692" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B692" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C692" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D692" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E692" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F692" t="s">
+        <v>65</v>
+      </c>
+      <c r="G692" t="s">
+        <v>8</v>
+      </c>
+      <c r="H692" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="693" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A693" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B693" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C693" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D693" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E693" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F693" t="s">
+        <v>47</v>
+      </c>
+      <c r="G693" t="s">
+        <v>8</v>
+      </c>
+      <c r="H693" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="694" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A694" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B694" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C694" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F694" t="s">
+        <v>16</v>
+      </c>
+      <c r="G694" t="s">
+        <v>8</v>
+      </c>
+      <c r="H694" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="695" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A695" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B695" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C695" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F695" t="s">
+        <v>17</v>
+      </c>
+      <c r="G695" t="s">
+        <v>8</v>
+      </c>
+      <c r="H695" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="696" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A696" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B696" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C696" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F696" t="s">
+        <v>1446</v>
+      </c>
+      <c r="H696" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="697" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A697" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B697" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C697" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F697" t="s">
+        <v>17</v>
+      </c>
+      <c r="G697" t="s">
+        <v>8</v>
+      </c>
+      <c r="H697" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="698" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A698" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B698" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C698" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F698" t="s">
+        <v>16</v>
+      </c>
+      <c r="G698" t="s">
+        <v>8</v>
+      </c>
+      <c r="H698" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/first-atlas/producao_2026-03.xlsx
+++ b/first-atlas/producao_2026-03.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E63B3B-0EC3-4415-8E09-0ACB01E0739A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0F4D4F-94D1-4416-BA6A-27874D0B80B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
+    <workbookView xWindow="-13620" yWindow="-3225" windowWidth="13740" windowHeight="21840" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4827" uniqueCount="1451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4837" uniqueCount="1450">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -4377,9 +4377,6 @@
   </si>
   <si>
     <t>EMPORIO E DISTRIBUIDORA BOI DE OURO LTDA</t>
-  </si>
-  <si>
-    <t>LETICIA VIVIANE CARVALHO DA PENA</t>
   </si>
   <si>
     <t>62921625000143</t>
@@ -4434,58 +4431,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -11815,10 +11761,10 @@
         <v>10</v>
       </c>
       <c r="H246" t="s">
-        <v>29</v>
-      </c>
-      <c r="I246" t="s">
-        <v>34</v>
+        <v>23</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
@@ -13427,7 +13373,7 @@
         <v>8</v>
       </c>
       <c r="H302" t="s">
-        <v>29</v>
+        <v>699</v>
       </c>
       <c r="I302">
         <v>0</v>
@@ -16660,7 +16606,7 @@
         <v>8</v>
       </c>
       <c r="H414" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.25">
@@ -21281,7 +21227,7 @@
         <v>8</v>
       </c>
       <c r="H575" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I575">
         <v>0</v>
@@ -21962,7 +21908,7 @@
         <v>7</v>
       </c>
       <c r="H599" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I599">
         <v>0</v>
@@ -21991,7 +21937,7 @@
         <v>7</v>
       </c>
       <c r="H600" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I600">
         <v>0</v>
@@ -22078,7 +22024,7 @@
         <v>7</v>
       </c>
       <c r="H603" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I603">
         <v>0</v>
@@ -22107,7 +22053,7 @@
         <v>8</v>
       </c>
       <c r="H604" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I604">
         <v>0</v>
@@ -22368,7 +22314,7 @@
         <v>7</v>
       </c>
       <c r="H613" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I613">
         <v>0</v>
@@ -22484,7 +22430,7 @@
         <v>7</v>
       </c>
       <c r="H617" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I617">
         <v>0</v>
@@ -22542,7 +22488,7 @@
         <v>8</v>
       </c>
       <c r="H619" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I619">
         <v>0</v>
@@ -23116,7 +23062,7 @@
         <v>8</v>
       </c>
       <c r="H639" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I639">
         <v>0</v>
@@ -23174,7 +23120,7 @@
         <v>10</v>
       </c>
       <c r="H641" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I641">
         <v>0</v>
@@ -23348,7 +23294,7 @@
         <v>8</v>
       </c>
       <c r="H647" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I647">
         <v>0</v>
@@ -23632,7 +23578,7 @@
         <v>8</v>
       </c>
       <c r="H657" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I657">
         <v>0</v>
@@ -23661,7 +23607,7 @@
         <v>8</v>
       </c>
       <c r="H658" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I658">
         <v>0</v>
@@ -23912,6 +23858,9 @@
       <c r="H667" t="s">
         <v>19</v>
       </c>
+      <c r="I667">
+        <v>0</v>
+      </c>
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" s="1">
@@ -23935,6 +23884,9 @@
       <c r="H668" t="s">
         <v>19</v>
       </c>
+      <c r="I668">
+        <v>0</v>
+      </c>
     </row>
     <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" s="1">
@@ -23958,6 +23910,9 @@
       <c r="H669" t="s">
         <v>19</v>
       </c>
+      <c r="I669">
+        <v>0</v>
+      </c>
     </row>
     <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" s="1">
@@ -23981,6 +23936,9 @@
       <c r="H670" t="s">
         <v>19</v>
       </c>
+      <c r="I670">
+        <v>0</v>
+      </c>
     </row>
     <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" s="1">
@@ -24004,6 +23962,9 @@
       <c r="H671" t="s">
         <v>19</v>
       </c>
+      <c r="I671">
+        <v>0</v>
+      </c>
     </row>
     <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" s="1">
@@ -24027,8 +23988,11 @@
       <c r="H672" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="673" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I672">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673" s="1">
         <v>46095</v>
       </c>
@@ -24053,8 +24017,11 @@
       <c r="H673" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I673">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674" s="1">
         <v>46095</v>
       </c>
@@ -24079,8 +24046,11 @@
       <c r="H674" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I674">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" s="1">
         <v>46095</v>
       </c>
@@ -24103,10 +24073,13 @@
         <v>8</v>
       </c>
       <c r="H675" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I675">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676" s="1">
         <v>46095</v>
       </c>
@@ -24132,7 +24105,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A677" s="1">
         <v>46095</v>
       </c>
@@ -24155,10 +24128,10 @@
         <v>8</v>
       </c>
       <c r="H677" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A678" s="1">
         <v>46095</v>
       </c>
@@ -24181,10 +24154,13 @@
         <v>8</v>
       </c>
       <c r="H678" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I678">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" s="1">
         <v>46095</v>
       </c>
@@ -24209,8 +24185,11 @@
       <c r="H679" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I679">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A680" s="1">
         <v>46095</v>
       </c>
@@ -24235,8 +24214,11 @@
       <c r="H680" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I680">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A681" s="1">
         <v>46095</v>
       </c>
@@ -24261,8 +24243,11 @@
       <c r="H681" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="682" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I681">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682" s="1">
         <v>46095</v>
       </c>
@@ -24284,8 +24269,11 @@
       <c r="H682" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="683" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I682">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A683" s="1">
         <v>46095</v>
       </c>
@@ -24310,8 +24298,11 @@
       <c r="H683" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="684" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I683">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" s="1">
         <v>46095</v>
       </c>
@@ -24331,10 +24322,13 @@
         <v>8</v>
       </c>
       <c r="H684" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="685" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I684">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685" s="1">
         <v>46095</v>
       </c>
@@ -24359,8 +24353,11 @@
       <c r="H685" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="686" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I685">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686" s="1">
         <v>46095</v>
       </c>
@@ -24374,7 +24371,7 @@
         <v>1064</v>
       </c>
       <c r="F686" t="s">
-        <v>1421</v>
+        <v>119</v>
       </c>
       <c r="G686" t="s">
         <v>8</v>
@@ -24382,8 +24379,11 @@
       <c r="H686" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="687" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I686">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A687" s="1">
         <v>46095</v>
       </c>
@@ -24406,10 +24406,13 @@
         <v>8</v>
       </c>
       <c r="H687" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="688" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I687">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688" s="1">
         <v>46095</v>
       </c>
@@ -24434,8 +24437,11 @@
       <c r="H688" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="689" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I688">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" s="1">
         <v>46095</v>
       </c>
@@ -24458,10 +24464,13 @@
         <v>8</v>
       </c>
       <c r="H689" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="690" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I689">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" s="1">
         <v>46095</v>
       </c>
@@ -24486,8 +24495,11 @@
       <c r="H690" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="691" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I690">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" s="1">
         <v>46095</v>
       </c>
@@ -24510,10 +24522,13 @@
         <v>8</v>
       </c>
       <c r="H691" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="692" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I691">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692" s="1">
         <v>46095</v>
       </c>
@@ -24538,8 +24553,11 @@
       <c r="H692" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="693" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I692">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693" s="1">
         <v>46095</v>
       </c>
@@ -24562,10 +24580,13 @@
         <v>8</v>
       </c>
       <c r="H693" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="694" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I693">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" s="1">
         <v>46097</v>
       </c>
@@ -24575,6 +24596,12 @@
       <c r="C694" t="s">
         <v>1441</v>
       </c>
+      <c r="D694" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E694" t="s">
+        <v>1062</v>
+      </c>
       <c r="F694" t="s">
         <v>16</v>
       </c>
@@ -24584,8 +24611,11 @@
       <c r="H694" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="695" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I694">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" s="1">
         <v>46097</v>
       </c>
@@ -24595,6 +24625,12 @@
       <c r="C695" t="s">
         <v>1443</v>
       </c>
+      <c r="D695" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E695" t="s">
+        <v>1062</v>
+      </c>
       <c r="F695" t="s">
         <v>17</v>
       </c>
@@ -24604,8 +24640,11 @@
       <c r="H695" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="696" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I695">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" s="1">
         <v>46097</v>
       </c>
@@ -24615,22 +24654,40 @@
       <c r="C696" t="s">
         <v>1445</v>
       </c>
+      <c r="D696" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E696" t="s">
+        <v>1062</v>
+      </c>
       <c r="F696" t="s">
-        <v>1446</v>
+        <v>47</v>
+      </c>
+      <c r="G696" t="s">
+        <v>8</v>
       </c>
       <c r="H696" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="697" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I696">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" s="1">
         <v>46097</v>
       </c>
       <c r="B697" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C697" t="s">
         <v>1447</v>
       </c>
-      <c r="C697" t="s">
-        <v>1448</v>
+      <c r="D697" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E697" t="s">
+        <v>1062</v>
       </c>
       <c r="F697" t="s">
         <v>17</v>
@@ -24641,16 +24698,25 @@
       <c r="H697" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="698" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I697">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698" s="1">
         <v>46097</v>
       </c>
       <c r="B698" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C698" t="s">
         <v>1449</v>
       </c>
-      <c r="C698" t="s">
-        <v>1450</v>
+      <c r="D698" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E698" t="s">
+        <v>1062</v>
       </c>
       <c r="F698" t="s">
         <v>16</v>
@@ -24660,6 +24726,9 @@
       </c>
       <c r="H698" t="s">
         <v>19</v>
+      </c>
+      <c r="I698">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/first-atlas/producao_2026-03.xlsx
+++ b/first-atlas/producao_2026-03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B133BA-F564-4FFE-BB71-FDCE634A43DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFD83C1-3397-4FAD-BB53-808214428643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7157" uniqueCount="2081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7663" uniqueCount="2272">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -6282,6 +6282,579 @@
   </si>
   <si>
     <t>Ata de eleicao da empresa ASSOCIACAO ESCOLINHA FUNDAMENTOS DO FUTEBOL, atualizado e registrada no orgao competente. Esse documento formaliza a eleicao e/ou nomeacao dos representantes legais e administradores, informando cargos, prazos de mandato e poderes de representacao, comprovando quem esta autorizado a agir em nome da entidade.&lt;br&gt;&lt;br&gt;Estatuto social da empresa ASSOCIACAO ESCOLINHA FUNDAMENTOS DO FUTEBOL, atualizado e registrado no orgao competente. Esse documento estabelece as regras de funcionamento da empresa, descrevendo sua finalidade, estrutura administrativa, orgaos de gestao e forma de representacao legal, comprovando sua existencia e regularidade.</t>
+  </si>
+  <si>
+    <t>31868637000128</t>
+  </si>
+  <si>
+    <t>42063902000117</t>
+  </si>
+  <si>
+    <t>52247270000103</t>
+  </si>
+  <si>
+    <t>62161364000100</t>
+  </si>
+  <si>
+    <t>59218814000140</t>
+  </si>
+  <si>
+    <t>07530434000142</t>
+  </si>
+  <si>
+    <t>58488593000167</t>
+  </si>
+  <si>
+    <t>62691113000138</t>
+  </si>
+  <si>
+    <t>48521770000106</t>
+  </si>
+  <si>
+    <t>21738366000132</t>
+  </si>
+  <si>
+    <t>17659973000130</t>
+  </si>
+  <si>
+    <t>22028750000104</t>
+  </si>
+  <si>
+    <t>47925982000196</t>
+  </si>
+  <si>
+    <t>55220635000196</t>
+  </si>
+  <si>
+    <t>36044844000181</t>
+  </si>
+  <si>
+    <t>61298260000180</t>
+  </si>
+  <si>
+    <t>54006045000100</t>
+  </si>
+  <si>
+    <t>59792053000135</t>
+  </si>
+  <si>
+    <t>58740619000201</t>
+  </si>
+  <si>
+    <t>47051883000122</t>
+  </si>
+  <si>
+    <t>52699450000118</t>
+  </si>
+  <si>
+    <t>59791910000182</t>
+  </si>
+  <si>
+    <t>43344176000173</t>
+  </si>
+  <si>
+    <t>17671515000116</t>
+  </si>
+  <si>
+    <t>00192878000176</t>
+  </si>
+  <si>
+    <t>09107200000112</t>
+  </si>
+  <si>
+    <t>26875809000150</t>
+  </si>
+  <si>
+    <t>64114216000160</t>
+  </si>
+  <si>
+    <t>17353487000199</t>
+  </si>
+  <si>
+    <t>60305011000101</t>
+  </si>
+  <si>
+    <t>38891070000150</t>
+  </si>
+  <si>
+    <t>47535579000150</t>
+  </si>
+  <si>
+    <t>28537790000249</t>
+  </si>
+  <si>
+    <t>42430521000129</t>
+  </si>
+  <si>
+    <t>11916506000161</t>
+  </si>
+  <si>
+    <t>36448699000102</t>
+  </si>
+  <si>
+    <t>53214837000108</t>
+  </si>
+  <si>
+    <t>45280899000181</t>
+  </si>
+  <si>
+    <t>64726336000119</t>
+  </si>
+  <si>
+    <t>46592778000138</t>
+  </si>
+  <si>
+    <t>64666153000155</t>
+  </si>
+  <si>
+    <t>15231029000151</t>
+  </si>
+  <si>
+    <t>26078145000107</t>
+  </si>
+  <si>
+    <t>64916272000119</t>
+  </si>
+  <si>
+    <t>60441695000179</t>
+  </si>
+  <si>
+    <t>52270574000183</t>
+  </si>
+  <si>
+    <t>09622925000149</t>
+  </si>
+  <si>
+    <t>65105661000127</t>
+  </si>
+  <si>
+    <t>38981445000172</t>
+  </si>
+  <si>
+    <t>60282404000147</t>
+  </si>
+  <si>
+    <t>59937472000118</t>
+  </si>
+  <si>
+    <t>61527450000121</t>
+  </si>
+  <si>
+    <t>32915024000167</t>
+  </si>
+  <si>
+    <t>47281884000163</t>
+  </si>
+  <si>
+    <t>60835621000117</t>
+  </si>
+  <si>
+    <t>64369662000116</t>
+  </si>
+  <si>
+    <t>44457840000153</t>
+  </si>
+  <si>
+    <t>32315559000288</t>
+  </si>
+  <si>
+    <t>61414103000192</t>
+  </si>
+  <si>
+    <t>51916183000120</t>
+  </si>
+  <si>
+    <t>09425553000160</t>
+  </si>
+  <si>
+    <t>49828832000190</t>
+  </si>
+  <si>
+    <t>PONTO DO TERERE LTDA</t>
+  </si>
+  <si>
+    <t>Raphael Ferreira Jacintho</t>
+  </si>
+  <si>
+    <t>60533126000153</t>
+  </si>
+  <si>
+    <t>PAINEIS EM LED H S PUBLICIDADE E PROPAGANDA LTDA</t>
+  </si>
+  <si>
+    <t>53139827000147</t>
+  </si>
+  <si>
+    <t>MC TECH ENGENHARIA LTDA</t>
+  </si>
+  <si>
+    <t>65716951000107</t>
+  </si>
+  <si>
+    <t>BERTEC MANUTENCAO DE MAQUINAS INDUSTRIAIS LTDA</t>
+  </si>
+  <si>
+    <t>64269100000109</t>
+  </si>
+  <si>
+    <t>GHF LOCACOES E TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>63183977000101</t>
+  </si>
+  <si>
+    <t>KJ DRINKS VIDA LTDA</t>
+  </si>
+  <si>
+    <t>30698034000162</t>
+  </si>
+  <si>
+    <t>REIS AUTO CENTER LTDA</t>
+  </si>
+  <si>
+    <t>59617054000143</t>
+  </si>
+  <si>
+    <t>PADUA ASSUNCAO LTDA</t>
+  </si>
+  <si>
+    <t>63439209000176</t>
+  </si>
+  <si>
+    <t>ACF TRANSPORTADORA URUPES LTDA</t>
+  </si>
+  <si>
+    <t>61317826000173</t>
+  </si>
+  <si>
+    <t>PE DE PANO MATERIAL DE CONSTRUCAO LTDA</t>
+  </si>
+  <si>
+    <t>17901115000150</t>
+  </si>
+  <si>
+    <t>TROPICAL MIX PRODUTOS PARA SORVETES EXPRESSO LTDA</t>
+  </si>
+  <si>
+    <t>10419748000187</t>
+  </si>
+  <si>
+    <t>RENFE INDUSTRIA E COMERCIO DE CONFECCOES LTDA</t>
+  </si>
+  <si>
+    <t>23973310000198</t>
+  </si>
+  <si>
+    <t>23.973.310 ROBSON BARBOZA VITERALE</t>
+  </si>
+  <si>
+    <t>12861245000192</t>
+  </si>
+  <si>
+    <t>ETERNOS TRAJES LTDA</t>
+  </si>
+  <si>
+    <t>62963203000130</t>
+  </si>
+  <si>
+    <t>MF AUTOMACAO LTDA</t>
+  </si>
+  <si>
+    <t>27970421000100</t>
+  </si>
+  <si>
+    <t>SUCATAS MAIA LTDA</t>
+  </si>
+  <si>
+    <t>52922100000179</t>
+  </si>
+  <si>
+    <t>RECONS OBRAS LTDA</t>
+  </si>
+  <si>
+    <t>61153190000171</t>
+  </si>
+  <si>
+    <t>LEON PRE FABRICADOS DE CONCRETO LTDA</t>
+  </si>
+  <si>
+    <t>60252607000190</t>
+  </si>
+  <si>
+    <t>UNIPLAY COMERCIO E IMPORTACAO DE BRINQUEDOS LTDA</t>
+  </si>
+  <si>
+    <t>19509903000120</t>
+  </si>
+  <si>
+    <t>M.Z AUTO PECAS LATAS E ACESSORIOS LTDA</t>
+  </si>
+  <si>
+    <t>17850958000174</t>
+  </si>
+  <si>
+    <t>CIDAUTOMOVEIS OFICINA MECANICA LTDA</t>
+  </si>
+  <si>
+    <t>61804342000159</t>
+  </si>
+  <si>
+    <t>RESOUDRE CONSULTORIA LTDA</t>
+  </si>
+  <si>
+    <t>64922299000114</t>
+  </si>
+  <si>
+    <t>DS MOREIRA COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>51763005000107</t>
+  </si>
+  <si>
+    <t>51.763.005 OSVALDO APARECIDO RODRIGUES TEIXEIRA</t>
+  </si>
+  <si>
+    <t>12230174000120</t>
+  </si>
+  <si>
+    <t>ESPACO LA BELLA LTDA</t>
+  </si>
+  <si>
+    <t>17457965000100</t>
+  </si>
+  <si>
+    <t>RESTAURANTE CANOAS LTDA</t>
+  </si>
+  <si>
+    <t>22321196000159</t>
+  </si>
+  <si>
+    <t>VIDRACARIA VD LTDA</t>
+  </si>
+  <si>
+    <t>48498515000190</t>
+  </si>
+  <si>
+    <t>RUBEM ISMAEL VASQUES</t>
+  </si>
+  <si>
+    <t>33095016000184</t>
+  </si>
+  <si>
+    <t>VIANEY RODRIGUES DE ALEXANDRIA</t>
+  </si>
+  <si>
+    <t>60673056000139</t>
+  </si>
+  <si>
+    <t>LUEDE CONFECCOES LTDA</t>
+  </si>
+  <si>
+    <t>32499745000133</t>
+  </si>
+  <si>
+    <t>GISLAINE DA SILVA LIMA</t>
+  </si>
+  <si>
+    <t>37576393000196</t>
+  </si>
+  <si>
+    <t>CARLA DE CARVALHO CAMPOS SOARES</t>
+  </si>
+  <si>
+    <t>62343534000178</t>
+  </si>
+  <si>
+    <t>62.343.534 DJEISON ASSUNCAO DA SILVA</t>
+  </si>
+  <si>
+    <t>49184636000120</t>
+  </si>
+  <si>
+    <t>49.184.636 JULIO DE SOUZA PINTO</t>
+  </si>
+  <si>
+    <t>65010763000169</t>
+  </si>
+  <si>
+    <t>ANDERSON OLIVEIRA DOS SANTOS SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
+    <t>49298069000132</t>
+  </si>
+  <si>
+    <t>49.298.069 JOAO CARLOS RIBEIRO MUNIZ</t>
+  </si>
+  <si>
+    <t>23161597000151</t>
+  </si>
+  <si>
+    <t>MARIA ERICA PEREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>59982299000170</t>
+  </si>
+  <si>
+    <t>LEVY PNEUS E RODAS LTDA</t>
+  </si>
+  <si>
+    <t>59126525000110</t>
+  </si>
+  <si>
+    <t>JK ATACAREJO DE MODAS E ACESSORIOS LTDA</t>
+  </si>
+  <si>
+    <t>40876870000305</t>
+  </si>
+  <si>
+    <t>S. C. DIAS DE OLIVEIRA LTDA</t>
+  </si>
+  <si>
+    <t>21944626000126</t>
+  </si>
+  <si>
+    <t>ZOOM PLAMOVEIS AMBIENTES PLANEJADOS LTDA</t>
+  </si>
+  <si>
+    <t>45551481000161</t>
+  </si>
+  <si>
+    <t>NICHOLLAS LAWER CANHET VIDIGAL</t>
+  </si>
+  <si>
+    <t>52594547000166</t>
+  </si>
+  <si>
+    <t>JI SERVICOS DE INSTALACOES LTDA</t>
+  </si>
+  <si>
+    <t>43297729000184</t>
+  </si>
+  <si>
+    <t>PONTO DA SUCATA LTDA</t>
+  </si>
+  <si>
+    <t>36017615000178</t>
+  </si>
+  <si>
+    <t>MARIA TEREZINHA DIAS DA CUNHA</t>
+  </si>
+  <si>
+    <t>41346335000143</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA DE CARNES SAO JUDAS TADEU LTDA</t>
+  </si>
+  <si>
+    <t>39712347000100</t>
+  </si>
+  <si>
+    <t>FERNANDO HENRIQUE FRANCA LTDA</t>
+  </si>
+  <si>
+    <t>Joao Pedro Mayer Ribeiro Oliveira</t>
+  </si>
+  <si>
+    <t>41406909000121</t>
+  </si>
+  <si>
+    <t>WELLINGTON RENATO BECA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>64336898000156</t>
+  </si>
+  <si>
+    <t>RESTAURANTE BOTECO GRILL LTDA</t>
+  </si>
+  <si>
+    <t>57842953000114</t>
+  </si>
+  <si>
+    <t>MANIA DE BICHO PET SHOP E CLINICA VETERINARIA LTDA</t>
+  </si>
+  <si>
+    <t>53206008000175</t>
+  </si>
+  <si>
+    <t>MARLIERE DE MELO JUNIOR LTDA</t>
+  </si>
+  <si>
+    <t>64106243000191</t>
+  </si>
+  <si>
+    <t>GOLL GRILL LANCHONETE LTDA</t>
+  </si>
+  <si>
+    <t>60110630000140</t>
+  </si>
+  <si>
+    <t>MARCELO F. RAMPAZZO LTDA</t>
+  </si>
+  <si>
+    <t>56960815000177</t>
+  </si>
+  <si>
+    <t>BARATINHA PIPAS COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>41697156000150</t>
+  </si>
+  <si>
+    <t>KWI CONSTRUCOES E REFORMAS LTDA</t>
+  </si>
+  <si>
+    <t>37636846000122</t>
+  </si>
+  <si>
+    <t>CRS EMPREITEIRA LTDA</t>
+  </si>
+  <si>
+    <t>50061409000196</t>
+  </si>
+  <si>
+    <t>50.061.409 DANIEL PEREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>27620284000175</t>
+  </si>
+  <si>
+    <t>27.620.284 JEAN TIAGO PEREIRA</t>
+  </si>
+  <si>
+    <t>43803389000116</t>
+  </si>
+  <si>
+    <t>LINO'S CONFECCOES LTDA</t>
+  </si>
+  <si>
+    <t>Mensageria</t>
+  </si>
+  <si>
+    <t>42630233000118</t>
+  </si>
+  <si>
+    <t>ELSON AMARANTE CARDOSO</t>
+  </si>
+  <si>
+    <t>57380929000100</t>
+  </si>
+  <si>
+    <t>M FERNANDES TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>64054764000142</t>
+  </si>
+  <si>
+    <t>Empresa: VANGINER RODRIGUES DOS ANJOS SILVA</t>
+  </si>
+  <si>
+    <t>34718763000194</t>
+  </si>
+  <si>
+    <t>34.718.763 CARLOS ALBERTO FLORINDO OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Ata de eleicao da empresa INSTITUTO VIDA MELHOR, atualizado e registrada no orgao competente. Esse documento formaliza a eleicao e/ou nomeacao dos representantes legais e administradores, informando cargos, prazos de mandato e poderes de representacao, comprovando quem esta autorizado a agir em nome da entidade.&lt;br&gt;&lt;br&gt;Estatuto social da empresa INSTITUTO VIDA MELHOR, atualizado e registrado no orgao competente. Esse documento estabelece as regras de funcionamento da empresa, descrevendo sua finalidade, estrutura administrativa, orgaos de gestao e forma de representacao legal, comprovando sua existencia e regularidade.</t>
   </si>
 </sst>
 </file>
@@ -6654,7 +7227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:I1041"/>
+  <dimension ref="A1:I1104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -6919,7 +7492,7 @@
         <v>7</v>
       </c>
       <c r="H9" t="s">
-        <v>23</v>
+        <v>696</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -8875,7 +9448,7 @@
         <v>7</v>
       </c>
       <c r="H78" t="s">
-        <v>23</v>
+        <v>696</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -9191,7 +9764,7 @@
         <v>7</v>
       </c>
       <c r="H89" t="s">
-        <v>23</v>
+        <v>696</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -12263,7 +12836,7 @@
         <v>7</v>
       </c>
       <c r="H197" t="s">
-        <v>23</v>
+        <v>696</v>
       </c>
       <c r="I197">
         <v>0</v>
@@ -15402,7 +15975,7 @@
         <v>8</v>
       </c>
       <c r="H307" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I307">
         <v>0</v>
@@ -15779,7 +16352,7 @@
         <v>8</v>
       </c>
       <c r="H320" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I320">
         <v>0</v>
@@ -17965,7 +18538,7 @@
         <v>8</v>
       </c>
       <c r="H396" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I396">
         <v>0</v>
@@ -21452,7 +22025,7 @@
         <v>7</v>
       </c>
       <c r="H518" t="s">
-        <v>696</v>
+        <v>19</v>
       </c>
       <c r="I518">
         <v>0</v>
@@ -22844,7 +23417,7 @@
         <v>929</v>
       </c>
       <c r="H566" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I566">
         <v>0</v>
@@ -26281,7 +26854,7 @@
         <v>8</v>
       </c>
       <c r="H687" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I687">
         <v>0</v>
@@ -28954,7 +29527,7 @@
         <v>8</v>
       </c>
       <c r="H780" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I780">
         <v>0</v>
@@ -31865,7 +32438,7 @@
         <v>8</v>
       </c>
       <c r="H881" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I881">
         <v>0</v>
@@ -33039,7 +33612,7 @@
         <v>8</v>
       </c>
       <c r="H922" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I922">
         <v>0</v>
@@ -33155,7 +33728,7 @@
         <v>8</v>
       </c>
       <c r="H926" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I926">
         <v>0</v>
@@ -33587,7 +34160,7 @@
         <v>8</v>
       </c>
       <c r="H941" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I941">
         <v>0</v>
@@ -33674,7 +34247,7 @@
         <v>8</v>
       </c>
       <c r="H944" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I944">
         <v>0</v>
@@ -33761,7 +34334,10 @@
         <v>7</v>
       </c>
       <c r="H947" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="I947">
+        <v>0</v>
       </c>
     </row>
     <row r="948" spans="1:9" x14ac:dyDescent="0.25">
@@ -33983,6 +34559,9 @@
       <c r="H955" t="s">
         <v>19</v>
       </c>
+      <c r="I955">
+        <v>0</v>
+      </c>
     </row>
     <row r="956" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A956" s="1">
@@ -34006,6 +34585,9 @@
       <c r="H956" t="s">
         <v>19</v>
       </c>
+      <c r="I956">
+        <v>0</v>
+      </c>
     </row>
     <row r="957" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A957" s="1">
@@ -34029,6 +34611,9 @@
       <c r="H957" t="s">
         <v>19</v>
       </c>
+      <c r="I957">
+        <v>0</v>
+      </c>
     </row>
     <row r="958" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A958" s="1">
@@ -34052,6 +34637,9 @@
       <c r="H958" t="s">
         <v>19</v>
       </c>
+      <c r="I958">
+        <v>0</v>
+      </c>
     </row>
     <row r="959" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A959" s="1">
@@ -34075,6 +34663,9 @@
       <c r="H959" t="s">
         <v>19</v>
       </c>
+      <c r="I959">
+        <v>0</v>
+      </c>
     </row>
     <row r="960" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A960" s="1">
@@ -34098,13 +34689,16 @@
       <c r="H960" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="961" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I960">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A961" s="1">
         <v>46101</v>
       </c>
-      <c r="B961">
-        <v>31868637000128</v>
+      <c r="B961" t="s">
+        <v>2081</v>
       </c>
       <c r="C961" t="s">
         <v>1984</v>
@@ -34122,15 +34716,18 @@
         <v>7</v>
       </c>
       <c r="H961" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="962" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I961">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A962" s="1">
         <v>46101</v>
       </c>
-      <c r="B962">
-        <v>42063902000117</v>
+      <c r="B962" t="s">
+        <v>2082</v>
       </c>
       <c r="C962" t="s">
         <v>1985</v>
@@ -34148,15 +34745,18 @@
         <v>8</v>
       </c>
       <c r="H962" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="963" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I962">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A963" s="1">
         <v>46101</v>
       </c>
-      <c r="B963">
-        <v>52247270000103</v>
+      <c r="B963" t="s">
+        <v>2083</v>
       </c>
       <c r="C963" t="s">
         <v>1986</v>
@@ -34176,13 +34776,16 @@
       <c r="H963" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="964" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I963">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A964" s="1">
         <v>46101</v>
       </c>
-      <c r="B964">
-        <v>62161364000100</v>
+      <c r="B964" t="s">
+        <v>2084</v>
       </c>
       <c r="C964" t="s">
         <v>1987</v>
@@ -34202,13 +34805,16 @@
       <c r="H964" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="965" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I964">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A965" s="1">
         <v>46101</v>
       </c>
-      <c r="B965">
-        <v>59218814000140</v>
+      <c r="B965" t="s">
+        <v>2085</v>
       </c>
       <c r="C965" t="s">
         <v>1988</v>
@@ -34228,13 +34834,16 @@
       <c r="H965" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="966" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I965">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A966" s="1">
         <v>46101</v>
       </c>
-      <c r="B966">
-        <v>7530434000142</v>
+      <c r="B966" t="s">
+        <v>2086</v>
       </c>
       <c r="C966" t="s">
         <v>1989</v>
@@ -34252,15 +34861,18 @@
         <v>7</v>
       </c>
       <c r="H966" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="967" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I966">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A967" s="1">
         <v>46101</v>
       </c>
-      <c r="B967">
-        <v>58488593000167</v>
+      <c r="B967" t="s">
+        <v>2087</v>
       </c>
       <c r="C967" t="s">
         <v>1990</v>
@@ -34280,13 +34892,16 @@
       <c r="H967" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="968" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I967">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A968" s="1">
         <v>46101</v>
       </c>
-      <c r="B968">
-        <v>62691113000138</v>
+      <c r="B968" t="s">
+        <v>2088</v>
       </c>
       <c r="C968" t="s">
         <v>1991</v>
@@ -34304,15 +34919,18 @@
         <v>8</v>
       </c>
       <c r="H968" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="969" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I968">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A969" s="1">
         <v>46101</v>
       </c>
-      <c r="B969">
-        <v>48521770000106</v>
+      <c r="B969" t="s">
+        <v>2089</v>
       </c>
       <c r="C969" t="s">
         <v>1992</v>
@@ -34332,13 +34950,16 @@
       <c r="H969" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="970" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I969">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A970" s="1">
         <v>46101</v>
       </c>
-      <c r="B970">
-        <v>21738366000132</v>
+      <c r="B970" t="s">
+        <v>2090</v>
       </c>
       <c r="C970" t="s">
         <v>1993</v>
@@ -34358,13 +34979,16 @@
       <c r="H970" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="971" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I970">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A971" s="1">
         <v>46101</v>
       </c>
-      <c r="B971">
-        <v>17659973000130</v>
+      <c r="B971" t="s">
+        <v>2091</v>
       </c>
       <c r="C971" t="s">
         <v>1994</v>
@@ -34384,13 +35008,16 @@
       <c r="H971" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="972" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I971">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A972" s="1">
         <v>46101</v>
       </c>
-      <c r="B972">
-        <v>22028750000104</v>
+      <c r="B972" t="s">
+        <v>2092</v>
       </c>
       <c r="C972" t="s">
         <v>1995</v>
@@ -34410,13 +35037,16 @@
       <c r="H972" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="973" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I972">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A973" s="1">
         <v>46101</v>
       </c>
-      <c r="B973">
-        <v>47925982000196</v>
+      <c r="B973" t="s">
+        <v>2093</v>
       </c>
       <c r="C973" t="s">
         <v>1996</v>
@@ -34436,13 +35066,16 @@
       <c r="H973" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="974" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I973">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A974" s="1">
         <v>46101</v>
       </c>
-      <c r="B974">
-        <v>55220635000196</v>
+      <c r="B974" t="s">
+        <v>2094</v>
       </c>
       <c r="C974" t="s">
         <v>1036</v>
@@ -34462,13 +35095,16 @@
       <c r="H974" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="975" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I974" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A975" s="1">
         <v>46101</v>
       </c>
-      <c r="B975">
-        <v>36044844000181</v>
+      <c r="B975" t="s">
+        <v>2095</v>
       </c>
       <c r="C975" t="s">
         <v>1997</v>
@@ -34488,13 +35124,16 @@
       <c r="H975" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="976" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I975">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A976" s="1">
         <v>46101</v>
       </c>
-      <c r="B976">
-        <v>61298260000180</v>
+      <c r="B976" t="s">
+        <v>2096</v>
       </c>
       <c r="C976" t="s">
         <v>1998</v>
@@ -34514,13 +35153,16 @@
       <c r="H976" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="977" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I976">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977" s="1">
         <v>46101</v>
       </c>
-      <c r="B977">
-        <v>54006045000100</v>
+      <c r="B977" t="s">
+        <v>2097</v>
       </c>
       <c r="C977" t="s">
         <v>1999</v>
@@ -34540,13 +35182,16 @@
       <c r="H977" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="978" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I977">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A978" s="1">
         <v>46101</v>
       </c>
-      <c r="B978">
-        <v>59792053000135</v>
+      <c r="B978" t="s">
+        <v>2098</v>
       </c>
       <c r="C978" t="s">
         <v>2000</v>
@@ -34566,13 +35211,16 @@
       <c r="H978" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="979" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I978">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A979" s="1">
         <v>46101</v>
       </c>
-      <c r="B979">
-        <v>58740619000201</v>
+      <c r="B979" t="s">
+        <v>2099</v>
       </c>
       <c r="C979" t="s">
         <v>2001</v>
@@ -34590,15 +35238,18 @@
         <v>8</v>
       </c>
       <c r="H979" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="980" spans="1:8" x14ac:dyDescent="0.25">
+        <v>696</v>
+      </c>
+      <c r="I979">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="980" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A980" s="1">
         <v>46101</v>
       </c>
-      <c r="B980">
-        <v>47051883000122</v>
+      <c r="B980" t="s">
+        <v>2100</v>
       </c>
       <c r="C980" t="s">
         <v>803</v>
@@ -34616,15 +35267,18 @@
         <v>13</v>
       </c>
       <c r="H980" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="981" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I980">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A981" s="1">
         <v>46101</v>
       </c>
-      <c r="B981">
-        <v>52699450000118</v>
+      <c r="B981" t="s">
+        <v>2101</v>
       </c>
       <c r="C981" t="s">
         <v>2002</v>
@@ -34642,15 +35296,18 @@
         <v>8</v>
       </c>
       <c r="H981" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="982" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I981">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A982" s="1">
         <v>46101</v>
       </c>
-      <c r="B982">
-        <v>59791910000182</v>
+      <c r="B982" t="s">
+        <v>2102</v>
       </c>
       <c r="C982" t="s">
         <v>2003</v>
@@ -34668,15 +35325,18 @@
         <v>7</v>
       </c>
       <c r="H982" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="983" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I982">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A983" s="1">
         <v>46101</v>
       </c>
-      <c r="B983">
-        <v>43344176000173</v>
+      <c r="B983" t="s">
+        <v>2103</v>
       </c>
       <c r="C983" t="s">
         <v>2004</v>
@@ -34696,13 +35356,16 @@
       <c r="H983" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="984" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I983">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A984" s="1">
         <v>46101</v>
       </c>
-      <c r="B984">
-        <v>17671515000116</v>
+      <c r="B984" t="s">
+        <v>2104</v>
       </c>
       <c r="C984" t="s">
         <v>2005</v>
@@ -34723,12 +35386,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="985" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A985" s="1">
         <v>46101</v>
       </c>
-      <c r="B985">
-        <v>192878000176</v>
+      <c r="B985" t="s">
+        <v>2105</v>
       </c>
       <c r="C985" t="s">
         <v>2006</v>
@@ -34746,15 +35409,18 @@
         <v>7</v>
       </c>
       <c r="H985" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="986" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I985">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="986" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A986" s="1">
         <v>46101</v>
       </c>
-      <c r="B986">
-        <v>9107200000112</v>
+      <c r="B986" t="s">
+        <v>2106</v>
       </c>
       <c r="C986" t="s">
         <v>2007</v>
@@ -34774,13 +35440,16 @@
       <c r="H986" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="987" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I986">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A987" s="1">
         <v>46101</v>
       </c>
-      <c r="B987">
-        <v>26875809000150</v>
+      <c r="B987" t="s">
+        <v>2107</v>
       </c>
       <c r="C987" t="s">
         <v>2008</v>
@@ -34800,13 +35469,16 @@
       <c r="H987" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="988" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I987">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="988" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A988" s="1">
         <v>46101</v>
       </c>
-      <c r="B988">
-        <v>64114216000160</v>
+      <c r="B988" t="s">
+        <v>2108</v>
       </c>
       <c r="C988" t="s">
         <v>2009</v>
@@ -34826,13 +35498,16 @@
       <c r="H988" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="989" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I988">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="989" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A989" s="1">
         <v>46101</v>
       </c>
-      <c r="B989">
-        <v>17353487000199</v>
+      <c r="B989" t="s">
+        <v>2109</v>
       </c>
       <c r="C989" t="s">
         <v>2011</v>
@@ -34850,15 +35525,18 @@
         <v>7</v>
       </c>
       <c r="H989" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="990" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I989">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="990" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A990" s="1">
         <v>46101</v>
       </c>
-      <c r="B990">
-        <v>60305011000101</v>
+      <c r="B990" t="s">
+        <v>2110</v>
       </c>
       <c r="C990" t="s">
         <v>2012</v>
@@ -34876,15 +35554,18 @@
         <v>8</v>
       </c>
       <c r="H990" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="991" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I990">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A991" s="1">
         <v>46101</v>
       </c>
-      <c r="B991">
-        <v>38891070000150</v>
+      <c r="B991" t="s">
+        <v>2111</v>
       </c>
       <c r="C991" t="s">
         <v>2013</v>
@@ -34902,15 +35583,18 @@
         <v>8</v>
       </c>
       <c r="H991" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="992" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I991" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="992" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A992" s="1">
         <v>46101</v>
       </c>
-      <c r="B992">
-        <v>47535579000150</v>
+      <c r="B992" t="s">
+        <v>2112</v>
       </c>
       <c r="C992" t="s">
         <v>2014</v>
@@ -34930,13 +35614,16 @@
       <c r="H992" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="993" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I992">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="993" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A993" s="1">
         <v>46101</v>
       </c>
-      <c r="B993">
-        <v>28537790000249</v>
+      <c r="B993" t="s">
+        <v>2113</v>
       </c>
       <c r="C993" t="s">
         <v>2015</v>
@@ -34954,15 +35641,18 @@
         <v>7</v>
       </c>
       <c r="H993" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="994" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I993">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="994" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A994" s="1">
         <v>46101</v>
       </c>
-      <c r="B994">
-        <v>42430521000129</v>
+      <c r="B994" t="s">
+        <v>2114</v>
       </c>
       <c r="C994" t="s">
         <v>2016</v>
@@ -34980,15 +35670,18 @@
         <v>7</v>
       </c>
       <c r="H994" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="995" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I994">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A995" s="1">
         <v>46101</v>
       </c>
-      <c r="B995">
-        <v>11916506000161</v>
+      <c r="B995" t="s">
+        <v>2115</v>
       </c>
       <c r="C995" t="s">
         <v>922</v>
@@ -35008,13 +35701,16 @@
       <c r="H995" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="996" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I995">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="996" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A996" s="1">
         <v>46101</v>
       </c>
-      <c r="B996">
-        <v>36448699000102</v>
+      <c r="B996" t="s">
+        <v>2116</v>
       </c>
       <c r="C996" t="s">
         <v>2017</v>
@@ -35034,13 +35730,16 @@
       <c r="H996" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="997" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I996">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="997" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A997" s="1">
         <v>46101</v>
       </c>
-      <c r="B997">
-        <v>53214837000108</v>
+      <c r="B997" t="s">
+        <v>2117</v>
       </c>
       <c r="C997" t="s">
         <v>2018</v>
@@ -35060,13 +35759,16 @@
       <c r="H997" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="998" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I997">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="998" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A998" s="1">
         <v>46101</v>
       </c>
-      <c r="B998">
-        <v>45280899000181</v>
+      <c r="B998" t="s">
+        <v>2118</v>
       </c>
       <c r="C998" t="s">
         <v>2019</v>
@@ -35084,15 +35786,18 @@
         <v>7</v>
       </c>
       <c r="H998" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="999" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I998">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="999" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A999" s="1">
         <v>46101</v>
       </c>
-      <c r="B999">
-        <v>64726336000119</v>
+      <c r="B999" t="s">
+        <v>2119</v>
       </c>
       <c r="C999" t="s">
         <v>2020</v>
@@ -35112,13 +35817,16 @@
       <c r="H999" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="1000" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I999">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1000" s="1">
         <v>46101</v>
       </c>
-      <c r="B1000">
-        <v>46592778000138</v>
+      <c r="B1000" t="s">
+        <v>2120</v>
       </c>
       <c r="C1000" t="s">
         <v>2021</v>
@@ -35136,15 +35844,18 @@
         <v>8</v>
       </c>
       <c r="H1000" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1001" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I1000">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1001" s="1">
         <v>46101</v>
       </c>
-      <c r="B1001">
-        <v>64666153000155</v>
+      <c r="B1001" t="s">
+        <v>2121</v>
       </c>
       <c r="C1001" t="s">
         <v>2022</v>
@@ -35162,15 +35873,18 @@
         <v>8</v>
       </c>
       <c r="H1001" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1002" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I1001">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1002" s="1">
         <v>46101</v>
       </c>
-      <c r="B1002">
-        <v>15231029000151</v>
+      <c r="B1002" t="s">
+        <v>2122</v>
       </c>
       <c r="C1002" t="s">
         <v>2023</v>
@@ -35190,13 +35904,16 @@
       <c r="H1002" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1003" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1002">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1003" s="1">
         <v>46101</v>
       </c>
-      <c r="B1003">
-        <v>26078145000107</v>
+      <c r="B1003" t="s">
+        <v>2123</v>
       </c>
       <c r="C1003" t="s">
         <v>2024</v>
@@ -35216,13 +35933,16 @@
       <c r="H1003" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1004" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1003">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1004" s="1">
         <v>46101</v>
       </c>
-      <c r="B1004">
-        <v>64916272000119</v>
+      <c r="B1004" t="s">
+        <v>2124</v>
       </c>
       <c r="C1004" t="s">
         <v>2025</v>
@@ -35240,15 +35960,18 @@
         <v>7</v>
       </c>
       <c r="H1004" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="1005" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I1004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1005" s="1">
         <v>46101</v>
       </c>
-      <c r="B1005">
-        <v>60441695000179</v>
+      <c r="B1005" t="s">
+        <v>2125</v>
       </c>
       <c r="C1005" t="s">
         <v>2026</v>
@@ -35266,15 +35989,18 @@
         <v>7</v>
       </c>
       <c r="H1005" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1006" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I1005">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1006" s="1">
         <v>46101</v>
       </c>
-      <c r="B1006">
-        <v>52270574000183</v>
+      <c r="B1006" t="s">
+        <v>2126</v>
       </c>
       <c r="C1006" t="s">
         <v>2027</v>
@@ -35292,15 +36018,18 @@
         <v>8</v>
       </c>
       <c r="H1006" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1007" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I1006">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1007" s="1">
         <v>46101</v>
       </c>
-      <c r="B1007">
-        <v>9622925000149</v>
+      <c r="B1007" t="s">
+        <v>2127</v>
       </c>
       <c r="C1007" t="s">
         <v>2028</v>
@@ -35320,13 +36049,16 @@
       <c r="H1007" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1008" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1007">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1008" s="1">
         <v>46101</v>
       </c>
-      <c r="B1008">
-        <v>65105661000127</v>
+      <c r="B1008" t="s">
+        <v>2128</v>
       </c>
       <c r="C1008" t="s">
         <v>2029</v>
@@ -35344,15 +36076,18 @@
         <v>7</v>
       </c>
       <c r="H1008" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I1008">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1009" s="1">
         <v>46101</v>
       </c>
-      <c r="B1009">
-        <v>38981445000172</v>
+      <c r="B1009" t="s">
+        <v>2129</v>
       </c>
       <c r="C1009" t="s">
         <v>2030</v>
@@ -35372,13 +36107,16 @@
       <c r="H1009" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1010" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1009">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1010" s="1">
         <v>46101</v>
       </c>
-      <c r="B1010">
-        <v>60282404000147</v>
+      <c r="B1010" t="s">
+        <v>2130</v>
       </c>
       <c r="C1010" t="s">
         <v>2031</v>
@@ -35396,15 +36134,18 @@
         <v>10</v>
       </c>
       <c r="H1010" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1011" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I1010">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1011" s="1">
         <v>46101</v>
       </c>
-      <c r="B1011">
-        <v>59937472000118</v>
+      <c r="B1011" t="s">
+        <v>2131</v>
       </c>
       <c r="C1011" t="s">
         <v>2032</v>
@@ -35424,13 +36165,16 @@
       <c r="H1011" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1012" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1011">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1012" s="1">
         <v>46101</v>
       </c>
-      <c r="B1012">
-        <v>61527450000121</v>
+      <c r="B1012" t="s">
+        <v>2132</v>
       </c>
       <c r="C1012" t="s">
         <v>2033</v>
@@ -35450,13 +36194,16 @@
       <c r="H1012" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1012">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1013" s="1">
         <v>46101</v>
       </c>
-      <c r="B1013">
-        <v>32915024000167</v>
+      <c r="B1013" t="s">
+        <v>2133</v>
       </c>
       <c r="C1013" t="s">
         <v>2034</v>
@@ -35474,15 +36221,15 @@
         <v>7</v>
       </c>
       <c r="H1013" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="1014" spans="1:8" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1014" s="1">
         <v>46101</v>
       </c>
-      <c r="B1014">
-        <v>47281884000163</v>
+      <c r="B1014" t="s">
+        <v>2134</v>
       </c>
       <c r="C1014" t="s">
         <v>2035</v>
@@ -35502,13 +36249,16 @@
       <c r="H1014" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="1015" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1014">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1015" s="1">
         <v>46101</v>
       </c>
-      <c r="B1015">
-        <v>60835621000117</v>
+      <c r="B1015" t="s">
+        <v>2135</v>
       </c>
       <c r="C1015" t="s">
         <v>2036</v>
@@ -35528,13 +36278,16 @@
       <c r="H1015" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="1016" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1015">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1016" s="1">
         <v>46101</v>
       </c>
-      <c r="B1016">
-        <v>64369662000116</v>
+      <c r="B1016" t="s">
+        <v>2136</v>
       </c>
       <c r="C1016" t="s">
         <v>1114</v>
@@ -35552,15 +36305,18 @@
         <v>7</v>
       </c>
       <c r="H1016" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1017" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I1016">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1017" s="1">
         <v>46101</v>
       </c>
-      <c r="B1017">
-        <v>44457840000153</v>
+      <c r="B1017" t="s">
+        <v>2137</v>
       </c>
       <c r="C1017" t="s">
         <v>2037</v>
@@ -35578,15 +36334,18 @@
         <v>13</v>
       </c>
       <c r="H1017" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1018" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I1017" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1018" s="1">
         <v>46101</v>
       </c>
-      <c r="B1018">
-        <v>32315559000288</v>
+      <c r="B1018" t="s">
+        <v>2138</v>
       </c>
       <c r="C1018" t="s">
         <v>2038</v>
@@ -35604,15 +36363,15 @@
         <v>8</v>
       </c>
       <c r="H1018" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1019" spans="1:8" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1019" s="1">
         <v>46101</v>
       </c>
-      <c r="B1019">
-        <v>61414103000192</v>
+      <c r="B1019" t="s">
+        <v>2139</v>
       </c>
       <c r="C1019" t="s">
         <v>2039</v>
@@ -35632,13 +36391,16 @@
       <c r="H1019" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1020" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1019">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1020" s="1">
         <v>46101</v>
       </c>
-      <c r="B1020">
-        <v>51916183000120</v>
+      <c r="B1020" t="s">
+        <v>2140</v>
       </c>
       <c r="C1020" t="s">
         <v>2040</v>
@@ -35656,15 +36418,18 @@
         <v>8</v>
       </c>
       <c r="H1020" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1021" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I1020" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1021" s="1">
         <v>46101</v>
       </c>
-      <c r="B1021">
-        <v>9425553000160</v>
+      <c r="B1021" t="s">
+        <v>2141</v>
       </c>
       <c r="C1021" t="s">
         <v>2041</v>
@@ -35684,8 +36449,11 @@
       <c r="H1021" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1022" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1021">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1022" s="1">
         <v>46102</v>
       </c>
@@ -35708,10 +36476,13 @@
         <v>8</v>
       </c>
       <c r="H1022" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1023" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I1022">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1023" s="1">
         <v>46102</v>
       </c>
@@ -35736,8 +36507,11 @@
       <c r="H1023" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1024" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1023">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1024" s="1">
         <v>46102</v>
       </c>
@@ -35762,8 +36536,11 @@
       <c r="H1024" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="1025" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1024">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1025" s="1">
         <v>46102</v>
       </c>
@@ -35786,10 +36563,13 @@
         <v>8</v>
       </c>
       <c r="H1025" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1026" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I1025">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1026" s="1">
         <v>46102</v>
       </c>
@@ -35812,10 +36592,13 @@
         <v>8</v>
       </c>
       <c r="H1026" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1027" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I1026" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1027" s="1">
         <v>46102</v>
       </c>
@@ -35838,10 +36621,13 @@
         <v>8</v>
       </c>
       <c r="H1027" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1028" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I1027" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1028" s="1">
         <v>46102</v>
       </c>
@@ -35864,10 +36650,13 @@
         <v>8</v>
       </c>
       <c r="H1028" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1029" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I1028">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1029" s="1">
         <v>46102</v>
       </c>
@@ -35892,8 +36681,11 @@
       <c r="H1029" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1029">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1030" s="1">
         <v>46102</v>
       </c>
@@ -35916,10 +36708,13 @@
         <v>929</v>
       </c>
       <c r="H1030" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1031" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I1030">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1031" s="1">
         <v>46102</v>
       </c>
@@ -35944,8 +36739,11 @@
       <c r="H1031" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1032" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1031">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1032" s="1">
         <v>46102</v>
       </c>
@@ -35968,10 +36766,13 @@
         <v>7</v>
       </c>
       <c r="H1032" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1033" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I1032">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1033" s="1">
         <v>46102</v>
       </c>
@@ -35996,8 +36797,11 @@
       <c r="H1033" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1033">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1034" s="1">
         <v>46102</v>
       </c>
@@ -36022,8 +36826,11 @@
       <c r="H1034" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1034">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1035" s="1">
         <v>46102</v>
       </c>
@@ -36046,10 +36853,13 @@
         <v>8</v>
       </c>
       <c r="H1035" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1036" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="I1035">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1036" s="1">
         <v>46102</v>
       </c>
@@ -36072,10 +36882,13 @@
         <v>8</v>
       </c>
       <c r="H1036" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1037" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I1036">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1037" s="1">
         <v>46102</v>
       </c>
@@ -36098,10 +36911,13 @@
         <v>8</v>
       </c>
       <c r="H1037" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1038" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I1037">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1038" s="1">
         <v>46102</v>
       </c>
@@ -36126,8 +36942,11 @@
       <c r="H1038" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1039" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1038">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1039" s="1">
         <v>46102</v>
       </c>
@@ -36150,10 +36969,13 @@
         <v>8</v>
       </c>
       <c r="H1039" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1040" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I1039">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1040" s="1">
         <v>46102</v>
       </c>
@@ -36178,8 +37000,11 @@
       <c r="H1040" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1041" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1040">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1041" s="1">
         <v>46102</v>
       </c>
@@ -36203,6 +37028,1653 @@
       </c>
       <c r="H1041" t="s">
         <v>19</v>
+      </c>
+      <c r="I1041">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1042" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1042" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>2143</v>
+      </c>
+      <c r="D1042" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1042" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1042" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G1042" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1042" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1042">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1043" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1043" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C1043" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D1043" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F1043" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1043" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1043" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1043">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1044" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1044" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C1044" t="s">
+        <v>2148</v>
+      </c>
+      <c r="D1044" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F1044" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1044" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1044" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1044">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1045" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C1045" t="s">
+        <v>2150</v>
+      </c>
+      <c r="D1045" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1045" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1045" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1045" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1045" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1045">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1046" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D1046" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1046" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1046" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1046" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1046" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1047" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C1047" t="s">
+        <v>2154</v>
+      </c>
+      <c r="D1047" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1047" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1047" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1047" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1047" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1048" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D1048" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1048" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1048" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1048" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1048" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1049" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1049" t="s">
+        <v>2157</v>
+      </c>
+      <c r="C1049" t="s">
+        <v>2158</v>
+      </c>
+      <c r="D1049" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1049" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1049" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1049" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1049" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1050" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>2159</v>
+      </c>
+      <c r="C1050" t="s">
+        <v>2160</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1050" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1050" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1050" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1050" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1051" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C1051" t="s">
+        <v>2162</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1051" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1051" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1051" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1051" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1052" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C1052" t="s">
+        <v>2164</v>
+      </c>
+      <c r="D1052" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1052" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1052" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1052" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1052" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1053" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1053" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C1053" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D1053" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1053" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1053" t="s">
+        <v>2010</v>
+      </c>
+      <c r="G1053" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1053" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1054" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C1054" t="s">
+        <v>2168</v>
+      </c>
+      <c r="D1054" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1054" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1054" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1054" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1054" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1055" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>2169</v>
+      </c>
+      <c r="C1055" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D1055" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1055" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1055" t="s">
+        <v>2010</v>
+      </c>
+      <c r="G1055" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1055" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1056" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C1056" t="s">
+        <v>2172</v>
+      </c>
+      <c r="D1056" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1056" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1056" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1056" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1056" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1057" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C1057" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D1057" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1057" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1057" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1057" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1057" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1058" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>2175</v>
+      </c>
+      <c r="C1058" t="s">
+        <v>2176</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1058" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1058" t="s">
+        <v>2010</v>
+      </c>
+      <c r="G1058" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1058" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1059" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C1059" t="s">
+        <v>2178</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1059" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1059" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1059" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1059" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1060" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C1060" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D1060" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1060" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1060" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1060" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1060" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1061" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C1061" t="s">
+        <v>2182</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1061" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1061" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1061" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1061" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1062" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C1062" t="s">
+        <v>2184</v>
+      </c>
+      <c r="D1062" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1062" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1062" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1062" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1062" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1063" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1063" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1063" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D1063" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1063" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1063" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1063" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1063" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1064" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1064" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C1064" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D1064" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1064" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1064" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1064" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1064" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1065" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1065" t="s">
+        <v>2189</v>
+      </c>
+      <c r="C1065" t="s">
+        <v>2190</v>
+      </c>
+      <c r="D1065" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1065" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1065" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1065" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1065" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1066" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1066" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>2192</v>
+      </c>
+      <c r="D1066" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1066" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1066" t="s">
+        <v>1753</v>
+      </c>
+      <c r="G1066" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1066" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1067" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1067" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C1067" t="s">
+        <v>2194</v>
+      </c>
+      <c r="D1067" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1067" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1067" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1067" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1067" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1068" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1068" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C1068" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D1068" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1068" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1068" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1068" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1068" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1069" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1069" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C1069" t="s">
+        <v>2198</v>
+      </c>
+      <c r="D1069" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1069" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1069" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1069" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1069" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1070" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1070" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C1070" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D1070" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1070" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1070" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1070" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1070" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1071" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1071" t="s">
+        <v>2201</v>
+      </c>
+      <c r="C1071" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D1071" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1071" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1071" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1071" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1071" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1072" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1072" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C1072" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D1072" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1072" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1072" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1072" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1072" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1073" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1073" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C1073" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D1073" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1073" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1073" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1073" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1073" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1074" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1074" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>2208</v>
+      </c>
+      <c r="D1074" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1074" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1074" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1074" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1074" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1075" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1075" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C1075" t="s">
+        <v>2210</v>
+      </c>
+      <c r="D1075" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1075" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1075" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1075" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1075" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1076" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1076" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C1076" t="s">
+        <v>2212</v>
+      </c>
+      <c r="D1076" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1076" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1076" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1076" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1076" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1077" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1077" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C1077" t="s">
+        <v>2214</v>
+      </c>
+      <c r="D1077" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1077" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1077" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1077" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1077" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1078" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1078" t="s">
+        <v>2215</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>2216</v>
+      </c>
+      <c r="D1078" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1078" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1078" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1078" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1078" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1079" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1079" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C1079" t="s">
+        <v>2218</v>
+      </c>
+      <c r="D1079" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1079" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1079" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1079" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1079" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1080" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1080" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D1080" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1080" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1080" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1080" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1080" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1081" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1081" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C1081" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D1081" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1081" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1081" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1081" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1081" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1082" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1082" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>2224</v>
+      </c>
+      <c r="D1082" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1082" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1082" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1082" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1082" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1083" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1083" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D1083" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1083" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1083" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1083" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1083" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1084" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1084" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C1084" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1084" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1084" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1084" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1084" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1084" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1085" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1085" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C1085" t="s">
+        <v>2230</v>
+      </c>
+      <c r="D1085" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1085" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1085" t="s">
+        <v>2010</v>
+      </c>
+      <c r="G1085" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1085" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1086" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1086" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C1086" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D1086" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1086" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1086" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1086" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1086" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1087" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1087" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C1087" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D1087" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1087" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1087" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1087" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1087" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1088" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1088" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D1088" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1088" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1088" t="s">
+        <v>2237</v>
+      </c>
+      <c r="G1088" t="s">
+        <v>929</v>
+      </c>
+      <c r="H1088" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1089" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1089" t="s">
+        <v>2238</v>
+      </c>
+      <c r="C1089" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D1089" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1089" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1089" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1089" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1089" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1090" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1090" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C1090" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D1090" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1090" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1090" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1090" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1090" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1091" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1091" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C1091" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D1091" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1091" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1091" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1091" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1091" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1092" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1092" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C1092" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D1092" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1092" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1092" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1092" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1092" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1093" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1093" t="s">
+        <v>2246</v>
+      </c>
+      <c r="C1093" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D1093" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1093" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1093" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1093" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1093" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1094" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1094" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D1094" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1094" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1094" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1094" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1094" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1095" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1095" t="s">
+        <v>2250</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>2251</v>
+      </c>
+      <c r="D1095" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1095" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1095" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1095" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1095" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1096" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1096" t="s">
+        <v>2252</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D1096" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1096" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1096" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1096" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1096" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1097" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1097" t="s">
+        <v>2254</v>
+      </c>
+      <c r="C1097" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D1097" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1097" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1097" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1097" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1097" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1098" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1098" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C1098" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D1098" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1098" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1098" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1098" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1098" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1099" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1099" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C1099" t="s">
+        <v>2259</v>
+      </c>
+      <c r="D1099" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1099" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1099" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1099" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1099" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1100" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1100" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C1100" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D1100" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1100" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1100" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1100" t="s">
+        <v>2262</v>
+      </c>
+      <c r="H1100" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1101" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1101" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C1101" t="s">
+        <v>2264</v>
+      </c>
+      <c r="D1101" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1101" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1101" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1101" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1101" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1102" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1102" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C1102" t="s">
+        <v>2266</v>
+      </c>
+      <c r="D1102" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1102" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1102" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1102" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1103" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1103" t="s">
+        <v>2267</v>
+      </c>
+      <c r="C1103" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D1103" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1103" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1103" t="s">
+        <v>1753</v>
+      </c>
+      <c r="G1103" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1103" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1104" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>2269</v>
+      </c>
+      <c r="C1104" t="s">
+        <v>2270</v>
+      </c>
+      <c r="D1104" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E1104" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1104" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1104" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1104" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
